--- a/Financial Analysis/SONO.xlsx
+++ b/Financial Analysis/SONO.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7333F251-8A78-4C92-88EF-EA9EA5651C20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFB8AFD7-F0BC-49B9-A8D4-EBC5C27CF584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{AE038E36-4BE5-4CF0-B4AF-8B96610ED707}"/>
   </bookViews>
@@ -345,14 +345,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>30</xdr:col>
-      <xdr:colOff>15240</xdr:colOff>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>30</xdr:col>
-      <xdr:colOff>15240</xdr:colOff>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
       <xdr:row>34</xdr:row>
       <xdr:rowOff>83820</xdr:rowOff>
     </xdr:to>
@@ -369,7 +369,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="22113240" y="0"/>
+          <a:off x="24300180" y="0"/>
           <a:ext cx="0" cy="6301740"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -768,17 +768,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="5">
-        <v>8.9</v>
+        <v>15.22</v>
       </c>
       <c r="E3" s="3">
-        <v>45751</v>
+        <v>45918</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45751</v>
+        <v>45918</v>
       </c>
       <c r="G3" s="3">
-        <v>45784</v>
+        <v>45973</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -786,11 +786,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="4">
-        <f>119.1</f>
-        <v>119.1</v>
+        <f>120.9</f>
+        <v>120.9</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -799,7 +799,7 @@
       </c>
       <c r="D5" s="4">
         <f>D3*D4</f>
-        <v>1059.99</v>
+        <v>1840.0980000000002</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -807,11 +807,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="4">
-        <f>280+47.9</f>
-        <v>327.9</v>
+        <f>201.3+52.7</f>
+        <v>254</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -822,7 +822,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -831,7 +831,7 @@
       </c>
       <c r="D8" s="4">
         <f>D6+D7</f>
-        <v>327.9</v>
+        <v>254</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -840,7 +840,7 @@
       </c>
       <c r="D9" s="4">
         <f>D5-D8</f>
-        <v>732.09</v>
+        <v>1586.0980000000002</v>
       </c>
     </row>
   </sheetData>
@@ -855,6 +855,7 @@
   <cols>
     <col min="2" max="2" width="17.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="35" width="10.5546875" customWidth="1"/>
+    <col min="37" max="54" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="56" max="56" width="11.88671875" bestFit="1" customWidth="1"/>
     <col min="57" max="57" width="17" customWidth="1"/>
   </cols>
@@ -957,6 +958,60 @@
         <v>45930</v>
       </c>
       <c r="AI1" s="10"/>
+      <c r="AK1" s="10">
+        <v>43373</v>
+      </c>
+      <c r="AL1" s="10">
+        <v>43738</v>
+      </c>
+      <c r="AM1" s="10">
+        <v>44104</v>
+      </c>
+      <c r="AN1" s="10">
+        <v>44469</v>
+      </c>
+      <c r="AO1" s="10">
+        <v>44834</v>
+      </c>
+      <c r="AP1" s="10">
+        <v>45199</v>
+      </c>
+      <c r="AQ1" s="10">
+        <v>45565</v>
+      </c>
+      <c r="AR1" s="10">
+        <v>45930</v>
+      </c>
+      <c r="AS1" s="10">
+        <v>46295</v>
+      </c>
+      <c r="AT1" s="10">
+        <v>46660</v>
+      </c>
+      <c r="AU1" s="10">
+        <v>47026</v>
+      </c>
+      <c r="AV1" s="10">
+        <v>47391</v>
+      </c>
+      <c r="AW1" s="10">
+        <v>47756</v>
+      </c>
+      <c r="AX1" s="10">
+        <v>48121</v>
+      </c>
+      <c r="AY1" s="10">
+        <v>48487</v>
+      </c>
+      <c r="AZ1" s="10">
+        <v>48852</v>
+      </c>
+      <c r="BA1" s="10">
+        <v>49217</v>
+      </c>
+      <c r="BB1" s="10">
+        <v>49582</v>
+      </c>
     </row>
     <row r="2" spans="2:176" x14ac:dyDescent="0.3">
       <c r="C2" s="6" t="s">
@@ -1203,16 +1258,14 @@
         <v>550.9</v>
       </c>
       <c r="AF3" s="7">
-        <f>AB3*0.95</f>
-        <v>240.06499999999997</v>
+        <v>259.8</v>
       </c>
       <c r="AG3" s="7">
-        <f>AC3*0.93</f>
-        <v>369.30300000000005</v>
+        <v>344.8</v>
       </c>
       <c r="AH3" s="7">
-        <f t="shared" ref="AH3" si="0">AD3*0.95</f>
-        <v>242.63</v>
+        <f>AD3*1.03</f>
+        <v>263.06200000000001</v>
       </c>
       <c r="AI3" s="7"/>
       <c r="AK3" s="7">
@@ -1245,47 +1298,47 @@
       </c>
       <c r="AR3" s="7">
         <f>SUM(AE3:AH3)</f>
-        <v>1402.8980000000001</v>
+        <v>1418.5619999999999</v>
       </c>
       <c r="AS3" s="7">
-        <f>AR3*1.05</f>
-        <v>1473.0429000000001</v>
+        <f>AR3*1.08</f>
+        <v>1532.0469599999999</v>
       </c>
       <c r="AT3" s="7">
-        <f>AS3*1.03</f>
-        <v>1517.2341870000002</v>
+        <f>AS3*1.05</f>
+        <v>1608.649308</v>
       </c>
       <c r="AU3" s="7">
-        <f>AT3*1.02</f>
-        <v>1547.5788707400002</v>
+        <f>AT3*1.03</f>
+        <v>1656.90878724</v>
       </c>
       <c r="AV3" s="7">
         <f>AU3*1.02</f>
-        <v>1578.5304481548003</v>
+        <v>1690.0469629848001</v>
       </c>
       <c r="AW3" s="7">
         <f>AV3*1.02</f>
-        <v>1610.1010571178963</v>
+        <v>1723.847902244496</v>
       </c>
       <c r="AX3" s="7">
-        <f t="shared" ref="AX3:BB3" si="1">AW3*1.01</f>
-        <v>1626.2020676890752</v>
+        <f t="shared" ref="AX3:BB3" si="0">AW3*1.02</f>
+        <v>1758.3248602893859</v>
       </c>
       <c r="AY3" s="7">
-        <f t="shared" si="1"/>
-        <v>1642.4640883659661</v>
+        <f t="shared" si="0"/>
+        <v>1793.4913574951736</v>
       </c>
       <c r="AZ3" s="7">
-        <f t="shared" si="1"/>
-        <v>1658.8887292496258</v>
+        <f t="shared" si="0"/>
+        <v>1829.3611846450772</v>
       </c>
       <c r="BA3" s="7">
-        <f t="shared" si="1"/>
-        <v>1675.4776165421222</v>
+        <f t="shared" si="0"/>
+        <v>1865.9484083379787</v>
       </c>
       <c r="BB3" s="7">
-        <f t="shared" si="1"/>
-        <v>1692.2323927075433</v>
+        <f t="shared" si="0"/>
+        <v>1903.2673765047382</v>
       </c>
     </row>
     <row r="4" spans="2:176" x14ac:dyDescent="0.3">
@@ -1380,16 +1433,14 @@
         <v>309.5</v>
       </c>
       <c r="AF4" s="4">
-        <f t="shared" ref="AF4:AH4" si="2">AF3-AF5</f>
-        <v>134.43639999999999</v>
+        <v>146.1</v>
       </c>
       <c r="AG4" s="4">
-        <f t="shared" si="2"/>
-        <v>199.42362000000003</v>
+        <v>195</v>
       </c>
       <c r="AH4" s="4">
-        <f t="shared" si="2"/>
-        <v>145.57799999999997</v>
+        <f t="shared" ref="AH4" si="1">AH3-AH5</f>
+        <v>157.8372</v>
       </c>
       <c r="AI4" s="4"/>
       <c r="AK4" s="4">
@@ -1422,47 +1473,47 @@
       </c>
       <c r="AR4" s="4">
         <f>SUM(AE4:AH4)</f>
-        <v>788.93802000000005</v>
+        <v>808.43720000000008</v>
       </c>
       <c r="AS4" s="4">
-        <f t="shared" ref="AS4:AW4" si="3">AS3-AS5</f>
-        <v>810.17359500000009</v>
+        <f t="shared" ref="AS4:AW4" si="2">AS3-AS5</f>
+        <v>842.62582799999996</v>
       </c>
       <c r="AT4" s="4">
+        <f t="shared" si="2"/>
+        <v>868.67062632</v>
+      </c>
+      <c r="AU4" s="4">
+        <f t="shared" si="2"/>
+        <v>878.16165723720007</v>
+      </c>
+      <c r="AV4" s="4">
+        <f t="shared" si="2"/>
+        <v>878.8244207520961</v>
+      </c>
+      <c r="AW4" s="4">
+        <f t="shared" si="2"/>
+        <v>896.40090916713791</v>
+      </c>
+      <c r="AX4" s="4">
+        <f t="shared" ref="AX4:BB4" si="3">AX3-AX5</f>
+        <v>914.32892735048074</v>
+      </c>
+      <c r="AY4" s="4">
         <f t="shared" si="3"/>
-        <v>819.30646098000011</v>
-      </c>
-      <c r="AU4" s="4">
+        <v>932.61550589749027</v>
+      </c>
+      <c r="AZ4" s="4">
         <f t="shared" si="3"/>
-        <v>820.21680149220015</v>
-      </c>
-      <c r="AV4" s="4">
+        <v>951.26781601544019</v>
+      </c>
+      <c r="BA4" s="4">
         <f t="shared" si="3"/>
-        <v>820.83583304049614</v>
-      </c>
-      <c r="AW4" s="4">
+        <v>970.29317233574898</v>
+      </c>
+      <c r="BB4" s="4">
         <f t="shared" si="3"/>
-        <v>837.25254970130607</v>
-      </c>
-      <c r="AX4" s="4">
-        <f t="shared" ref="AX4:BB4" si="4">AX3-AX5</f>
-        <v>845.62507519831911</v>
-      </c>
-      <c r="AY4" s="4">
-        <f t="shared" si="4"/>
-        <v>854.08132595030236</v>
-      </c>
-      <c r="AZ4" s="4">
-        <f t="shared" si="4"/>
-        <v>862.62213920980548</v>
-      </c>
-      <c r="BA4" s="4">
-        <f t="shared" si="4"/>
-        <v>871.24836060190353</v>
-      </c>
-      <c r="BB4" s="4">
-        <f t="shared" si="4"/>
-        <v>879.96084420792261</v>
+        <v>989.69903578246385</v>
       </c>
     </row>
     <row r="5" spans="2:176" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1470,132 +1521,132 @@
         <v>24</v>
       </c>
       <c r="C5" s="7">
-        <f t="shared" ref="C5:Q5" si="5">C3-C4</f>
+        <f t="shared" ref="C5:Q5" si="4">C3-C4</f>
         <v>196.2</v>
       </c>
       <c r="D5" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>81.299999999999983</v>
       </c>
       <c r="E5" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>95.5</v>
       </c>
       <c r="F5" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>116.19999999999999</v>
       </c>
       <c r="G5" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>195.29999999999995</v>
       </c>
       <c r="H5" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>90.399999999999991</v>
       </c>
       <c r="I5" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>117.30000000000001</v>
       </c>
       <c r="J5" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>124.29999999999998</v>
       </c>
       <c r="K5" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>227.60000000000002</v>
       </c>
       <c r="L5" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>73</v>
       </c>
       <c r="M5" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>109.80000000000001</v>
       </c>
       <c r="N5" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>161.5</v>
       </c>
       <c r="O5" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>299.40000000000003</v>
       </c>
       <c r="P5" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>165.7</v>
       </c>
       <c r="Q5" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>177.89999999999998</v>
       </c>
       <c r="R5" s="7">
-        <f t="shared" ref="R5" si="6">R3-R4</f>
+        <f t="shared" ref="R5" si="5">R3-R4</f>
         <v>166.79999999999998</v>
       </c>
       <c r="S5" s="7">
-        <f t="shared" ref="S5:T5" si="7">S3-S4</f>
+        <f t="shared" ref="S5:T5" si="6">S3-S4</f>
         <v>317.39999999999998</v>
       </c>
       <c r="T5" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>179.10000000000002</v>
       </c>
       <c r="U5" s="7">
-        <f t="shared" ref="U5" si="8">U3-U4</f>
+        <f t="shared" ref="U5" si="7">U3-U4</f>
         <v>175.9</v>
       </c>
       <c r="V5" s="7">
-        <f t="shared" ref="V5:W5" si="9">V3-V4</f>
+        <f t="shared" ref="V5:W5" si="8">V3-V4</f>
         <v>124.10000000000002</v>
       </c>
       <c r="W5" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>285.10000000000002</v>
       </c>
       <c r="X5" s="7">
-        <f t="shared" ref="X5" si="10">X3-X4</f>
+        <f t="shared" ref="X5" si="9">X3-X4</f>
         <v>131.6</v>
       </c>
       <c r="Y5" s="7">
-        <f t="shared" ref="Y5" si="11">Y3-Y4</f>
+        <f t="shared" ref="Y5" si="10">Y3-Y4</f>
         <v>171.79999999999998</v>
       </c>
       <c r="Z5" s="7">
-        <f t="shared" ref="Z5:AA5" si="12">Z3-Z4</f>
+        <f t="shared" ref="Z5:AA5" si="11">Z3-Z4</f>
         <v>128.00000000000003</v>
       </c>
       <c r="AA5" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>282.7</v>
       </c>
       <c r="AB5" s="7">
-        <f t="shared" ref="AB5" si="13">AB3-AB4</f>
+        <f t="shared" ref="AB5" si="12">AB3-AB4</f>
         <v>112.1</v>
       </c>
       <c r="AC5" s="7">
-        <f t="shared" ref="AC5" si="14">AC3-AC4</f>
+        <f t="shared" ref="AC5" si="13">AC3-AC4</f>
         <v>191.60000000000002</v>
       </c>
       <c r="AD5" s="7">
-        <f t="shared" ref="AD5:AE5" si="15">AD3-AD4</f>
+        <f t="shared" ref="AD5:AG5" si="14">AD3-AD4</f>
         <v>103</v>
       </c>
       <c r="AE5" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>241.39999999999998</v>
       </c>
       <c r="AF5" s="7">
-        <f>AF3*0.44</f>
-        <v>105.62859999999999</v>
+        <f t="shared" si="14"/>
+        <v>113.70000000000002</v>
       </c>
       <c r="AG5" s="7">
-        <f>AG3*0.46</f>
-        <v>169.87938000000003</v>
+        <f t="shared" si="14"/>
+        <v>149.80000000000001</v>
       </c>
       <c r="AH5" s="7">
         <f>AH3*0.4</f>
-        <v>97.052000000000007</v>
+        <v>105.22480000000002</v>
       </c>
       <c r="AI5" s="7"/>
       <c r="AK5" s="7">
@@ -1615,60 +1666,60 @@
         <v>809.79999999999984</v>
       </c>
       <c r="AO5" s="7">
-        <f t="shared" ref="AO5:AR5" si="16">AO3-AO4</f>
+        <f t="shared" ref="AO5:AR5" si="15">AO3-AO4</f>
         <v>796.5</v>
       </c>
       <c r="AP5" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>716.49999999999966</v>
       </c>
       <c r="AQ5" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>689.4</v>
       </c>
       <c r="AR5" s="7">
-        <f t="shared" si="16"/>
-        <v>613.95998000000009</v>
+        <f t="shared" si="15"/>
+        <v>610.12479999999982</v>
       </c>
       <c r="AS5" s="7">
         <f>AS3*0.45</f>
-        <v>662.86930500000005</v>
+        <v>689.42113199999994</v>
       </c>
       <c r="AT5" s="7">
         <f>AT3*0.46</f>
-        <v>697.92772602000014</v>
+        <v>739.97868168000002</v>
       </c>
       <c r="AU5" s="7">
-        <f t="shared" ref="AU5" si="17">AU3*0.47</f>
-        <v>727.36206924780004</v>
+        <f t="shared" ref="AU5" si="16">AU3*0.47</f>
+        <v>778.74713000279996</v>
       </c>
       <c r="AV5" s="7">
         <f>AV3*0.48</f>
-        <v>757.69461511430416</v>
+        <v>811.22254223270397</v>
       </c>
       <c r="AW5" s="7">
-        <f t="shared" ref="AW5:BB5" si="18">AW3*0.48</f>
-        <v>772.84850741659022</v>
+        <f t="shared" ref="AW5:BB5" si="17">AW3*0.48</f>
+        <v>827.44699307735812</v>
       </c>
       <c r="AX5" s="7">
-        <f t="shared" si="18"/>
-        <v>780.57699249075608</v>
+        <f t="shared" si="17"/>
+        <v>843.99593293890518</v>
       </c>
       <c r="AY5" s="7">
-        <f t="shared" si="18"/>
-        <v>788.38276241566371</v>
+        <f t="shared" si="17"/>
+        <v>860.87585159768332</v>
       </c>
       <c r="AZ5" s="7">
-        <f t="shared" si="18"/>
-        <v>796.26659003982036</v>
+        <f t="shared" si="17"/>
+        <v>878.09336862963698</v>
       </c>
       <c r="BA5" s="7">
-        <f t="shared" si="18"/>
-        <v>804.22925594021865</v>
+        <f t="shared" si="17"/>
+        <v>895.65523600222969</v>
       </c>
       <c r="BB5" s="7">
-        <f t="shared" si="18"/>
-        <v>812.27154849962074</v>
+        <f t="shared" si="17"/>
+        <v>913.56834072227434</v>
       </c>
     </row>
     <row r="6" spans="2:176" x14ac:dyDescent="0.3">
@@ -1763,16 +1814,13 @@
         <v>80.8</v>
       </c>
       <c r="AF6" s="4">
-        <f t="shared" ref="AF6:AG6" si="19">AB6*1.03</f>
-        <v>82.709000000000003</v>
+        <v>77.400000000000006</v>
       </c>
       <c r="AG6" s="4">
-        <f t="shared" si="19"/>
-        <v>76.426000000000002</v>
+        <v>59.8</v>
       </c>
       <c r="AH6" s="4">
-        <f>AD6*1.01</f>
-        <v>71.507999999999996</v>
+        <v>65</v>
       </c>
       <c r="AI6" s="4"/>
       <c r="AK6" s="4">
@@ -1805,47 +1853,47 @@
       </c>
       <c r="AR6" s="4">
         <f>SUM(AE6:AH6)</f>
-        <v>311.44299999999998</v>
+        <v>283</v>
       </c>
       <c r="AS6" s="4">
-        <f>AR6*1.02</f>
-        <v>317.67185999999998</v>
+        <f>AR6*0.9</f>
+        <v>254.70000000000002</v>
       </c>
       <c r="AT6" s="4">
-        <f>AS6*1.02</f>
-        <v>324.02529720000001</v>
+        <f t="shared" ref="AT6:AV6" si="18">AS6*1.01</f>
+        <v>257.24700000000001</v>
       </c>
       <c r="AU6" s="4">
-        <f>AT6*1.02</f>
-        <v>330.50580314400003</v>
+        <f t="shared" si="18"/>
+        <v>259.81947000000002</v>
       </c>
       <c r="AV6" s="4">
-        <f t="shared" ref="AV6" si="20">AU6*1.01</f>
-        <v>333.81086117544004</v>
+        <f t="shared" si="18"/>
+        <v>262.41766470000005</v>
       </c>
       <c r="AW6" s="4">
-        <f t="shared" ref="AW6" si="21">AV6*1.01</f>
-        <v>337.14896978719446</v>
+        <f t="shared" ref="AW6" si="19">AV6*1.01</f>
+        <v>265.04184134700006</v>
       </c>
       <c r="AX6" s="4">
-        <f t="shared" ref="AX6" si="22">AW6*1.01</f>
-        <v>340.5204594850664</v>
+        <f t="shared" ref="AX6" si="20">AW6*1.01</f>
+        <v>267.69225976047005</v>
       </c>
       <c r="AY6" s="4">
-        <f t="shared" ref="AY6" si="23">AX6*1.01</f>
-        <v>343.92566407991706</v>
+        <f t="shared" ref="AY6" si="21">AX6*1.01</f>
+        <v>270.36918235807474</v>
       </c>
       <c r="AZ6" s="4">
-        <f t="shared" ref="AZ6" si="24">AY6*1.01</f>
-        <v>347.36492072071621</v>
+        <f t="shared" ref="AZ6" si="22">AY6*1.01</f>
+        <v>273.07287418165549</v>
       </c>
       <c r="BA6" s="4">
-        <f t="shared" ref="BA6" si="25">AZ6*1.01</f>
-        <v>350.8385699279234</v>
+        <f t="shared" ref="BA6" si="23">AZ6*1.01</f>
+        <v>275.80360292347206</v>
       </c>
       <c r="BB6" s="4">
-        <f t="shared" ref="BB6" si="26">BA6*1.01</f>
-        <v>354.34695562720265</v>
+        <f t="shared" ref="BB6" si="24">BA6*1.01</f>
+        <v>278.5616389527068</v>
       </c>
     </row>
     <row r="7" spans="2:176" x14ac:dyDescent="0.3">
@@ -1940,16 +1988,14 @@
         <v>86.6</v>
       </c>
       <c r="AF7" s="4">
-        <f>AF3*0.26</f>
-        <v>62.416899999999991</v>
+        <v>64.2</v>
       </c>
       <c r="AG7" s="4">
-        <f>AG3*0.19</f>
-        <v>70.167570000000012</v>
+        <v>62.6</v>
       </c>
       <c r="AH7" s="4">
         <f>AH3*0.3</f>
-        <v>72.789000000000001</v>
+        <v>78.918599999999998</v>
       </c>
       <c r="AI7" s="4"/>
       <c r="AK7" s="4">
@@ -1982,47 +2028,47 @@
       </c>
       <c r="AR7" s="4">
         <f>SUM(AE7:AH7)</f>
-        <v>291.97347000000002</v>
+        <v>292.3186</v>
       </c>
       <c r="AS7" s="4">
         <f>AS3*0.2</f>
-        <v>294.60858000000002</v>
+        <v>306.40939199999997</v>
       </c>
       <c r="AT7" s="4">
         <f>AT3*0.19</f>
-        <v>288.27449553000002</v>
+        <v>305.64336852000002</v>
       </c>
       <c r="AU7" s="4">
         <f>AU3*0.18</f>
-        <v>278.56419673320005</v>
+        <v>298.24358170319999</v>
       </c>
       <c r="AV7" s="4">
         <f>AV3*0.17</f>
-        <v>268.35017618631605</v>
+        <v>287.30798370741604</v>
       </c>
       <c r="AW7" s="4">
-        <f t="shared" ref="AW7" si="27">AW3*0.16</f>
-        <v>257.61616913886343</v>
+        <f t="shared" ref="AW7" si="25">AW3*0.16</f>
+        <v>275.81566435911935</v>
       </c>
       <c r="AX7" s="4">
-        <f t="shared" ref="AX7:BB7" si="28">AX3*0.16</f>
-        <v>260.19233083025205</v>
+        <f t="shared" ref="AX7:BB7" si="26">AX3*0.16</f>
+        <v>281.33197764630177</v>
       </c>
       <c r="AY7" s="4">
-        <f t="shared" si="28"/>
-        <v>262.79425413855455</v>
+        <f t="shared" si="26"/>
+        <v>286.95861719922777</v>
       </c>
       <c r="AZ7" s="4">
-        <f t="shared" si="28"/>
-        <v>265.42219667994016</v>
+        <f t="shared" si="26"/>
+        <v>292.69778954321237</v>
       </c>
       <c r="BA7" s="4">
-        <f t="shared" si="28"/>
-        <v>268.07641864673957</v>
+        <f t="shared" si="26"/>
+        <v>298.5517453340766</v>
       </c>
       <c r="BB7" s="4">
-        <f t="shared" si="28"/>
-        <v>270.75718283320691</v>
+        <f t="shared" si="26"/>
+        <v>304.5227802407581</v>
       </c>
     </row>
     <row r="8" spans="2:176" x14ac:dyDescent="0.3">
@@ -2117,12 +2163,10 @@
         <v>25.8</v>
       </c>
       <c r="AF8" s="4">
-        <f>AB8*0.75</f>
-        <v>30.599999999999998</v>
+        <v>33.200000000000003</v>
       </c>
       <c r="AG8" s="4">
-        <f>AC8*0.95</f>
-        <v>31.540000000000003</v>
+        <v>30.3</v>
       </c>
       <c r="AH8" s="4">
         <f>AD8*1.15</f>
@@ -2159,47 +2203,47 @@
       </c>
       <c r="AR8" s="4">
         <f>SUM(AE8:AH8)</f>
-        <v>120.6</v>
+        <v>121.96</v>
       </c>
       <c r="AS8" s="4">
-        <f>AR8*1.02</f>
-        <v>123.012</v>
+        <f>AR8*1.01</f>
+        <v>123.17959999999999</v>
       </c>
       <c r="AT8" s="4">
-        <f>AS8*1.02</f>
-        <v>125.47224</v>
+        <f t="shared" ref="AT8:BB8" si="27">AS8*1.01</f>
+        <v>124.411396</v>
       </c>
       <c r="AU8" s="4">
-        <f t="shared" ref="AU8:AV8" si="29">AT8*1.02</f>
-        <v>127.9816848</v>
+        <f t="shared" si="27"/>
+        <v>125.65550996</v>
       </c>
       <c r="AV8" s="4">
-        <f t="shared" si="29"/>
-        <v>130.541318496</v>
+        <f t="shared" si="27"/>
+        <v>126.91206505960001</v>
       </c>
       <c r="AW8" s="4">
-        <f>AV8*1.01</f>
-        <v>131.84673168096</v>
+        <f t="shared" si="27"/>
+        <v>128.18118571019602</v>
       </c>
       <c r="AX8" s="4">
-        <f t="shared" ref="AX8:BB8" si="30">AW8*1.01</f>
-        <v>133.16519899776961</v>
+        <f t="shared" si="27"/>
+        <v>129.46299756729798</v>
       </c>
       <c r="AY8" s="4">
-        <f t="shared" si="30"/>
-        <v>134.49685098774731</v>
+        <f t="shared" si="27"/>
+        <v>130.75762754297097</v>
       </c>
       <c r="AZ8" s="4">
-        <f t="shared" si="30"/>
-        <v>135.84181949762478</v>
+        <f t="shared" si="27"/>
+        <v>132.06520381840068</v>
       </c>
       <c r="BA8" s="4">
-        <f t="shared" si="30"/>
-        <v>137.20023769260104</v>
+        <f t="shared" si="27"/>
+        <v>133.3858558565847</v>
       </c>
       <c r="BB8" s="4">
-        <f t="shared" si="30"/>
-        <v>138.57224006952706</v>
+        <f t="shared" si="27"/>
+        <v>134.71971441515055</v>
       </c>
     </row>
     <row r="9" spans="2:176" x14ac:dyDescent="0.3">
@@ -2207,132 +2251,132 @@
         <v>28</v>
       </c>
       <c r="C9" s="4">
-        <f t="shared" ref="C9:M9" si="31">C6+C7+C8</f>
+        <f t="shared" ref="C9:M9" si="28">C6+C7+C8</f>
         <v>149.9</v>
       </c>
       <c r="D9" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="28"/>
         <v>115</v>
       </c>
       <c r="E9" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="28"/>
         <v>117.1</v>
       </c>
       <c r="F9" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="28"/>
         <v>116.1</v>
       </c>
       <c r="G9" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="28"/>
         <v>126.8</v>
       </c>
       <c r="H9" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="28"/>
         <v>113.4</v>
       </c>
       <c r="I9" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="28"/>
         <v>132.5</v>
       </c>
       <c r="J9" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="28"/>
         <v>149.1</v>
       </c>
       <c r="K9" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="28"/>
         <v>160.1</v>
       </c>
       <c r="L9" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="28"/>
         <v>126.19999999999999</v>
       </c>
       <c r="M9" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="28"/>
         <v>166.79999999999998</v>
       </c>
       <c r="N9" s="4">
-        <f t="shared" ref="N9:O9" si="32">N6+N7+N8</f>
+        <f t="shared" ref="N9:O9" si="29">N6+N7+N8</f>
         <v>146.1</v>
       </c>
       <c r="O9" s="4">
+        <f t="shared" si="29"/>
+        <v>161.9</v>
+      </c>
+      <c r="P9" s="4">
+        <f t="shared" ref="P9:Q9" si="30">P6+P7+P8</f>
+        <v>153.39999999999998</v>
+      </c>
+      <c r="Q9" s="4">
+        <f t="shared" si="30"/>
+        <v>161.10000000000002</v>
+      </c>
+      <c r="R9" s="4">
+        <f t="shared" ref="R9" si="31">R6+R7+R8</f>
+        <v>178.5</v>
+      </c>
+      <c r="S9" s="4">
+        <f t="shared" ref="S9:T9" si="32">S6+S7+S8</f>
+        <v>184.7</v>
+      </c>
+      <c r="T9" s="4">
         <f t="shared" si="32"/>
-        <v>161.9</v>
-      </c>
-      <c r="P9" s="4">
-        <f t="shared" ref="P9:Q9" si="33">P6+P7+P8</f>
-        <v>153.39999999999998</v>
-      </c>
-      <c r="Q9" s="4">
-        <f t="shared" si="33"/>
-        <v>161.10000000000002</v>
-      </c>
-      <c r="R9" s="4">
-        <f t="shared" ref="R9" si="34">R6+R7+R8</f>
-        <v>178.5</v>
-      </c>
-      <c r="S9" s="4">
-        <f t="shared" ref="S9:T9" si="35">S6+S7+S8</f>
-        <v>184.7</v>
-      </c>
-      <c r="T9" s="4">
-        <f t="shared" si="35"/>
         <v>169</v>
       </c>
       <c r="U9" s="4">
-        <f t="shared" ref="U9" si="36">U6+U7+U8</f>
+        <f t="shared" ref="U9" si="33">U6+U7+U8</f>
         <v>168.9</v>
       </c>
       <c r="V9" s="4">
-        <f t="shared" ref="V9:W9" si="37">V6+V7+V8</f>
+        <f t="shared" ref="V9:W9" si="34">V6+V7+V8</f>
         <v>184.09999999999997</v>
       </c>
       <c r="W9" s="4">
+        <f t="shared" si="34"/>
+        <v>198.70000000000002</v>
+      </c>
+      <c r="X9" s="4">
+        <f t="shared" ref="X9" si="35">X6+X7+X8</f>
+        <v>188.8</v>
+      </c>
+      <c r="Y9" s="4">
+        <f t="shared" ref="Y9" si="36">Y6+Y7+Y8</f>
+        <v>193.09999999999997</v>
+      </c>
+      <c r="Z9" s="4">
+        <f t="shared" ref="Z9:AA9" si="37">Z6+Z7+Z8</f>
+        <v>156.39999999999998</v>
+      </c>
+      <c r="AA9" s="4">
         <f t="shared" si="37"/>
-        <v>198.70000000000002</v>
-      </c>
-      <c r="X9" s="4">
-        <f t="shared" ref="X9" si="38">X6+X7+X8</f>
-        <v>188.8</v>
-      </c>
-      <c r="Y9" s="4">
-        <f t="shared" ref="Y9" si="39">Y6+Y7+Y8</f>
-        <v>193.09999999999997</v>
-      </c>
-      <c r="Z9" s="4">
-        <f t="shared" ref="Z9:AA9" si="40">Z6+Z7+Z8</f>
-        <v>156.39999999999998</v>
-      </c>
-      <c r="AA9" s="4">
+        <v>203</v>
+      </c>
+      <c r="AB9" s="4">
+        <f t="shared" ref="AB9" si="38">AB6+AB7+AB8</f>
+        <v>182.89999999999998</v>
+      </c>
+      <c r="AC9" s="4">
+        <f t="shared" ref="AC9" si="39">AC6+AC7+AC8</f>
+        <v>179</v>
+      </c>
+      <c r="AD9" s="4">
+        <f t="shared" ref="AD9:AH9" si="40">AD6+AD7+AD8</f>
+        <v>172.4</v>
+      </c>
+      <c r="AE9" s="4">
         <f t="shared" si="40"/>
-        <v>203</v>
-      </c>
-      <c r="AB9" s="4">
-        <f t="shared" ref="AB9" si="41">AB6+AB7+AB8</f>
-        <v>182.89999999999998</v>
-      </c>
-      <c r="AC9" s="4">
-        <f t="shared" ref="AC9" si="42">AC6+AC7+AC8</f>
-        <v>179</v>
-      </c>
-      <c r="AD9" s="4">
-        <f t="shared" ref="AD9:AH9" si="43">AD6+AD7+AD8</f>
-        <v>172.4</v>
-      </c>
-      <c r="AE9" s="4">
-        <f t="shared" si="43"/>
         <v>193.2</v>
       </c>
       <c r="AF9" s="4">
-        <f t="shared" si="43"/>
-        <v>175.7259</v>
+        <f t="shared" si="40"/>
+        <v>174.8</v>
       </c>
       <c r="AG9" s="4">
-        <f t="shared" si="43"/>
-        <v>178.13356999999999</v>
+        <f t="shared" si="40"/>
+        <v>152.70000000000002</v>
       </c>
       <c r="AH9" s="4">
-        <f t="shared" si="43"/>
-        <v>176.95699999999999</v>
+        <f t="shared" si="40"/>
+        <v>176.57859999999999</v>
       </c>
       <c r="AI9" s="4"/>
       <c r="AK9" s="4">
@@ -2352,60 +2396,60 @@
         <v>654.9</v>
       </c>
       <c r="AO9" s="4">
-        <f t="shared" ref="AO9:AW9" si="44">AO6+AO7+AO8</f>
+        <f t="shared" ref="AO9:AW9" si="41">AO6+AO7+AO8</f>
         <v>706.7</v>
       </c>
       <c r="AP9" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="41"/>
         <v>737</v>
       </c>
       <c r="AQ9" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="41"/>
         <v>737.3</v>
       </c>
       <c r="AR9" s="4">
-        <f t="shared" si="44"/>
-        <v>724.01647000000003</v>
+        <f t="shared" si="41"/>
+        <v>697.2786000000001</v>
       </c>
       <c r="AS9" s="4">
-        <f t="shared" si="44"/>
-        <v>735.29243999999994</v>
+        <f t="shared" si="41"/>
+        <v>684.28899200000001</v>
       </c>
       <c r="AT9" s="4">
-        <f t="shared" si="44"/>
-        <v>737.77203273000009</v>
+        <f t="shared" si="41"/>
+        <v>687.30176452000001</v>
       </c>
       <c r="AU9" s="4">
-        <f t="shared" si="44"/>
-        <v>737.05168467720011</v>
+        <f t="shared" si="41"/>
+        <v>683.71856166320003</v>
       </c>
       <c r="AV9" s="4">
-        <f t="shared" si="44"/>
-        <v>732.70235585775617</v>
+        <f t="shared" si="41"/>
+        <v>676.63771346701606</v>
       </c>
       <c r="AW9" s="4">
-        <f t="shared" si="44"/>
-        <v>726.61187060701798</v>
+        <f t="shared" si="41"/>
+        <v>669.03869141631537</v>
       </c>
       <c r="AX9" s="4">
-        <f t="shared" ref="AX9:BB9" si="45">AX6+AX7+AX8</f>
-        <v>733.87798931308805</v>
+        <f t="shared" ref="AX9:BB9" si="42">AX6+AX7+AX8</f>
+        <v>678.48723497406979</v>
       </c>
       <c r="AY9" s="4">
-        <f t="shared" si="45"/>
-        <v>741.21676920621883</v>
+        <f t="shared" si="42"/>
+        <v>688.08542710027359</v>
       </c>
       <c r="AZ9" s="4">
-        <f t="shared" si="45"/>
-        <v>748.62893689828115</v>
+        <f t="shared" si="42"/>
+        <v>697.83586754326848</v>
       </c>
       <c r="BA9" s="4">
-        <f t="shared" si="45"/>
-        <v>756.11522626726401</v>
+        <f t="shared" si="42"/>
+        <v>707.74120411413344</v>
       </c>
       <c r="BB9" s="4">
-        <f t="shared" si="45"/>
-        <v>763.67637852993664</v>
+        <f t="shared" si="42"/>
+        <v>717.80413360861542</v>
       </c>
     </row>
     <row r="10" spans="2:176" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2413,132 +2457,132 @@
         <v>29</v>
       </c>
       <c r="C10" s="7">
-        <f t="shared" ref="C10:M10" si="46">C5-C9</f>
+        <f t="shared" ref="C10:M10" si="43">C5-C9</f>
         <v>46.299999999999983</v>
       </c>
       <c r="D10" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="43"/>
         <v>-33.700000000000017</v>
       </c>
       <c r="E10" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="43"/>
         <v>-21.599999999999994</v>
       </c>
       <c r="F10" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="43"/>
         <v>9.9999999999994316E-2</v>
       </c>
       <c r="G10" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="43"/>
         <v>68.499999999999957</v>
       </c>
       <c r="H10" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="43"/>
         <v>-23.000000000000014</v>
       </c>
       <c r="I10" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="43"/>
         <v>-15.199999999999989</v>
       </c>
       <c r="J10" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="43"/>
         <v>-24.800000000000011</v>
       </c>
       <c r="K10" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="43"/>
         <v>67.500000000000028</v>
       </c>
       <c r="L10" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="43"/>
         <v>-53.199999999999989</v>
       </c>
       <c r="M10" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="43"/>
         <v>-56.999999999999972</v>
       </c>
       <c r="N10" s="7">
-        <f t="shared" ref="N10:O10" si="47">N5-N9</f>
+        <f t="shared" ref="N10:O10" si="44">N5-N9</f>
         <v>15.400000000000006</v>
       </c>
       <c r="O10" s="7">
+        <f t="shared" si="44"/>
+        <v>137.50000000000003</v>
+      </c>
+      <c r="P10" s="7">
+        <f t="shared" ref="P10:Q10" si="45">P5-P9</f>
+        <v>12.300000000000011</v>
+      </c>
+      <c r="Q10" s="7">
+        <f t="shared" si="45"/>
+        <v>16.799999999999955</v>
+      </c>
+      <c r="R10" s="7">
+        <f t="shared" ref="R10" si="46">R5-R9</f>
+        <v>-11.700000000000017</v>
+      </c>
+      <c r="S10" s="7">
+        <f t="shared" ref="S10:T10" si="47">S5-S9</f>
+        <v>132.69999999999999</v>
+      </c>
+      <c r="T10" s="7">
         <f t="shared" si="47"/>
-        <v>137.50000000000003</v>
-      </c>
-      <c r="P10" s="7">
-        <f t="shared" ref="P10:Q10" si="48">P5-P9</f>
-        <v>12.300000000000011</v>
-      </c>
-      <c r="Q10" s="7">
-        <f t="shared" si="48"/>
-        <v>16.799999999999955</v>
-      </c>
-      <c r="R10" s="7">
-        <f t="shared" ref="R10" si="49">R5-R9</f>
-        <v>-11.700000000000017</v>
-      </c>
-      <c r="S10" s="7">
-        <f t="shared" ref="S10:T10" si="50">S5-S9</f>
-        <v>132.69999999999999</v>
-      </c>
-      <c r="T10" s="7">
-        <f t="shared" si="50"/>
         <v>10.100000000000023</v>
       </c>
       <c r="U10" s="7">
-        <f t="shared" ref="U10" si="51">U5-U9</f>
+        <f t="shared" ref="U10" si="48">U5-U9</f>
         <v>7</v>
       </c>
       <c r="V10" s="7">
-        <f t="shared" ref="V10:W10" si="52">V5-V9</f>
+        <f t="shared" ref="V10:W10" si="49">V5-V9</f>
         <v>-59.999999999999943</v>
       </c>
       <c r="W10" s="7">
+        <f t="shared" si="49"/>
+        <v>86.4</v>
+      </c>
+      <c r="X10" s="7">
+        <f t="shared" ref="X10" si="50">X5-X9</f>
+        <v>-57.200000000000017</v>
+      </c>
+      <c r="Y10" s="7">
+        <f t="shared" ref="Y10" si="51">Y5-Y9</f>
+        <v>-21.299999999999983</v>
+      </c>
+      <c r="Z10" s="7">
+        <f t="shared" ref="Z10:AA10" si="52">Z5-Z9</f>
+        <v>-28.399999999999949</v>
+      </c>
+      <c r="AA10" s="7">
         <f t="shared" si="52"/>
-        <v>86.4</v>
-      </c>
-      <c r="X10" s="7">
-        <f t="shared" ref="X10" si="53">X5-X9</f>
-        <v>-57.200000000000017</v>
-      </c>
-      <c r="Y10" s="7">
-        <f t="shared" ref="Y10" si="54">Y5-Y9</f>
-        <v>-21.299999999999983</v>
-      </c>
-      <c r="Z10" s="7">
-        <f t="shared" ref="Z10:AA10" si="55">Z5-Z9</f>
-        <v>-28.399999999999949</v>
-      </c>
-      <c r="AA10" s="7">
+        <v>79.699999999999989</v>
+      </c>
+      <c r="AB10" s="7">
+        <f t="shared" ref="AB10" si="53">AB5-AB9</f>
+        <v>-70.799999999999983</v>
+      </c>
+      <c r="AC10" s="7">
+        <f t="shared" ref="AC10" si="54">AC5-AC9</f>
+        <v>12.600000000000023</v>
+      </c>
+      <c r="AD10" s="7">
+        <f t="shared" ref="AD10:AH10" si="55">AD5-AD9</f>
+        <v>-69.400000000000006</v>
+      </c>
+      <c r="AE10" s="7">
         <f t="shared" si="55"/>
-        <v>79.699999999999989</v>
-      </c>
-      <c r="AB10" s="7">
-        <f t="shared" ref="AB10" si="56">AB5-AB9</f>
-        <v>-70.799999999999983</v>
-      </c>
-      <c r="AC10" s="7">
-        <f t="shared" ref="AC10" si="57">AC5-AC9</f>
-        <v>12.600000000000023</v>
-      </c>
-      <c r="AD10" s="7">
-        <f t="shared" ref="AD10:AH10" si="58">AD5-AD9</f>
-        <v>-69.400000000000006</v>
-      </c>
-      <c r="AE10" s="7">
-        <f t="shared" si="58"/>
         <v>48.199999999999989</v>
       </c>
       <c r="AF10" s="7">
-        <f t="shared" si="58"/>
-        <v>-70.097300000000004</v>
+        <f t="shared" si="55"/>
+        <v>-61.099999999999994</v>
       </c>
       <c r="AG10" s="7">
-        <f t="shared" si="58"/>
-        <v>-8.2541899999999657</v>
+        <f t="shared" si="55"/>
+        <v>-2.9000000000000057</v>
       </c>
       <c r="AH10" s="7">
-        <f t="shared" si="58"/>
-        <v>-79.904999999999987</v>
+        <f t="shared" si="55"/>
+        <v>-71.353799999999978</v>
       </c>
       <c r="AI10" s="7"/>
       <c r="AK10" s="7">
@@ -2554,64 +2598,64 @@
         <v>-27.300000000000182</v>
       </c>
       <c r="AN10" s="7">
-        <f t="shared" ref="AN10:AW10" si="59">AN5-AN9</f>
+        <f t="shared" ref="AN10:AW10" si="56">AN5-AN9</f>
         <v>154.89999999999986</v>
       </c>
       <c r="AO10" s="7">
-        <f t="shared" si="59"/>
+        <f t="shared" si="56"/>
         <v>89.799999999999955</v>
       </c>
       <c r="AP10" s="7">
-        <f t="shared" si="59"/>
+        <f t="shared" si="56"/>
         <v>-20.500000000000341</v>
       </c>
       <c r="AQ10" s="7">
-        <f t="shared" si="59"/>
+        <f t="shared" si="56"/>
         <v>-47.899999999999977</v>
       </c>
       <c r="AR10" s="7">
-        <f t="shared" si="59"/>
-        <v>-110.05648999999994</v>
+        <f t="shared" si="56"/>
+        <v>-87.153800000000274</v>
       </c>
       <c r="AS10" s="7">
-        <f t="shared" si="59"/>
-        <v>-72.423134999999888</v>
+        <f t="shared" si="56"/>
+        <v>5.1321399999999358</v>
       </c>
       <c r="AT10" s="7">
-        <f t="shared" si="59"/>
-        <v>-39.844306709999955</v>
+        <f t="shared" si="56"/>
+        <v>52.676917160000016</v>
       </c>
       <c r="AU10" s="7">
-        <f t="shared" si="59"/>
-        <v>-9.689615429400078</v>
+        <f t="shared" si="56"/>
+        <v>95.028568339599929</v>
       </c>
       <c r="AV10" s="7">
-        <f t="shared" si="59"/>
-        <v>24.992259256547982</v>
+        <f t="shared" si="56"/>
+        <v>134.58482876568792</v>
       </c>
       <c r="AW10" s="7">
-        <f t="shared" si="59"/>
-        <v>46.236636809572246</v>
+        <f t="shared" si="56"/>
+        <v>158.40830166104274</v>
       </c>
       <c r="AX10" s="7">
-        <f t="shared" ref="AX10:BB10" si="60">AX5-AX9</f>
-        <v>46.699003177668033</v>
+        <f t="shared" ref="AX10:BB10" si="57">AX5-AX9</f>
+        <v>165.50869796483539</v>
       </c>
       <c r="AY10" s="7">
-        <f t="shared" si="60"/>
-        <v>47.165993209444878</v>
+        <f t="shared" si="57"/>
+        <v>172.79042449740973</v>
       </c>
       <c r="AZ10" s="7">
-        <f t="shared" si="60"/>
-        <v>47.637653141539204</v>
+        <f t="shared" si="57"/>
+        <v>180.25750108636851</v>
       </c>
       <c r="BA10" s="7">
-        <f t="shared" si="60"/>
-        <v>48.114029672954644</v>
+        <f t="shared" si="57"/>
+        <v>187.91403188809625</v>
       </c>
       <c r="BB10" s="7">
-        <f t="shared" si="60"/>
-        <v>48.595169969684093</v>
+        <f t="shared" si="57"/>
+        <v>195.76420711365893</v>
       </c>
     </row>
     <row r="11" spans="2:176" x14ac:dyDescent="0.3">
@@ -2707,10 +2751,10 @@
         <v>4.2</v>
       </c>
       <c r="AF11" s="4">
-        <v>0</v>
+        <v>-2.1</v>
       </c>
       <c r="AG11" s="4">
-        <v>0</v>
+        <v>-2.1</v>
       </c>
       <c r="AH11" s="4">
         <v>0</v>
@@ -2746,47 +2790,47 @@
       </c>
       <c r="AR11" s="4">
         <f>SUM(AE11:AH11)</f>
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AS11" s="4">
-        <f t="shared" ref="AS11:AW11" si="61">-AR14*0.01</f>
-        <v>0.92030840999999952</v>
+        <f t="shared" ref="AS11:AW11" si="58">-AR14*0.01</f>
+        <v>0.87218420000000285</v>
       </c>
       <c r="AT11" s="4">
-        <f t="shared" si="61"/>
-        <v>0.58674754727999912</v>
+        <f t="shared" si="58"/>
+        <v>-3.4079646399999462E-2</v>
       </c>
       <c r="AU11" s="4">
-        <f t="shared" si="61"/>
-        <v>0.32344843405823964</v>
+        <f t="shared" si="58"/>
+        <v>-0.42168797445120015</v>
       </c>
       <c r="AV11" s="4">
-        <f t="shared" si="61"/>
-        <v>8.0104510907666543E-2</v>
+        <f t="shared" si="58"/>
+        <v>-0.76360205051240915</v>
       </c>
       <c r="AW11" s="4">
-        <f t="shared" si="61"/>
-        <v>-0.19929723796512253</v>
+        <f t="shared" si="58"/>
+        <v>-1.0827874465296028</v>
       </c>
       <c r="AX11" s="4">
-        <f t="shared" ref="AX11" si="62">-AW14*0.01</f>
-        <v>-0.37148747238029894</v>
+        <f t="shared" ref="AX11" si="59">-AW14*0.01</f>
+        <v>-1.275928712860579</v>
       </c>
       <c r="AY11" s="4">
-        <f t="shared" ref="AY11" si="63">-AX14*0.01</f>
-        <v>-0.37656392520038667</v>
+        <f t="shared" ref="AY11" si="60">-AX14*0.01</f>
+        <v>-1.3342770134215678</v>
       </c>
       <c r="AZ11" s="4">
-        <f t="shared" ref="AZ11" si="64">-AY14*0.01</f>
-        <v>-0.38034045707716213</v>
+        <f t="shared" ref="AZ11" si="61">-AY14*0.01</f>
+        <v>-1.3929976120866505</v>
       </c>
       <c r="BA11" s="4">
-        <f t="shared" ref="BA11" si="65">-AZ14*0.01</f>
-        <v>-0.38414394878893093</v>
+        <f t="shared" ref="BA11" si="62">-AZ14*0.01</f>
+        <v>-1.4532039895876412</v>
       </c>
       <c r="BB11" s="4">
-        <f t="shared" ref="BB11" si="66">-BA14*0.01</f>
-        <v>-0.38798538897394863</v>
+        <f t="shared" ref="BB11" si="63">-BA14*0.01</f>
+        <v>-1.5149378870214714</v>
       </c>
     </row>
     <row r="12" spans="2:176" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2794,132 +2838,132 @@
         <v>31</v>
       </c>
       <c r="C12" s="7">
-        <f t="shared" ref="C12:O12" si="67">C10-C11</f>
+        <f t="shared" ref="C12:O12" si="64">C10-C11</f>
         <v>45.799999999999983</v>
       </c>
       <c r="D12" s="7">
+        <f t="shared" si="64"/>
+        <v>-32.000000000000014</v>
+      </c>
+      <c r="E12" s="7">
+        <f t="shared" si="64"/>
+        <v>-26.499999999999993</v>
+      </c>
+      <c r="F12" s="7">
+        <f t="shared" si="64"/>
+        <v>-1.9000000000000057</v>
+      </c>
+      <c r="G12" s="7">
+        <f t="shared" si="64"/>
+        <v>64.099999999999952</v>
+      </c>
+      <c r="H12" s="7">
+        <f t="shared" si="64"/>
+        <v>-23.100000000000016</v>
+      </c>
+      <c r="I12" s="7">
+        <f t="shared" si="64"/>
+        <v>-13.299999999999988</v>
+      </c>
+      <c r="J12" s="7">
+        <f t="shared" si="64"/>
+        <v>-29.000000000000011</v>
+      </c>
+      <c r="K12" s="7">
+        <f t="shared" si="64"/>
+        <v>72.500000000000028</v>
+      </c>
+      <c r="L12" s="7">
+        <f t="shared" si="64"/>
+        <v>-54.099999999999987</v>
+      </c>
+      <c r="M12" s="7">
+        <f t="shared" si="64"/>
+        <v>-56.89999999999997</v>
+      </c>
+      <c r="N12" s="7">
+        <f t="shared" si="64"/>
+        <v>18.400000000000006</v>
+      </c>
+      <c r="O12" s="7">
+        <f t="shared" si="64"/>
+        <v>141.50000000000003</v>
+      </c>
+      <c r="P12" s="7">
+        <f t="shared" ref="P12:Q12" si="65">P10-P11</f>
+        <v>10.700000000000012</v>
+      </c>
+      <c r="Q12" s="7">
+        <f t="shared" si="65"/>
+        <v>18.799999999999955</v>
+      </c>
+      <c r="R12" s="7">
+        <f t="shared" ref="R12" si="66">R10-R11</f>
+        <v>-14.000000000000018</v>
+      </c>
+      <c r="S12" s="7">
+        <f t="shared" ref="S12:T12" si="67">S10-S11</f>
+        <v>131.19999999999999</v>
+      </c>
+      <c r="T12" s="7">
         <f t="shared" si="67"/>
-        <v>-32.000000000000014</v>
-      </c>
-      <c r="E12" s="7">
-        <f t="shared" si="67"/>
-        <v>-26.499999999999993</v>
-      </c>
-      <c r="F12" s="7">
-        <f t="shared" si="67"/>
-        <v>-1.9000000000000057</v>
-      </c>
-      <c r="G12" s="7">
-        <f t="shared" si="67"/>
-        <v>64.099999999999952</v>
-      </c>
-      <c r="H12" s="7">
-        <f t="shared" si="67"/>
-        <v>-23.100000000000016</v>
-      </c>
-      <c r="I12" s="7">
-        <f t="shared" si="67"/>
-        <v>-13.299999999999988</v>
-      </c>
-      <c r="J12" s="7">
-        <f t="shared" si="67"/>
-        <v>-29.000000000000011</v>
-      </c>
-      <c r="K12" s="7">
-        <f t="shared" si="67"/>
-        <v>72.500000000000028</v>
-      </c>
-      <c r="L12" s="7">
-        <f t="shared" si="67"/>
-        <v>-54.099999999999987</v>
-      </c>
-      <c r="M12" s="7">
-        <f t="shared" si="67"/>
-        <v>-56.89999999999997</v>
-      </c>
-      <c r="N12" s="7">
-        <f t="shared" si="67"/>
-        <v>18.400000000000006</v>
-      </c>
-      <c r="O12" s="7">
-        <f t="shared" si="67"/>
-        <v>141.50000000000003</v>
-      </c>
-      <c r="P12" s="7">
-        <f t="shared" ref="P12:Q12" si="68">P10-P11</f>
-        <v>10.700000000000012</v>
-      </c>
-      <c r="Q12" s="7">
-        <f t="shared" si="68"/>
-        <v>18.799999999999955</v>
-      </c>
-      <c r="R12" s="7">
-        <f t="shared" ref="R12" si="69">R10-R11</f>
-        <v>-14.000000000000018</v>
-      </c>
-      <c r="S12" s="7">
-        <f t="shared" ref="S12:T12" si="70">S10-S11</f>
-        <v>131.19999999999999</v>
-      </c>
-      <c r="T12" s="7">
-        <f t="shared" si="70"/>
         <v>7.9000000000000226</v>
       </c>
       <c r="U12" s="7">
-        <f t="shared" ref="U12" si="71">U10-U11</f>
+        <f t="shared" ref="U12" si="68">U10-U11</f>
         <v>-2.5999999999999996</v>
       </c>
       <c r="V12" s="7">
-        <f t="shared" ref="V12:W12" si="72">V10-V11</f>
+        <f t="shared" ref="V12:W12" si="69">V10-V11</f>
         <v>-67.499999999999943</v>
       </c>
       <c r="W12" s="7">
+        <f t="shared" si="69"/>
+        <v>111.80000000000001</v>
+      </c>
+      <c r="X12" s="7">
+        <f t="shared" ref="X12" si="70">X10-X11</f>
+        <v>-57.000000000000014</v>
+      </c>
+      <c r="Y12" s="7">
+        <f t="shared" ref="Y12" si="71">Y10-Y11</f>
+        <v>-17.799999999999983</v>
+      </c>
+      <c r="Z12" s="7">
+        <f t="shared" ref="Z12:AA12" si="72">Z10-Z11</f>
+        <v>-32.599999999999952</v>
+      </c>
+      <c r="AA12" s="7">
         <f t="shared" si="72"/>
-        <v>111.80000000000001</v>
-      </c>
-      <c r="X12" s="7">
-        <f t="shared" ref="X12" si="73">X10-X11</f>
-        <v>-57.000000000000014</v>
-      </c>
-      <c r="Y12" s="7">
-        <f t="shared" ref="Y12" si="74">Y10-Y11</f>
-        <v>-17.799999999999983</v>
-      </c>
-      <c r="Z12" s="7">
-        <f t="shared" ref="Z12:AA12" si="75">Z10-Z11</f>
-        <v>-32.599999999999952</v>
-      </c>
-      <c r="AA12" s="7">
+        <v>92.899999999999991</v>
+      </c>
+      <c r="AB12" s="7">
+        <f t="shared" ref="AB12" si="73">AB10-AB11</f>
+        <v>-70.299999999999983</v>
+      </c>
+      <c r="AC12" s="7">
+        <f t="shared" ref="AC12" si="74">AC10-AC11</f>
+        <v>12.600000000000023</v>
+      </c>
+      <c r="AD12" s="7">
+        <f t="shared" ref="AD12:AH12" si="75">AD10-AD11</f>
+        <v>-62.300000000000004</v>
+      </c>
+      <c r="AE12" s="7">
         <f t="shared" si="75"/>
-        <v>92.899999999999991</v>
-      </c>
-      <c r="AB12" s="7">
-        <f t="shared" ref="AB12" si="76">AB10-AB11</f>
-        <v>-70.299999999999983</v>
-      </c>
-      <c r="AC12" s="7">
-        <f t="shared" ref="AC12" si="77">AC10-AC11</f>
-        <v>12.600000000000023</v>
-      </c>
-      <c r="AD12" s="7">
-        <f t="shared" ref="AD12:AH12" si="78">AD10-AD11</f>
-        <v>-62.300000000000004</v>
-      </c>
-      <c r="AE12" s="7">
-        <f t="shared" si="78"/>
         <v>43.999999999999986</v>
       </c>
       <c r="AF12" s="7">
-        <f t="shared" si="78"/>
-        <v>-70.097300000000004</v>
+        <f t="shared" si="75"/>
+        <v>-58.999999999999993</v>
       </c>
       <c r="AG12" s="7">
-        <f t="shared" si="78"/>
-        <v>-8.2541899999999657</v>
+        <f t="shared" si="75"/>
+        <v>-0.8000000000000056</v>
       </c>
       <c r="AH12" s="7">
-        <f t="shared" si="78"/>
-        <v>-79.904999999999987</v>
+        <f t="shared" si="75"/>
+        <v>-71.353799999999978</v>
       </c>
       <c r="AI12" s="7"/>
       <c r="AK12" s="7">
@@ -2935,64 +2979,64 @@
         <v>-20.100000000000183</v>
       </c>
       <c r="AN12" s="7">
-        <f t="shared" ref="AN12:AW12" si="79">AN10-AN11</f>
+        <f t="shared" ref="AN12:AW12" si="76">AN10-AN11</f>
         <v>156.99999999999986</v>
       </c>
       <c r="AO12" s="7">
-        <f t="shared" si="79"/>
+        <f t="shared" si="76"/>
         <v>68.999999999999957</v>
       </c>
       <c r="AP12" s="7">
-        <f t="shared" si="79"/>
+        <f t="shared" si="76"/>
         <v>4.3999999999996575</v>
       </c>
       <c r="AQ12" s="7">
-        <f t="shared" si="79"/>
+        <f t="shared" si="76"/>
         <v>-27.09999999999998</v>
       </c>
       <c r="AR12" s="7">
-        <f t="shared" si="79"/>
-        <v>-114.25648999999994</v>
+        <f t="shared" si="76"/>
+        <v>-87.153800000000274</v>
       </c>
       <c r="AS12" s="7">
-        <f t="shared" si="79"/>
-        <v>-73.343443409999892</v>
+        <f t="shared" si="76"/>
+        <v>4.2599557999999327</v>
       </c>
       <c r="AT12" s="7">
-        <f t="shared" si="79"/>
-        <v>-40.431054257279953</v>
+        <f t="shared" si="76"/>
+        <v>52.710996806400018</v>
       </c>
       <c r="AU12" s="7">
-        <f t="shared" si="79"/>
-        <v>-10.013063863458317</v>
+        <f t="shared" si="76"/>
+        <v>95.450256314051131</v>
       </c>
       <c r="AV12" s="7">
-        <f t="shared" si="79"/>
-        <v>24.912154745640315</v>
+        <f t="shared" si="76"/>
+        <v>135.34843081620033</v>
       </c>
       <c r="AW12" s="7">
-        <f t="shared" si="79"/>
-        <v>46.435934047537366</v>
+        <f t="shared" si="76"/>
+        <v>159.49108910757235</v>
       </c>
       <c r="AX12" s="7">
-        <f t="shared" ref="AX12:BB12" si="80">AX10-AX11</f>
-        <v>47.070490650048335</v>
+        <f t="shared" ref="AX12:BB12" si="77">AX10-AX11</f>
+        <v>166.78462667769597</v>
       </c>
       <c r="AY12" s="7">
-        <f t="shared" si="80"/>
-        <v>47.542557134645264</v>
+        <f t="shared" si="77"/>
+        <v>174.1247015108313</v>
       </c>
       <c r="AZ12" s="7">
-        <f t="shared" si="80"/>
-        <v>48.017993598616364</v>
+        <f t="shared" si="77"/>
+        <v>181.65049869845515</v>
       </c>
       <c r="BA12" s="7">
-        <f t="shared" si="80"/>
-        <v>48.498173621743575</v>
+        <f t="shared" si="77"/>
+        <v>189.3672358776839</v>
       </c>
       <c r="BB12" s="7">
-        <f t="shared" si="80"/>
-        <v>48.983155358658038</v>
+        <f t="shared" si="77"/>
+        <v>197.27914500068039</v>
       </c>
     </row>
     <row r="13" spans="2:176" x14ac:dyDescent="0.3">
@@ -3087,16 +3131,14 @@
         <v>-6.4</v>
       </c>
       <c r="AF13" s="4">
-        <f t="shared" ref="AF13:AH13" si="81">AF12*0.1</f>
-        <v>-7.0097300000000011</v>
+        <v>11</v>
       </c>
       <c r="AG13" s="4">
-        <f t="shared" si="81"/>
-        <v>-0.82541899999999657</v>
+        <v>2.6</v>
       </c>
       <c r="AH13" s="4">
-        <f t="shared" si="81"/>
-        <v>-7.990499999999999</v>
+        <f t="shared" ref="AH13" si="78">AH12*0.1</f>
+        <v>-7.1353799999999978</v>
       </c>
       <c r="AI13" s="4"/>
       <c r="AK13" s="4">
@@ -3129,47 +3171,47 @@
       </c>
       <c r="AR13" s="4">
         <f>SUM(AE13:AH13)</f>
-        <v>-22.225648999999997</v>
+        <v>6.4620000000001454E-2</v>
       </c>
       <c r="AS13" s="4">
         <f>AS12*0.2</f>
-        <v>-14.66868868199998</v>
+        <v>0.85199115999998654</v>
       </c>
       <c r="AT13" s="4">
-        <f t="shared" ref="AT13:AW13" si="82">AT12*0.2</f>
-        <v>-8.0862108514559914</v>
+        <f t="shared" ref="AT13:AW13" si="79">AT12*0.2</f>
+        <v>10.542199361280005</v>
       </c>
       <c r="AU13" s="4">
-        <f t="shared" si="82"/>
-        <v>-2.0026127726916636</v>
+        <f t="shared" si="79"/>
+        <v>19.090051262810228</v>
       </c>
       <c r="AV13" s="4">
-        <f t="shared" si="82"/>
-        <v>4.9824309491280632</v>
+        <f t="shared" si="79"/>
+        <v>27.069686163240068</v>
       </c>
       <c r="AW13" s="4">
-        <f t="shared" si="82"/>
-        <v>9.2871868095074728</v>
+        <f t="shared" si="79"/>
+        <v>31.898217821514471</v>
       </c>
       <c r="AX13" s="4">
-        <f t="shared" ref="AX13:BB13" si="83">AX12*0.2</f>
-        <v>9.414098130009668</v>
+        <f t="shared" ref="AX13:BB13" si="80">AX12*0.2</f>
+        <v>33.356925335539195</v>
       </c>
       <c r="AY13" s="4">
-        <f t="shared" si="83"/>
-        <v>9.5085114269290525</v>
+        <f t="shared" si="80"/>
+        <v>34.824940302166262</v>
       </c>
       <c r="AZ13" s="4">
-        <f t="shared" si="83"/>
-        <v>9.6035987197232728</v>
+        <f t="shared" si="80"/>
+        <v>36.330099739691029</v>
       </c>
       <c r="BA13" s="4">
-        <f t="shared" si="83"/>
-        <v>9.6996347243487158</v>
+        <f t="shared" si="80"/>
+        <v>37.873447175536782</v>
       </c>
       <c r="BB13" s="4">
-        <f t="shared" si="83"/>
-        <v>9.7966310717316087</v>
+        <f t="shared" si="80"/>
+        <v>39.455829000136077</v>
       </c>
     </row>
     <row r="14" spans="2:176" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3177,132 +3219,132 @@
         <v>33</v>
       </c>
       <c r="C14" s="7">
-        <f t="shared" ref="C14:M14" si="84">C12-C13</f>
+        <f t="shared" ref="C14:M14" si="81">C12-C13</f>
         <v>45.799999999999983</v>
       </c>
       <c r="D14" s="7">
-        <f t="shared" si="84"/>
+        <f t="shared" si="81"/>
         <v>-32.600000000000016</v>
       </c>
       <c r="E14" s="7">
-        <f t="shared" si="84"/>
+        <f t="shared" si="81"/>
         <v>-26.999999999999993</v>
       </c>
       <c r="F14" s="7">
-        <f t="shared" si="84"/>
+        <f t="shared" si="81"/>
         <v>-1.8000000000000056</v>
       </c>
       <c r="G14" s="7">
-        <f t="shared" si="84"/>
+        <f t="shared" si="81"/>
         <v>61.599999999999952</v>
       </c>
       <c r="H14" s="7">
-        <f t="shared" si="84"/>
+        <f t="shared" si="81"/>
         <v>-22.900000000000016</v>
       </c>
       <c r="I14" s="7">
-        <f t="shared" si="84"/>
+        <f t="shared" si="81"/>
         <v>-14.099999999999989</v>
       </c>
       <c r="J14" s="7">
-        <f t="shared" si="84"/>
+        <f t="shared" si="81"/>
         <v>-29.600000000000012</v>
       </c>
       <c r="K14" s="7">
-        <f t="shared" si="84"/>
+        <f t="shared" si="81"/>
         <v>70.800000000000026</v>
       </c>
       <c r="L14" s="7">
-        <f t="shared" si="84"/>
+        <f t="shared" si="81"/>
         <v>-52.29999999999999</v>
       </c>
       <c r="M14" s="7">
-        <f t="shared" si="84"/>
+        <f t="shared" si="81"/>
         <v>-57.099999999999973</v>
       </c>
       <c r="N14" s="7">
-        <f t="shared" ref="N14:O14" si="85">N12-N13</f>
+        <f t="shared" ref="N14:O14" si="82">N12-N13</f>
         <v>18.400000000000006</v>
       </c>
       <c r="O14" s="7">
+        <f t="shared" si="82"/>
+        <v>132.40000000000003</v>
+      </c>
+      <c r="P14" s="7">
+        <f t="shared" ref="P14:Q14" si="83">P12-P13</f>
+        <v>17.20000000000001</v>
+      </c>
+      <c r="Q14" s="7">
+        <f t="shared" si="83"/>
+        <v>17.899999999999956</v>
+      </c>
+      <c r="R14" s="7">
+        <f t="shared" ref="R14" si="84">R12-R13</f>
+        <v>-8.9000000000000181</v>
+      </c>
+      <c r="S14" s="7">
+        <f t="shared" ref="S14:T14" si="85">S12-S13</f>
+        <v>123.6</v>
+      </c>
+      <c r="T14" s="7">
         <f t="shared" si="85"/>
-        <v>132.40000000000003</v>
-      </c>
-      <c r="P14" s="7">
-        <f t="shared" ref="P14:Q14" si="86">P12-P13</f>
-        <v>17.20000000000001</v>
-      </c>
-      <c r="Q14" s="7">
-        <f t="shared" si="86"/>
-        <v>17.899999999999956</v>
-      </c>
-      <c r="R14" s="7">
-        <f t="shared" ref="R14" si="87">R12-R13</f>
-        <v>-8.9000000000000181</v>
-      </c>
-      <c r="S14" s="7">
-        <f t="shared" ref="S14:T14" si="88">S12-S13</f>
-        <v>123.6</v>
-      </c>
-      <c r="T14" s="7">
-        <f t="shared" si="88"/>
         <v>8.7000000000000224</v>
       </c>
       <c r="U14" s="7">
-        <f t="shared" ref="U14" si="89">U12-U13</f>
+        <f t="shared" ref="U14" si="86">U12-U13</f>
         <v>-0.49999999999999956</v>
       </c>
       <c r="V14" s="7">
-        <f t="shared" ref="V14:W14" si="90">V12-V13</f>
+        <f t="shared" ref="V14:W14" si="87">V12-V13</f>
         <v>-63.999999999999943</v>
       </c>
       <c r="W14" s="7">
+        <f t="shared" si="87"/>
+        <v>75.300000000000011</v>
+      </c>
+      <c r="X14" s="7">
+        <f t="shared" ref="X14" si="88">X12-X13</f>
+        <v>-30.600000000000016</v>
+      </c>
+      <c r="Y14" s="7">
+        <f t="shared" ref="Y14" si="89">Y12-Y13</f>
+        <v>-23.699999999999982</v>
+      </c>
+      <c r="Z14" s="7">
+        <f t="shared" ref="Z14:AA14" si="90">Z12-Z13</f>
+        <v>-31.299999999999951</v>
+      </c>
+      <c r="AA14" s="7">
         <f t="shared" si="90"/>
-        <v>75.300000000000011</v>
-      </c>
-      <c r="X14" s="7">
-        <f t="shared" ref="X14" si="91">X12-X13</f>
-        <v>-30.600000000000016</v>
-      </c>
-      <c r="Y14" s="7">
-        <f t="shared" ref="Y14" si="92">Y12-Y13</f>
-        <v>-23.699999999999982</v>
-      </c>
-      <c r="Z14" s="7">
-        <f t="shared" ref="Z14:AA14" si="93">Z12-Z13</f>
-        <v>-31.299999999999951</v>
-      </c>
-      <c r="AA14" s="7">
+        <v>80.899999999999991</v>
+      </c>
+      <c r="AB14" s="7">
+        <f t="shared" ref="AB14" si="91">AB12-AB13</f>
+        <v>-69.59999999999998</v>
+      </c>
+      <c r="AC14" s="7">
+        <f t="shared" ref="AC14" si="92">AC12-AC13</f>
+        <v>3.7000000000000224</v>
+      </c>
+      <c r="AD14" s="7">
+        <f t="shared" ref="AD14:AH14" si="93">AD12-AD13</f>
+        <v>-53.100000000000009</v>
+      </c>
+      <c r="AE14" s="7">
         <f t="shared" si="93"/>
-        <v>80.899999999999991</v>
-      </c>
-      <c r="AB14" s="7">
-        <f t="shared" ref="AB14" si="94">AB12-AB13</f>
-        <v>-69.59999999999998</v>
-      </c>
-      <c r="AC14" s="7">
-        <f t="shared" ref="AC14" si="95">AC12-AC13</f>
-        <v>3.7000000000000224</v>
-      </c>
-      <c r="AD14" s="7">
-        <f t="shared" ref="AD14:AH14" si="96">AD12-AD13</f>
-        <v>-53.100000000000009</v>
-      </c>
-      <c r="AE14" s="7">
-        <f t="shared" si="96"/>
         <v>50.399999999999984</v>
       </c>
       <c r="AF14" s="7">
-        <f t="shared" si="96"/>
-        <v>-63.087569999999999</v>
+        <f t="shared" si="93"/>
+        <v>-70</v>
       </c>
       <c r="AG14" s="7">
-        <f t="shared" si="96"/>
-        <v>-7.4287709999999691</v>
+        <f t="shared" si="93"/>
+        <v>-3.4000000000000057</v>
       </c>
       <c r="AH14" s="7">
-        <f t="shared" si="96"/>
-        <v>-71.91449999999999</v>
+        <f t="shared" si="93"/>
+        <v>-64.218419999999981</v>
       </c>
       <c r="AI14" s="7"/>
       <c r="AJ14" s="7"/>
@@ -3319,552 +3361,552 @@
         <v>-20.200000000000184</v>
       </c>
       <c r="AN14" s="7">
-        <f t="shared" ref="AN14:AW14" si="97">AN12-AN13</f>
+        <f t="shared" ref="AN14:AW14" si="94">AN12-AN13</f>
         <v>158.59999999999985</v>
       </c>
       <c r="AO14" s="7">
-        <f t="shared" si="97"/>
+        <f t="shared" si="94"/>
         <v>67.799999999999955</v>
       </c>
       <c r="AP14" s="7">
-        <f t="shared" si="97"/>
+        <f t="shared" si="94"/>
         <v>-10.300000000000342</v>
       </c>
       <c r="AQ14" s="7">
-        <f t="shared" si="97"/>
+        <f t="shared" si="94"/>
         <v>-38.09999999999998</v>
       </c>
       <c r="AR14" s="7">
-        <f t="shared" si="97"/>
-        <v>-92.030840999999953</v>
+        <f t="shared" si="94"/>
+        <v>-87.218420000000279</v>
       </c>
       <c r="AS14" s="7">
-        <f t="shared" si="97"/>
-        <v>-58.674754727999911</v>
+        <f t="shared" si="94"/>
+        <v>3.4079646399999461</v>
       </c>
       <c r="AT14" s="7">
-        <f t="shared" si="97"/>
-        <v>-32.344843405823966</v>
+        <f t="shared" si="94"/>
+        <v>42.168797445120013</v>
       </c>
       <c r="AU14" s="7">
-        <f t="shared" si="97"/>
-        <v>-8.0104510907666544</v>
+        <f t="shared" si="94"/>
+        <v>76.360205051240911</v>
       </c>
       <c r="AV14" s="7">
-        <f t="shared" si="97"/>
-        <v>19.929723796512253</v>
+        <f t="shared" si="94"/>
+        <v>108.27874465296027</v>
       </c>
       <c r="AW14" s="7">
-        <f t="shared" si="97"/>
-        <v>37.148747238029891</v>
+        <f t="shared" si="94"/>
+        <v>127.59287128605789</v>
       </c>
       <c r="AX14" s="7">
-        <f t="shared" ref="AX14:BB14" si="98">AX12-AX13</f>
-        <v>37.656392520038665</v>
+        <f t="shared" ref="AX14:BB14" si="95">AX12-AX13</f>
+        <v>133.42770134215678</v>
       </c>
       <c r="AY14" s="7">
-        <f t="shared" si="98"/>
-        <v>38.03404570771621</v>
+        <f t="shared" si="95"/>
+        <v>139.29976120866505</v>
       </c>
       <c r="AZ14" s="7">
-        <f t="shared" si="98"/>
-        <v>38.414394878893091</v>
+        <f t="shared" si="95"/>
+        <v>145.32039895876412</v>
       </c>
       <c r="BA14" s="7">
-        <f t="shared" si="98"/>
-        <v>38.798538897394863</v>
+        <f t="shared" si="95"/>
+        <v>151.49378870214713</v>
       </c>
       <c r="BB14" s="7">
-        <f t="shared" si="98"/>
-        <v>39.186524286926428</v>
+        <f t="shared" si="95"/>
+        <v>157.82331600054431</v>
       </c>
       <c r="BC14" s="1">
         <f>BB14*(1+$BE$20)</f>
-        <v>38.794659044057163</v>
+        <v>156.24508284053886</v>
       </c>
       <c r="BD14" s="1">
-        <f t="shared" ref="BD14:DO14" si="99">BC14*(1+$BE$20)</f>
-        <v>38.406712453616592</v>
+        <f t="shared" ref="BD14:DO14" si="96">BC14*(1+$BE$20)</f>
+        <v>154.68263201213347</v>
       </c>
       <c r="BE14" s="1">
-        <f t="shared" si="99"/>
-        <v>38.022645329080426</v>
+        <f t="shared" si="96"/>
+        <v>153.13580569201213</v>
       </c>
       <c r="BF14" s="1">
-        <f t="shared" si="99"/>
-        <v>37.642418875789623</v>
+        <f t="shared" si="96"/>
+        <v>151.60444763509201</v>
       </c>
       <c r="BG14" s="1">
-        <f t="shared" si="99"/>
-        <v>37.265994687031728</v>
+        <f t="shared" si="96"/>
+        <v>150.0884031587411</v>
       </c>
       <c r="BH14" s="1">
-        <f t="shared" si="99"/>
-        <v>36.893334740161414</v>
+        <f t="shared" si="96"/>
+        <v>148.58751912715368</v>
       </c>
       <c r="BI14" s="1">
-        <f t="shared" si="99"/>
-        <v>36.524401392759799</v>
+        <f t="shared" si="96"/>
+        <v>147.10164393588215</v>
       </c>
       <c r="BJ14" s="1">
-        <f t="shared" si="99"/>
-        <v>36.159157378832198</v>
+        <f t="shared" si="96"/>
+        <v>145.63062749652332</v>
       </c>
       <c r="BK14" s="1">
-        <f t="shared" si="99"/>
-        <v>35.797565805043874</v>
+        <f t="shared" si="96"/>
+        <v>144.17432122155807</v>
       </c>
       <c r="BL14" s="1">
-        <f t="shared" si="99"/>
-        <v>35.439590146993432</v>
+        <f t="shared" si="96"/>
+        <v>142.73257800934249</v>
       </c>
       <c r="BM14" s="1">
-        <f t="shared" si="99"/>
-        <v>35.085194245523496</v>
+        <f t="shared" si="96"/>
+        <v>141.30525222924905</v>
       </c>
       <c r="BN14" s="1">
-        <f t="shared" si="99"/>
-        <v>34.73434230306826</v>
+        <f t="shared" si="96"/>
+        <v>139.89219970695655</v>
       </c>
       <c r="BO14" s="1">
-        <f t="shared" si="99"/>
-        <v>34.386998880037574</v>
+        <f t="shared" si="96"/>
+        <v>138.49327770988697</v>
       </c>
       <c r="BP14" s="1">
-        <f t="shared" si="99"/>
-        <v>34.043128891237195</v>
+        <f t="shared" si="96"/>
+        <v>137.1083449327881</v>
       </c>
       <c r="BQ14" s="1">
-        <f t="shared" si="99"/>
-        <v>33.702697602324825</v>
+        <f t="shared" si="96"/>
+        <v>135.73726148346023</v>
       </c>
       <c r="BR14" s="1">
-        <f t="shared" si="99"/>
-        <v>33.365670626301579</v>
+        <f t="shared" si="96"/>
+        <v>134.37988886862561</v>
       </c>
       <c r="BS14" s="1">
-        <f t="shared" si="99"/>
-        <v>33.032013920038565</v>
+        <f t="shared" si="96"/>
+        <v>133.03608997993936</v>
       </c>
       <c r="BT14" s="1">
-        <f t="shared" si="99"/>
-        <v>32.701693780838177</v>
+        <f t="shared" si="96"/>
+        <v>131.70572908013997</v>
       </c>
       <c r="BU14" s="1">
-        <f t="shared" si="99"/>
-        <v>32.374676843029796</v>
+        <f t="shared" si="96"/>
+        <v>130.38867178933856</v>
       </c>
       <c r="BV14" s="1">
-        <f t="shared" si="99"/>
-        <v>32.050930074599499</v>
+        <f t="shared" si="96"/>
+        <v>129.08478507144517</v>
       </c>
       <c r="BW14" s="1">
-        <f t="shared" si="99"/>
-        <v>31.730420773853503</v>
+        <f t="shared" si="96"/>
+        <v>127.79393722073071</v>
       </c>
       <c r="BX14" s="1">
-        <f t="shared" si="99"/>
-        <v>31.413116566114969</v>
+        <f t="shared" si="96"/>
+        <v>126.5159978485234</v>
       </c>
       <c r="BY14" s="1">
-        <f t="shared" si="99"/>
-        <v>31.09898540045382</v>
+        <f t="shared" si="96"/>
+        <v>125.25083787003817</v>
       </c>
       <c r="BZ14" s="1">
-        <f t="shared" si="99"/>
-        <v>30.787995546449281</v>
+        <f t="shared" si="96"/>
+        <v>123.99832949133778</v>
       </c>
       <c r="CA14" s="1">
-        <f t="shared" si="99"/>
-        <v>30.480115590984788</v>
+        <f t="shared" si="96"/>
+        <v>122.75834619642441</v>
       </c>
       <c r="CB14" s="1">
-        <f t="shared" si="99"/>
-        <v>30.175314435074938</v>
+        <f t="shared" si="96"/>
+        <v>121.53076273446017</v>
       </c>
       <c r="CC14" s="1">
-        <f t="shared" si="99"/>
-        <v>29.87356129072419</v>
+        <f t="shared" si="96"/>
+        <v>120.31545510711557</v>
       </c>
       <c r="CD14" s="1">
-        <f t="shared" si="99"/>
-        <v>29.574825677816946</v>
+        <f t="shared" si="96"/>
+        <v>119.11230055604442</v>
       </c>
       <c r="CE14" s="1">
-        <f t="shared" si="99"/>
-        <v>29.279077421038778</v>
+        <f t="shared" si="96"/>
+        <v>117.92117755048397</v>
       </c>
       <c r="CF14" s="1">
-        <f t="shared" si="99"/>
-        <v>28.98628664682839</v>
+        <f t="shared" si="96"/>
+        <v>116.74196577497914</v>
       </c>
       <c r="CG14" s="1">
-        <f t="shared" si="99"/>
-        <v>28.696423780360107</v>
+        <f t="shared" si="96"/>
+        <v>115.57454611722935</v>
       </c>
       <c r="CH14" s="1">
-        <f t="shared" si="99"/>
-        <v>28.409459542556505</v>
+        <f t="shared" si="96"/>
+        <v>114.41880065605706</v>
       </c>
       <c r="CI14" s="1">
-        <f t="shared" si="99"/>
-        <v>28.12536494713094</v>
+        <f t="shared" si="96"/>
+        <v>113.27461264949649</v>
       </c>
       <c r="CJ14" s="1">
-        <f t="shared" si="99"/>
-        <v>27.84411129765963</v>
+        <f t="shared" si="96"/>
+        <v>112.14186652300153</v>
       </c>
       <c r="CK14" s="1">
-        <f t="shared" si="99"/>
-        <v>27.565670184683032</v>
+        <f t="shared" si="96"/>
+        <v>111.02044785777152</v>
       </c>
       <c r="CL14" s="1">
-        <f t="shared" si="99"/>
-        <v>27.290013482836201</v>
+        <f t="shared" si="96"/>
+        <v>109.9102433791938</v>
       </c>
       <c r="CM14" s="1">
-        <f t="shared" si="99"/>
-        <v>27.01711334800784</v>
+        <f t="shared" si="96"/>
+        <v>108.81114094540186</v>
       </c>
       <c r="CN14" s="1">
-        <f t="shared" si="99"/>
-        <v>26.74694221452776</v>
+        <f t="shared" si="96"/>
+        <v>107.72302953594784</v>
       </c>
       <c r="CO14" s="1">
-        <f t="shared" si="99"/>
-        <v>26.479472792382481</v>
+        <f t="shared" si="96"/>
+        <v>106.64579924058836</v>
       </c>
       <c r="CP14" s="1">
-        <f t="shared" si="99"/>
-        <v>26.214678064458656</v>
+        <f t="shared" si="96"/>
+        <v>105.57934124818247</v>
       </c>
       <c r="CQ14" s="1">
-        <f t="shared" si="99"/>
-        <v>25.952531283814068</v>
+        <f t="shared" si="96"/>
+        <v>104.52354783570065</v>
       </c>
       <c r="CR14" s="1">
-        <f t="shared" si="99"/>
-        <v>25.693005970975928</v>
+        <f t="shared" si="96"/>
+        <v>103.47831235734364</v>
       </c>
       <c r="CS14" s="1">
-        <f t="shared" si="99"/>
-        <v>25.436075911266169</v>
+        <f t="shared" si="96"/>
+        <v>102.44352923377021</v>
       </c>
       <c r="CT14" s="1">
-        <f t="shared" si="99"/>
-        <v>25.181715152153508</v>
+        <f t="shared" si="96"/>
+        <v>101.41909394143251</v>
       </c>
       <c r="CU14" s="1">
-        <f t="shared" si="99"/>
-        <v>24.929898000631972</v>
+        <f t="shared" si="96"/>
+        <v>100.40490300201819</v>
       </c>
       <c r="CV14" s="1">
-        <f t="shared" si="99"/>
-        <v>24.680599020625653</v>
+        <f t="shared" si="96"/>
+        <v>99.400853971998004</v>
       </c>
       <c r="CW14" s="1">
-        <f t="shared" si="99"/>
-        <v>24.433793030419395</v>
+        <f t="shared" si="96"/>
+        <v>98.406845432278018</v>
       </c>
       <c r="CX14" s="1">
-        <f t="shared" si="99"/>
-        <v>24.1894551001152</v>
+        <f t="shared" si="96"/>
+        <v>97.422776977955237</v>
       </c>
       <c r="CY14" s="1">
-        <f t="shared" si="99"/>
-        <v>23.947560549114048</v>
+        <f t="shared" si="96"/>
+        <v>96.448549208175677</v>
       </c>
       <c r="CZ14" s="1">
-        <f t="shared" si="99"/>
-        <v>23.708084943622907</v>
+        <f t="shared" si="96"/>
+        <v>95.484063716093914</v>
       </c>
       <c r="DA14" s="1">
-        <f t="shared" si="99"/>
-        <v>23.471004094186679</v>
+        <f t="shared" si="96"/>
+        <v>94.529223078932972</v>
       </c>
       <c r="DB14" s="1">
-        <f t="shared" si="99"/>
-        <v>23.236294053244812</v>
+        <f t="shared" si="96"/>
+        <v>93.583930848143638</v>
       </c>
       <c r="DC14" s="1">
-        <f t="shared" si="99"/>
-        <v>23.003931112712365</v>
+        <f t="shared" si="96"/>
+        <v>92.648091539662204</v>
       </c>
       <c r="DD14" s="1">
-        <f t="shared" si="99"/>
-        <v>22.77389180158524</v>
+        <f t="shared" si="96"/>
+        <v>91.72161062426558</v>
       </c>
       <c r="DE14" s="1">
-        <f t="shared" si="99"/>
-        <v>22.546152883569388</v>
+        <f t="shared" si="96"/>
+        <v>90.804394518022917</v>
       </c>
       <c r="DF14" s="1">
-        <f t="shared" si="99"/>
-        <v>22.320691354733693</v>
+        <f t="shared" si="96"/>
+        <v>89.896350572842692</v>
       </c>
       <c r="DG14" s="1">
-        <f t="shared" si="99"/>
-        <v>22.097484441186356</v>
+        <f t="shared" si="96"/>
+        <v>88.997387067114261</v>
       </c>
       <c r="DH14" s="1">
-        <f t="shared" si="99"/>
-        <v>21.876509596774493</v>
+        <f t="shared" si="96"/>
+        <v>88.107413196443119</v>
       </c>
       <c r="DI14" s="1">
-        <f t="shared" si="99"/>
-        <v>21.65774450080675</v>
+        <f t="shared" si="96"/>
+        <v>87.226339064478694</v>
       </c>
       <c r="DJ14" s="1">
-        <f t="shared" si="99"/>
-        <v>21.441167055798683</v>
+        <f t="shared" si="96"/>
+        <v>86.354075673833904</v>
       </c>
       <c r="DK14" s="1">
-        <f t="shared" si="99"/>
-        <v>21.226755385240697</v>
+        <f t="shared" si="96"/>
+        <v>85.490534917095559</v>
       </c>
       <c r="DL14" s="1">
-        <f t="shared" si="99"/>
-        <v>21.014487831388291</v>
+        <f t="shared" si="96"/>
+        <v>84.635629567924596</v>
       </c>
       <c r="DM14" s="1">
-        <f t="shared" si="99"/>
-        <v>20.804342953074407</v>
+        <f t="shared" si="96"/>
+        <v>83.789273272245353</v>
       </c>
       <c r="DN14" s="1">
-        <f t="shared" si="99"/>
-        <v>20.596299523543664</v>
+        <f t="shared" si="96"/>
+        <v>82.951380539522901</v>
       </c>
       <c r="DO14" s="1">
-        <f t="shared" si="99"/>
-        <v>20.390336528308225</v>
+        <f t="shared" si="96"/>
+        <v>82.121866734127678</v>
       </c>
       <c r="DP14" s="1">
-        <f t="shared" ref="DP14:FT14" si="100">DO14*(1+$BE$20)</f>
-        <v>20.186433163025143</v>
+        <f t="shared" ref="DP14:FT14" si="97">DO14*(1+$BE$20)</f>
+        <v>81.300648066786394</v>
       </c>
       <c r="DQ14" s="1">
-        <f t="shared" si="100"/>
-        <v>19.984568831394892</v>
+        <f t="shared" si="97"/>
+        <v>80.487641586118528</v>
       </c>
       <c r="DR14" s="1">
-        <f t="shared" si="100"/>
-        <v>19.784723143080942</v>
+        <f t="shared" si="97"/>
+        <v>79.682765170257341</v>
       </c>
       <c r="DS14" s="1">
-        <f t="shared" si="100"/>
-        <v>19.586875911650132</v>
+        <f t="shared" si="97"/>
+        <v>78.885937518554769</v>
       </c>
       <c r="DT14" s="1">
-        <f t="shared" si="100"/>
-        <v>19.391007152533632</v>
+        <f t="shared" si="97"/>
+        <v>78.097078143369217</v>
       </c>
       <c r="DU14" s="1">
-        <f t="shared" si="100"/>
-        <v>19.197097081008295</v>
+        <f t="shared" si="97"/>
+        <v>77.316107361935522</v>
       </c>
       <c r="DV14" s="1">
-        <f t="shared" si="100"/>
-        <v>19.005126110198212</v>
+        <f t="shared" si="97"/>
+        <v>76.542946288316173</v>
       </c>
       <c r="DW14" s="1">
-        <f t="shared" si="100"/>
-        <v>18.815074849096231</v>
+        <f t="shared" si="97"/>
+        <v>75.777516825433011</v>
       </c>
       <c r="DX14" s="1">
-        <f t="shared" si="100"/>
-        <v>18.626924100605269</v>
+        <f t="shared" si="97"/>
+        <v>75.019741657178685</v>
       </c>
       <c r="DY14" s="1">
-        <f t="shared" si="100"/>
-        <v>18.440654859599217</v>
+        <f t="shared" si="97"/>
+        <v>74.269544240606891</v>
       </c>
       <c r="DZ14" s="1">
-        <f t="shared" si="100"/>
-        <v>18.256248311003226</v>
+        <f t="shared" si="97"/>
+        <v>73.526848798200817</v>
       </c>
       <c r="EA14" s="1">
-        <f t="shared" si="100"/>
-        <v>18.073685827893193</v>
+        <f t="shared" si="97"/>
+        <v>72.791580310218805</v>
       </c>
       <c r="EB14" s="1">
-        <f t="shared" si="100"/>
-        <v>17.89294896961426</v>
+        <f t="shared" si="97"/>
+        <v>72.063664507116613</v>
       </c>
       <c r="EC14" s="1">
-        <f t="shared" si="100"/>
-        <v>17.714019479918118</v>
+        <f t="shared" si="97"/>
+        <v>71.343027862045446</v>
       </c>
       <c r="ED14" s="1">
-        <f t="shared" si="100"/>
-        <v>17.536879285118935</v>
+        <f t="shared" si="97"/>
+        <v>70.629597583424996</v>
       </c>
       <c r="EE14" s="1">
-        <f t="shared" si="100"/>
-        <v>17.361510492267747</v>
+        <f t="shared" si="97"/>
+        <v>69.923301607590744</v>
       </c>
       <c r="EF14" s="1">
-        <f t="shared" si="100"/>
-        <v>17.187895387345069</v>
+        <f t="shared" si="97"/>
+        <v>69.224068591514836</v>
       </c>
       <c r="EG14" s="1">
-        <f t="shared" si="100"/>
-        <v>17.01601643347162</v>
+        <f t="shared" si="97"/>
+        <v>68.531827905599684</v>
       </c>
       <c r="EH14" s="1">
-        <f t="shared" si="100"/>
-        <v>16.845856269136902</v>
+        <f t="shared" si="97"/>
+        <v>67.846509626543693</v>
       </c>
       <c r="EI14" s="1">
-        <f t="shared" si="100"/>
-        <v>16.677397706445532</v>
+        <f t="shared" si="97"/>
+        <v>67.168044530278252</v>
       </c>
       <c r="EJ14" s="1">
-        <f t="shared" si="100"/>
-        <v>16.510623729381077</v>
+        <f t="shared" si="97"/>
+        <v>66.496364084975468</v>
       </c>
       <c r="EK14" s="1">
-        <f t="shared" si="100"/>
-        <v>16.345517492087268</v>
+        <f t="shared" si="97"/>
+        <v>65.83140044412572</v>
       </c>
       <c r="EL14" s="1">
-        <f t="shared" si="100"/>
-        <v>16.182062317166395</v>
+        <f t="shared" si="97"/>
+        <v>65.173086439684468</v>
       </c>
       <c r="EM14" s="1">
-        <f t="shared" si="100"/>
-        <v>16.020241693994731</v>
+        <f t="shared" si="97"/>
+        <v>64.521355575287629</v>
       </c>
       <c r="EN14" s="1">
-        <f t="shared" si="100"/>
-        <v>15.860039277054783</v>
+        <f t="shared" si="97"/>
+        <v>63.876142019534754</v>
       </c>
       <c r="EO14" s="1">
-        <f t="shared" si="100"/>
-        <v>15.701438884284235</v>
+        <f t="shared" si="97"/>
+        <v>63.237380599339403</v>
       </c>
       <c r="EP14" s="1">
-        <f t="shared" si="100"/>
-        <v>15.544424495441392</v>
+        <f t="shared" si="97"/>
+        <v>62.605006793346007</v>
       </c>
       <c r="EQ14" s="1">
-        <f t="shared" si="100"/>
-        <v>15.388980250486979</v>
+        <f t="shared" si="97"/>
+        <v>61.978956725412544</v>
       </c>
       <c r="ER14" s="1">
-        <f t="shared" si="100"/>
-        <v>15.23509044798211</v>
+        <f t="shared" si="97"/>
+        <v>61.359167158158421</v>
       </c>
       <c r="ES14" s="1">
-        <f t="shared" si="100"/>
-        <v>15.082739543502289</v>
+        <f t="shared" si="97"/>
+        <v>60.745575486576833</v>
       </c>
       <c r="ET14" s="1">
-        <f t="shared" si="100"/>
-        <v>14.931912148067266</v>
+        <f t="shared" si="97"/>
+        <v>60.138119731711065</v>
       </c>
       <c r="EU14" s="1">
-        <f t="shared" si="100"/>
-        <v>14.782593026586593</v>
+        <f t="shared" si="97"/>
+        <v>59.536738534393955</v>
       </c>
       <c r="EV14" s="1">
-        <f t="shared" si="100"/>
-        <v>14.634767096320727</v>
+        <f t="shared" si="97"/>
+        <v>58.941371149050013</v>
       </c>
       <c r="EW14" s="1">
-        <f t="shared" si="100"/>
-        <v>14.48841942535752</v>
+        <f t="shared" si="97"/>
+        <v>58.351957437559513</v>
       </c>
       <c r="EX14" s="1">
-        <f t="shared" si="100"/>
-        <v>14.343535231103944</v>
+        <f t="shared" si="97"/>
+        <v>57.768437863183919</v>
       </c>
       <c r="EY14" s="1">
-        <f t="shared" si="100"/>
-        <v>14.200099878792905</v>
+        <f t="shared" si="97"/>
+        <v>57.190753484552083</v>
       </c>
       <c r="EZ14" s="1">
-        <f t="shared" si="100"/>
-        <v>14.058098880004975</v>
+        <f t="shared" si="97"/>
+        <v>56.618845949706561</v>
       </c>
       <c r="FA14" s="1">
-        <f t="shared" si="100"/>
-        <v>13.917517891204925</v>
+        <f t="shared" si="97"/>
+        <v>56.052657490209498</v>
       </c>
       <c r="FB14" s="1">
-        <f t="shared" si="100"/>
-        <v>13.778342712292876</v>
+        <f t="shared" si="97"/>
+        <v>55.492130915307399</v>
       </c>
       <c r="FC14" s="1">
-        <f t="shared" si="100"/>
-        <v>13.640559285169946</v>
+        <f t="shared" si="97"/>
+        <v>54.937209606154326</v>
       </c>
       <c r="FD14" s="1">
-        <f t="shared" si="100"/>
-        <v>13.504153692318246</v>
+        <f t="shared" si="97"/>
+        <v>54.38783751009278</v>
       </c>
       <c r="FE14" s="1">
-        <f t="shared" si="100"/>
-        <v>13.369112155395063</v>
+        <f t="shared" si="97"/>
+        <v>53.843959134991849</v>
       </c>
       <c r="FF14" s="1">
-        <f t="shared" si="100"/>
-        <v>13.235421033841112</v>
+        <f t="shared" si="97"/>
+        <v>53.305519543641928</v>
       </c>
       <c r="FG14" s="1">
-        <f t="shared" si="100"/>
-        <v>13.103066823502701</v>
+        <f t="shared" si="97"/>
+        <v>52.77246434820551</v>
       </c>
       <c r="FH14" s="1">
-        <f t="shared" si="100"/>
-        <v>12.972036155267674</v>
+        <f t="shared" si="97"/>
+        <v>52.244739704723457</v>
       </c>
       <c r="FI14" s="1">
-        <f t="shared" si="100"/>
-        <v>12.842315793714997</v>
+        <f t="shared" si="97"/>
+        <v>51.72229230767622</v>
       </c>
       <c r="FJ14" s="1">
-        <f t="shared" si="100"/>
-        <v>12.713892635777848</v>
+        <f t="shared" si="97"/>
+        <v>51.205069384599454</v>
       </c>
       <c r="FK14" s="1">
-        <f t="shared" si="100"/>
-        <v>12.586753709420069</v>
+        <f t="shared" si="97"/>
+        <v>50.693018690753462</v>
       </c>
       <c r="FL14" s="1">
-        <f t="shared" si="100"/>
-        <v>12.460886172325868</v>
+        <f t="shared" si="97"/>
+        <v>50.18608850384593</v>
       </c>
       <c r="FM14" s="1">
-        <f t="shared" si="100"/>
-        <v>12.336277310602609</v>
+        <f t="shared" si="97"/>
+        <v>49.684227618807469</v>
       </c>
       <c r="FN14" s="1">
-        <f t="shared" si="100"/>
-        <v>12.212914537496584</v>
+        <f t="shared" si="97"/>
+        <v>49.187385342619393</v>
       </c>
       <c r="FO14" s="1">
-        <f t="shared" si="100"/>
-        <v>12.090785392121617</v>
+        <f t="shared" si="97"/>
+        <v>48.695511489193201</v>
       </c>
       <c r="FP14" s="1">
-        <f t="shared" si="100"/>
-        <v>11.9698775382004</v>
+        <f t="shared" si="97"/>
+        <v>48.208556374301267</v>
       </c>
       <c r="FQ14" s="1">
-        <f t="shared" si="100"/>
-        <v>11.850178762818397</v>
+        <f t="shared" si="97"/>
+        <v>47.726470810558254</v>
       </c>
       <c r="FR14" s="1">
-        <f t="shared" si="100"/>
-        <v>11.731676975190213</v>
+        <f t="shared" si="97"/>
+        <v>47.249206102452675</v>
       </c>
       <c r="FS14" s="1">
-        <f t="shared" si="100"/>
-        <v>11.614360205438311</v>
+        <f t="shared" si="97"/>
+        <v>46.77671404142815</v>
       </c>
       <c r="FT14" s="1">
-        <f t="shared" si="100"/>
-        <v>11.498216603383929</v>
+        <f t="shared" si="97"/>
+        <v>46.308946901013869</v>
       </c>
     </row>
     <row r="15" spans="2:176" x14ac:dyDescent="0.3">
@@ -3960,16 +4002,13 @@
         <v>119.1</v>
       </c>
       <c r="AF15" s="4">
-        <f>119.1</f>
-        <v>119.1</v>
+        <v>120.1</v>
       </c>
       <c r="AG15" s="4">
-        <f>119.1</f>
-        <v>119.1</v>
+        <v>120.1</v>
       </c>
       <c r="AH15" s="4">
-        <f>119.1</f>
-        <v>119.1</v>
+        <v>120.1</v>
       </c>
       <c r="AI15" s="4"/>
       <c r="AK15" s="4">
@@ -3994,48 +4033,37 @@
         <v>121.4</v>
       </c>
       <c r="AR15" s="4">
-        <f t="shared" ref="AR15:BB15" si="101">119.1</f>
-        <v>119.1</v>
+        <v>120.1</v>
       </c>
       <c r="AS15" s="4">
-        <f t="shared" si="101"/>
-        <v>119.1</v>
+        <v>120.1</v>
       </c>
       <c r="AT15" s="4">
-        <f t="shared" si="101"/>
-        <v>119.1</v>
+        <v>120.1</v>
       </c>
       <c r="AU15" s="4">
-        <f t="shared" si="101"/>
-        <v>119.1</v>
+        <v>120.1</v>
       </c>
       <c r="AV15" s="4">
-        <f t="shared" si="101"/>
-        <v>119.1</v>
+        <v>120.1</v>
       </c>
       <c r="AW15" s="4">
-        <f t="shared" si="101"/>
-        <v>119.1</v>
+        <v>120.1</v>
       </c>
       <c r="AX15" s="4">
-        <f t="shared" si="101"/>
-        <v>119.1</v>
+        <v>120.1</v>
       </c>
       <c r="AY15" s="4">
-        <f t="shared" si="101"/>
-        <v>119.1</v>
+        <v>120.1</v>
       </c>
       <c r="AZ15" s="4">
-        <f t="shared" si="101"/>
-        <v>119.1</v>
+        <v>120.1</v>
       </c>
       <c r="BA15" s="4">
-        <f t="shared" si="101"/>
-        <v>119.1</v>
+        <v>120.1</v>
       </c>
       <c r="BB15" s="4">
-        <f t="shared" si="101"/>
-        <v>119.1</v>
+        <v>120.1</v>
       </c>
     </row>
     <row r="16" spans="2:176" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -4043,132 +4071,132 @@
         <v>34</v>
       </c>
       <c r="C16" s="9">
-        <f t="shared" ref="C16:M16" si="102">C14/C15</f>
+        <f t="shared" ref="C16:M16" si="98">C14/C15</f>
         <v>0.41261261261261245</v>
       </c>
       <c r="D16" s="9">
+        <f t="shared" si="98"/>
+        <v>-0.29369369369369386</v>
+      </c>
+      <c r="E16" s="9">
+        <f t="shared" si="98"/>
+        <v>-0.24324324324324317</v>
+      </c>
+      <c r="F16" s="9">
+        <f t="shared" si="98"/>
+        <v>-1.6216216216216266E-2</v>
+      </c>
+      <c r="G16" s="9">
+        <f t="shared" si="98"/>
+        <v>0.5549549549549545</v>
+      </c>
+      <c r="H16" s="9">
+        <f t="shared" si="98"/>
+        <v>-0.20630630630630645</v>
+      </c>
+      <c r="I16" s="9">
+        <f t="shared" si="98"/>
+        <v>-0.12702702702702692</v>
+      </c>
+      <c r="J16" s="9">
+        <f t="shared" si="98"/>
+        <v>-0.26666666666666677</v>
+      </c>
+      <c r="K16" s="9">
+        <f t="shared" si="98"/>
+        <v>0.6378378378378381</v>
+      </c>
+      <c r="L16" s="9">
+        <f t="shared" si="98"/>
+        <v>-0.47117117117117108</v>
+      </c>
+      <c r="M16" s="9">
+        <f t="shared" si="98"/>
+        <v>-0.51441441441441416</v>
+      </c>
+      <c r="N16" s="9">
+        <f t="shared" ref="N16:O16" si="99">N14/N15</f>
+        <v>0.1628318584070797</v>
+      </c>
+      <c r="O16" s="9">
+        <f t="shared" si="99"/>
+        <v>1.1716814159292039</v>
+      </c>
+      <c r="P16" s="9">
+        <f t="shared" ref="P16:Q16" si="100">P14/P15</f>
+        <v>0.15221238938053105</v>
+      </c>
+      <c r="Q16" s="9">
+        <f t="shared" si="100"/>
+        <v>0.14744645799011497</v>
+      </c>
+      <c r="R16" s="9">
+        <f t="shared" ref="R16" si="101">R14/R15</f>
+        <v>-7.331136738056028E-2</v>
+      </c>
+      <c r="S16" s="9">
+        <f t="shared" ref="S16:T16" si="102">S14/S15</f>
+        <v>1.0181219110378912</v>
+      </c>
+      <c r="T16" s="9">
         <f t="shared" si="102"/>
-        <v>-0.29369369369369386</v>
-      </c>
-      <c r="E16" s="9">
-        <f t="shared" si="102"/>
-        <v>-0.24324324324324317</v>
-      </c>
-      <c r="F16" s="9">
-        <f t="shared" si="102"/>
-        <v>-1.6216216216216266E-2</v>
-      </c>
-      <c r="G16" s="9">
-        <f t="shared" si="102"/>
-        <v>0.5549549549549545</v>
-      </c>
-      <c r="H16" s="9">
-        <f t="shared" si="102"/>
-        <v>-0.20630630630630645</v>
-      </c>
-      <c r="I16" s="9">
-        <f t="shared" si="102"/>
-        <v>-0.12702702702702692</v>
-      </c>
-      <c r="J16" s="9">
-        <f t="shared" si="102"/>
-        <v>-0.26666666666666677</v>
-      </c>
-      <c r="K16" s="9">
-        <f t="shared" si="102"/>
-        <v>0.6378378378378381</v>
-      </c>
-      <c r="L16" s="9">
-        <f t="shared" si="102"/>
-        <v>-0.47117117117117108</v>
-      </c>
-      <c r="M16" s="9">
-        <f t="shared" si="102"/>
-        <v>-0.51441441441441416</v>
-      </c>
-      <c r="N16" s="9">
-        <f t="shared" ref="N16:O16" si="103">N14/N15</f>
-        <v>0.1628318584070797</v>
-      </c>
-      <c r="O16" s="9">
-        <f t="shared" si="103"/>
-        <v>1.1716814159292039</v>
-      </c>
-      <c r="P16" s="9">
-        <f t="shared" ref="P16:Q16" si="104">P14/P15</f>
-        <v>0.15221238938053105</v>
-      </c>
-      <c r="Q16" s="9">
+        <v>7.1663920922570193E-2</v>
+      </c>
+      <c r="U16" s="9">
+        <f t="shared" ref="U16" si="103">U14/U15</f>
+        <v>-4.1186161449752847E-3</v>
+      </c>
+      <c r="V16" s="9">
+        <f t="shared" ref="V16:W16" si="104">V14/V15</f>
+        <v>-0.52718286655683644</v>
+      </c>
+      <c r="W16" s="9">
         <f t="shared" si="104"/>
-        <v>0.14744645799011497</v>
-      </c>
-      <c r="R16" s="9">
-        <f t="shared" ref="R16" si="105">R14/R15</f>
-        <v>-7.331136738056028E-2</v>
-      </c>
-      <c r="S16" s="9">
-        <f t="shared" ref="S16:T16" si="106">S14/S15</f>
-        <v>1.0181219110378912</v>
-      </c>
-      <c r="T16" s="9">
-        <f t="shared" si="106"/>
-        <v>7.1663920922570193E-2</v>
-      </c>
-      <c r="U16" s="9">
-        <f t="shared" ref="U16" si="107">U14/U15</f>
-        <v>-4.1186161449752847E-3</v>
-      </c>
-      <c r="V16" s="9">
-        <f t="shared" ref="V16:W16" si="108">V14/V15</f>
-        <v>-0.52718286655683644</v>
-      </c>
-      <c r="W16" s="9">
-        <f t="shared" si="108"/>
         <v>0.62026359143327847</v>
       </c>
       <c r="X16" s="9">
-        <f t="shared" ref="X16" si="109">X14/X15</f>
+        <f t="shared" ref="X16" si="105">X14/X15</f>
         <v>-0.25205930807248778</v>
       </c>
       <c r="Y16" s="9">
-        <f t="shared" ref="Y16" si="110">Y14/Y15</f>
+        <f t="shared" ref="Y16" si="106">Y14/Y15</f>
         <v>-0.19522240527182849</v>
       </c>
       <c r="Z16" s="9">
-        <f t="shared" ref="Z16:AA16" si="111">Z14/Z15</f>
+        <f t="shared" ref="Z16:AA16" si="107">Z14/Z15</f>
         <v>-0.25782537067545264</v>
       </c>
       <c r="AA16" s="9">
-        <f t="shared" si="111"/>
+        <f t="shared" si="107"/>
         <v>0.66639209225700158</v>
       </c>
       <c r="AB16" s="9">
-        <f t="shared" ref="AB16" si="112">AB14/AB15</f>
+        <f t="shared" ref="AB16" si="108">AB14/AB15</f>
         <v>-0.57331136738055999</v>
       </c>
       <c r="AC16" s="9">
-        <f t="shared" ref="AC16" si="113">AC14/AC15</f>
+        <f t="shared" ref="AC16" si="109">AC14/AC15</f>
         <v>3.0477759472817317E-2</v>
       </c>
       <c r="AD16" s="9">
-        <f t="shared" ref="AD16:AH16" si="114">AD14/AD15</f>
+        <f t="shared" ref="AD16:AH16" si="110">AD14/AD15</f>
         <v>-0.43739703459637569</v>
       </c>
       <c r="AE16" s="9">
-        <f t="shared" si="114"/>
+        <f t="shared" si="110"/>
         <v>0.42317380352644823</v>
       </c>
       <c r="AF16" s="9">
-        <f t="shared" si="114"/>
-        <v>-0.52970251889168762</v>
+        <f t="shared" si="110"/>
+        <v>-0.5828476269775188</v>
       </c>
       <c r="AG16" s="9">
-        <f t="shared" si="114"/>
-        <v>-6.237423173803501E-2</v>
+        <f t="shared" si="110"/>
+        <v>-2.8309741881765244E-2</v>
       </c>
       <c r="AH16" s="9">
-        <f t="shared" si="114"/>
-        <v>-0.60381612090680092</v>
+        <f t="shared" si="110"/>
+        <v>-0.53470791007493745</v>
       </c>
       <c r="AI16" s="9"/>
       <c r="AK16" s="9">
@@ -4184,64 +4212,64 @@
         <v>-0.17876106194690428</v>
       </c>
       <c r="AN16" s="9">
-        <f t="shared" ref="AN16:AW16" si="115">AN14/AN15</f>
+        <f t="shared" ref="AN16:AW16" si="111">AN14/AN15</f>
         <v>1.4035398230088483</v>
       </c>
       <c r="AO16" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="111"/>
         <v>0.59999999999999964</v>
       </c>
       <c r="AP16" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="111"/>
         <v>-9.1150442477879137E-2</v>
       </c>
       <c r="AQ16" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="111"/>
         <v>-0.31383855024711677</v>
       </c>
       <c r="AR16" s="9">
-        <f t="shared" si="115"/>
-        <v>-0.77271906801007517</v>
+        <f t="shared" si="111"/>
+        <v>-0.72621498751041036</v>
       </c>
       <c r="AS16" s="9">
-        <f t="shared" si="115"/>
-        <v>-0.49265117319899171</v>
+        <f t="shared" si="111"/>
+        <v>2.8376058617818039E-2</v>
       </c>
       <c r="AT16" s="9">
-        <f t="shared" si="115"/>
-        <v>-0.27157719064503749</v>
+        <f t="shared" si="111"/>
+        <v>0.35111405033405507</v>
       </c>
       <c r="AU16" s="9">
-        <f t="shared" si="115"/>
-        <v>-6.725819555639509E-2</v>
+        <f t="shared" si="111"/>
+        <v>0.63580520442332156</v>
       </c>
       <c r="AV16" s="9">
-        <f t="shared" si="115"/>
-        <v>0.16733605202781068</v>
+        <f t="shared" si="111"/>
+        <v>0.9015715624726085</v>
       </c>
       <c r="AW16" s="9">
-        <f t="shared" si="115"/>
-        <v>0.3119122354158681</v>
+        <f t="shared" si="111"/>
+        <v>1.0623886035475261</v>
       </c>
       <c r="AX16" s="9">
-        <f t="shared" ref="AX16:BB16" si="116">AX14/AX15</f>
-        <v>0.31617458035296947</v>
+        <f t="shared" ref="AX16:BB16" si="112">AX14/AX15</f>
+        <v>1.1109717014334453</v>
       </c>
       <c r="AY16" s="9">
-        <f t="shared" si="116"/>
-        <v>0.31934547193716384</v>
+        <f t="shared" si="112"/>
+        <v>1.1598647894143634</v>
       </c>
       <c r="AZ16" s="9">
-        <f t="shared" si="116"/>
-        <v>0.32253899982277995</v>
+        <f t="shared" si="112"/>
+        <v>1.2099949954934566</v>
       </c>
       <c r="BA16" s="9">
-        <f t="shared" si="116"/>
-        <v>0.32576439040633809</v>
+        <f t="shared" si="112"/>
+        <v>1.26139707495543</v>
       </c>
       <c r="BB16" s="9">
-        <f t="shared" si="116"/>
-        <v>0.32902203431508337</v>
+        <f t="shared" si="112"/>
+        <v>1.3140992173234332</v>
       </c>
     </row>
     <row r="18" spans="2:57" x14ac:dyDescent="0.3">
@@ -4253,112 +4281,112 @@
         <v>5.8422174840085273E-2</v>
       </c>
       <c r="H18" s="11">
-        <f t="shared" ref="H18:N18" si="117">H3/D3-1</f>
+        <f t="shared" ref="H18:N18" si="113">H3/D3-1</f>
         <v>0.12587038028923403</v>
       </c>
       <c r="I18" s="11">
-        <f t="shared" si="117"/>
+        <f t="shared" si="113"/>
         <v>0.24808061420345506</v>
       </c>
       <c r="J18" s="11">
-        <f t="shared" si="117"/>
+        <f t="shared" si="113"/>
         <v>7.8050567973616758E-2</v>
       </c>
       <c r="K18" s="11">
-        <f t="shared" si="117"/>
+        <f t="shared" si="113"/>
         <v>0.13235294117647078</v>
       </c>
       <c r="L18" s="11">
-        <f t="shared" si="117"/>
+        <f t="shared" si="113"/>
         <v>-0.16698382492863939</v>
       </c>
       <c r="M18" s="11">
-        <f t="shared" si="117"/>
+        <f t="shared" si="113"/>
         <v>-4.152249134948105E-2</v>
       </c>
       <c r="N18" s="11">
-        <f t="shared" si="117"/>
+        <f t="shared" si="113"/>
         <v>0.15499660095173362</v>
       </c>
       <c r="O18" s="11">
-        <f t="shared" ref="O18" si="118">O3/K3-1</f>
+        <f t="shared" ref="O18" si="114">O3/K3-1</f>
         <v>0.14855008005692927</v>
       </c>
       <c r="P18" s="11">
-        <f t="shared" ref="P18" si="119">P3/L3-1</f>
+        <f t="shared" ref="P18" si="115">P3/L3-1</f>
         <v>0.90119931467732717</v>
       </c>
       <c r="Q18" s="11">
-        <f t="shared" ref="Q18" si="120">Q3/M3-1</f>
+        <f t="shared" ref="Q18" si="116">Q3/M3-1</f>
         <v>0.51905334937825898</v>
       </c>
       <c r="R18" s="11">
-        <f t="shared" ref="R18" si="121">R3/N3-1</f>
+        <f t="shared" ref="R18" si="117">R3/N3-1</f>
         <v>5.768098881695094E-2</v>
       </c>
       <c r="S18" s="11">
-        <f t="shared" ref="S18" si="122">S3/O3-1</f>
+        <f t="shared" ref="S18" si="118">S3/O3-1</f>
         <v>2.927509293680286E-2</v>
       </c>
       <c r="T18" s="11">
-        <f t="shared" ref="T18" si="123">T3/P3-1</f>
+        <f t="shared" ref="T18" si="119">T3/P3-1</f>
         <v>0.2009612496245119</v>
       </c>
       <c r="U18" s="11">
-        <f t="shared" ref="U18" si="124">U3/Q3-1</f>
+        <f t="shared" ref="U18" si="120">U3/Q3-1</f>
         <v>-1.8220227092685448E-2</v>
       </c>
       <c r="V18" s="11">
-        <f t="shared" ref="V18" si="125">V3/R3-1</f>
+        <f t="shared" ref="V18" si="121">V3/R3-1</f>
         <v>-0.11992209237618245</v>
       </c>
       <c r="W18" s="11">
-        <f t="shared" ref="W18" si="126">W3/S3-1</f>
+        <f t="shared" ref="W18" si="122">W3/S3-1</f>
         <v>1.2189616252821667E-2</v>
       </c>
       <c r="X18" s="11">
-        <f t="shared" ref="X18" si="127">X3/T3-1</f>
+        <f t="shared" ref="X18" si="123">X3/T3-1</f>
         <v>-0.23911955977988997</v>
       </c>
       <c r="Y18" s="11">
-        <f t="shared" ref="Y18" si="128">Y3/U3-1</f>
+        <f t="shared" ref="Y18" si="124">Y3/U3-1</f>
         <v>4.3033889187733543E-3</v>
       </c>
       <c r="Z18" s="11">
-        <f t="shared" ref="Z18" si="129">Z3/V3-1</f>
+        <f t="shared" ref="Z18" si="125">Z3/V3-1</f>
         <v>-3.54094214353462E-2</v>
       </c>
       <c r="AA18" s="11">
-        <f t="shared" ref="AA18" si="130">AA3/W3-1</f>
+        <f t="shared" ref="AA18" si="126">AA3/W3-1</f>
         <v>-8.8760035682426519E-2</v>
       </c>
       <c r="AB18" s="11">
-        <f t="shared" ref="AB18" si="131">AB3/X3-1</f>
+        <f t="shared" ref="AB18" si="127">AB3/X3-1</f>
         <v>-0.16929651545036162</v>
       </c>
       <c r="AC18" s="11">
-        <f t="shared" ref="AC18" si="132">AC3/Y3-1</f>
+        <f t="shared" ref="AC18" si="128">AC3/Y3-1</f>
         <v>6.3470808784145794E-2</v>
       </c>
       <c r="AD18" s="11">
-        <f t="shared" ref="AD18" si="133">AD3/Z3-1</f>
+        <f t="shared" ref="AD18" si="129">AD3/Z3-1</f>
         <v>-0.16289741068502139</v>
       </c>
       <c r="AE18" s="11">
-        <f t="shared" ref="AE18" si="134">AE3/AA3-1</f>
+        <f t="shared" ref="AE18" si="130">AE3/AA3-1</f>
         <v>-0.10115842714961654</v>
       </c>
       <c r="AF18" s="11">
-        <f t="shared" ref="AF18" si="135">AF3/AB3-1</f>
-        <v>-5.0000000000000044E-2</v>
+        <f t="shared" ref="AF18" si="131">AF3/AB3-1</f>
+        <v>2.8096557182429871E-2</v>
       </c>
       <c r="AG18" s="11">
-        <f t="shared" ref="AG18" si="136">AG3/AC3-1</f>
-        <v>-6.9999999999999951E-2</v>
+        <f t="shared" ref="AG18" si="132">AG3/AC3-1</f>
+        <v>-0.13170486023671624</v>
       </c>
       <c r="AH18" s="11">
-        <f t="shared" ref="AH18" si="137">AH3/AD3-1</f>
-        <v>-5.0000000000000044E-2</v>
+        <f t="shared" ref="AH18" si="133">AH3/AD3-1</f>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AI18" s="11"/>
       <c r="AL18" s="11">
@@ -4370,64 +4398,64 @@
         <v>5.1867713537949056E-2</v>
       </c>
       <c r="AN18" s="11">
-        <f t="shared" ref="AN18:AW18" si="138">AN3/AM3-1</f>
+        <f t="shared" ref="AN18:AW18" si="134">AN3/AM3-1</f>
         <v>0.29427731282515257</v>
       </c>
       <c r="AO18" s="11">
-        <f t="shared" si="138"/>
+        <f t="shared" si="134"/>
         <v>2.0855178841896693E-2</v>
       </c>
       <c r="AP18" s="11">
-        <f t="shared" si="138"/>
+        <f t="shared" si="134"/>
         <v>-5.5409723807349986E-2</v>
       </c>
       <c r="AQ18" s="11">
-        <f t="shared" si="138"/>
+        <f t="shared" si="134"/>
         <v>-8.2885277593185425E-2</v>
       </c>
       <c r="AR18" s="11">
-        <f t="shared" si="138"/>
-        <v>-7.5885646531848927E-2</v>
+        <f t="shared" si="134"/>
+        <v>-6.5567485672880621E-2</v>
       </c>
       <c r="AS18" s="11">
-        <f t="shared" si="138"/>
+        <f t="shared" si="134"/>
+        <v>8.0000000000000071E-2</v>
+      </c>
+      <c r="AT18" s="11">
+        <f t="shared" si="134"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AT18" s="11">
-        <f t="shared" si="138"/>
+      <c r="AU18" s="11">
+        <f t="shared" si="134"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AU18" s="11">
-        <f t="shared" si="138"/>
+      <c r="AV18" s="11">
+        <f t="shared" si="134"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AV18" s="11">
-        <f t="shared" si="138"/>
+      <c r="AW18" s="11">
+        <f t="shared" si="134"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AW18" s="11">
-        <f t="shared" si="138"/>
+      <c r="AX18" s="11">
+        <f t="shared" ref="AX18" si="135">AX3/AW3-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AX18" s="11">
-        <f t="shared" ref="AX18" si="139">AX3/AW3-1</f>
-        <v>1.0000000000000009E-2</v>
-      </c>
       <c r="AY18" s="11">
-        <f t="shared" ref="AY18" si="140">AY3/AX3-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="AY18" si="136">AY3/AX3-1</f>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AZ18" s="11">
-        <f t="shared" ref="AZ18" si="141">AZ3/AY3-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="AZ18" si="137">AZ3/AY3-1</f>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="BA18" s="11">
-        <f t="shared" ref="BA18" si="142">BA3/AZ3-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="BA18" si="138">BA3/AZ3-1</f>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="BB18" s="11">
-        <f t="shared" ref="BB18" si="143">BB3/BA3-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="BB18" si="139">BB3/BA3-1</f>
+        <v>2.0000000000000018E-2</v>
       </c>
     </row>
     <row r="19" spans="2:57" x14ac:dyDescent="0.3">
@@ -4439,200 +4467,200 @@
         <v>0.41833688699360339</v>
       </c>
       <c r="D19" s="11">
-        <f t="shared" ref="D19:N19" si="144">D5/D3</f>
+        <f t="shared" ref="D19:N19" si="140">D5/D3</f>
         <v>0.43545795393679693</v>
       </c>
       <c r="E19" s="11">
-        <f t="shared" si="144"/>
+        <f t="shared" si="140"/>
         <v>0.45825335892514396</v>
       </c>
       <c r="F19" s="11">
-        <f t="shared" si="144"/>
+        <f t="shared" si="140"/>
         <v>0.42579699523635028</v>
       </c>
       <c r="G19" s="11">
-        <f t="shared" si="144"/>
+        <f t="shared" si="140"/>
         <v>0.39343271555197412</v>
       </c>
       <c r="H19" s="11">
-        <f t="shared" si="144"/>
+        <f t="shared" si="140"/>
         <v>0.43006660323501428</v>
       </c>
       <c r="I19" s="11">
-        <f t="shared" si="144"/>
+        <f t="shared" si="140"/>
         <v>0.45098039215686275</v>
       </c>
       <c r="J19" s="11">
-        <f t="shared" si="144"/>
+        <f t="shared" si="140"/>
         <v>0.42250169952413319</v>
       </c>
       <c r="K19" s="11">
-        <f t="shared" si="144"/>
+        <f t="shared" si="140"/>
         <v>0.40491015833481592</v>
       </c>
       <c r="L19" s="11">
-        <f t="shared" si="144"/>
+        <f t="shared" si="140"/>
         <v>0.41690462592804112</v>
       </c>
       <c r="M19" s="11">
-        <f t="shared" si="144"/>
+        <f t="shared" si="140"/>
         <v>0.44043321299638993</v>
       </c>
       <c r="N19" s="11">
-        <f t="shared" si="144"/>
+        <f t="shared" si="140"/>
         <v>0.47527957622130662</v>
       </c>
       <c r="O19" s="11">
-        <f t="shared" ref="O19:R19" si="145">O5/O3</f>
+        <f t="shared" ref="O19:R19" si="141">O5/O3</f>
         <v>0.46375464684014872</v>
       </c>
       <c r="P19" s="11">
-        <f t="shared" si="145"/>
+        <f t="shared" si="141"/>
         <v>0.49774707119255029</v>
       </c>
       <c r="Q19" s="11">
-        <f t="shared" si="145"/>
+        <f t="shared" si="141"/>
         <v>0.46976498547663054</v>
       </c>
       <c r="R19" s="11">
-        <f t="shared" si="145"/>
+        <f t="shared" si="141"/>
         <v>0.46410684474123537</v>
       </c>
       <c r="S19" s="11">
-        <f t="shared" ref="S19:AH19" si="146">S5/S3</f>
+        <f t="shared" ref="S19:AH19" si="142">S5/S3</f>
         <v>0.47765237020316026</v>
       </c>
       <c r="T19" s="11">
-        <f t="shared" si="146"/>
+        <f t="shared" si="142"/>
         <v>0.44797398699349678</v>
       </c>
       <c r="U19" s="11">
-        <f t="shared" si="146"/>
+        <f t="shared" si="142"/>
         <v>0.47310381925766543</v>
       </c>
       <c r="V19" s="11">
-        <f t="shared" si="146"/>
+        <f t="shared" si="142"/>
         <v>0.39234903572557706</v>
       </c>
       <c r="W19" s="11">
-        <f t="shared" si="146"/>
+        <f t="shared" si="142"/>
         <v>0.42387749033600952</v>
       </c>
       <c r="X19" s="11">
-        <f t="shared" si="146"/>
+        <f t="shared" si="142"/>
         <v>0.4326101249178172</v>
       </c>
       <c r="Y19" s="11">
-        <f t="shared" si="146"/>
+        <f t="shared" si="142"/>
         <v>0.46009641135511514</v>
       </c>
       <c r="Z19" s="11">
-        <f t="shared" si="146"/>
+        <f t="shared" si="142"/>
         <v>0.41953457882661427</v>
       </c>
       <c r="AA19" s="11">
-        <f t="shared" si="146"/>
+        <f t="shared" si="142"/>
         <v>0.46124979605155819</v>
       </c>
       <c r="AB19" s="11">
-        <f t="shared" si="146"/>
+        <f t="shared" si="142"/>
         <v>0.44360902255639095</v>
       </c>
       <c r="AC19" s="11">
-        <f t="shared" si="146"/>
+        <f t="shared" si="142"/>
         <v>0.48249811130697562</v>
       </c>
       <c r="AD19" s="11">
-        <f t="shared" si="146"/>
+        <f t="shared" si="142"/>
         <v>0.40328895849647611</v>
       </c>
       <c r="AE19" s="11">
-        <f t="shared" si="146"/>
+        <f t="shared" si="142"/>
         <v>0.438192049373752</v>
       </c>
       <c r="AF19" s="11">
-        <f t="shared" si="146"/>
-        <v>0.44</v>
+        <f t="shared" si="142"/>
+        <v>0.43764434180138573</v>
       </c>
       <c r="AG19" s="11">
-        <f t="shared" si="146"/>
-        <v>0.46</v>
+        <f t="shared" si="142"/>
+        <v>0.43445475638051045</v>
       </c>
       <c r="AH19" s="11">
-        <f t="shared" si="146"/>
+        <f t="shared" si="142"/>
         <v>0.4</v>
       </c>
       <c r="AI19" s="11"/>
       <c r="AK19" s="11">
-        <f t="shared" ref="AK19:AM19" si="147">AK5/AK3</f>
+        <f t="shared" ref="AK19:AM19" si="143">AK5/AK3</f>
         <v>0.43025505716798595</v>
       </c>
       <c r="AL19" s="11">
-        <f t="shared" si="147"/>
+        <f t="shared" si="143"/>
         <v>0.41819335395352519</v>
       </c>
       <c r="AM19" s="11">
-        <f t="shared" si="147"/>
+        <f t="shared" si="143"/>
         <v>0.4311995777727512</v>
       </c>
       <c r="AN19" s="11">
-        <f t="shared" ref="AN19:AW19" si="148">AN5/AN3</f>
+        <f t="shared" ref="AN19:AW19" si="144">AN5/AN3</f>
         <v>0.47174647559128502</v>
       </c>
       <c r="AO19" s="11">
-        <f t="shared" si="148"/>
+        <f t="shared" si="144"/>
         <v>0.45451951609221641</v>
       </c>
       <c r="AP19" s="11">
-        <f t="shared" si="148"/>
+        <f t="shared" si="144"/>
         <v>0.43285205098773621</v>
       </c>
       <c r="AQ19" s="11">
-        <f t="shared" si="148"/>
+        <f t="shared" si="144"/>
         <v>0.45412028193136156</v>
       </c>
       <c r="AR19" s="11">
-        <f t="shared" si="148"/>
-        <v>0.43763693440292883</v>
+        <f t="shared" si="144"/>
+        <v>0.43010090500097975</v>
       </c>
       <c r="AS19" s="11">
-        <f t="shared" si="148"/>
+        <f t="shared" si="144"/>
         <v>0.45</v>
       </c>
       <c r="AT19" s="11">
-        <f t="shared" si="148"/>
+        <f t="shared" si="144"/>
         <v>0.46</v>
       </c>
       <c r="AU19" s="11">
-        <f t="shared" si="148"/>
+        <f t="shared" si="144"/>
         <v>0.47</v>
       </c>
       <c r="AV19" s="11">
-        <f t="shared" si="148"/>
+        <f t="shared" si="144"/>
         <v>0.48</v>
       </c>
       <c r="AW19" s="11">
-        <f t="shared" si="148"/>
+        <f t="shared" si="144"/>
+        <v>0.48000000000000004</v>
+      </c>
+      <c r="AX19" s="11">
+        <f t="shared" ref="AX19:BB19" si="145">AX5/AX3</f>
         <v>0.48</v>
       </c>
-      <c r="AX19" s="11">
-        <f t="shared" ref="AX19:BB19" si="149">AX5/AX3</f>
+      <c r="AY19" s="11">
+        <f t="shared" si="145"/>
         <v>0.48</v>
       </c>
-      <c r="AY19" s="11">
-        <f t="shared" si="149"/>
+      <c r="AZ19" s="11">
+        <f t="shared" si="145"/>
         <v>0.48</v>
       </c>
-      <c r="AZ19" s="11">
-        <f t="shared" si="149"/>
+      <c r="BA19" s="11">
+        <f t="shared" si="145"/>
         <v>0.48</v>
       </c>
-      <c r="BA19" s="11">
-        <f t="shared" si="149"/>
-        <v>0.48</v>
-      </c>
       <c r="BB19" s="11">
-        <f t="shared" si="149"/>
+        <f t="shared" si="145"/>
         <v>0.48</v>
       </c>
     </row>
@@ -4645,201 +4673,201 @@
         <v>9.8720682302771826E-2</v>
       </c>
       <c r="D20" s="11">
-        <f t="shared" ref="D20:N20" si="150">D10/D3</f>
+        <f t="shared" ref="D20:N20" si="146">D10/D3</f>
         <v>-0.18050348152115703</v>
       </c>
       <c r="E20" s="11">
-        <f t="shared" si="150"/>
+        <f t="shared" si="146"/>
         <v>-0.10364683301343568</v>
       </c>
       <c r="F20" s="11">
-        <f t="shared" si="150"/>
+        <f t="shared" si="146"/>
         <v>3.6643459142540974E-4</v>
       </c>
       <c r="G20" s="11">
-        <f t="shared" si="150"/>
+        <f t="shared" si="146"/>
         <v>0.1379935535858178</v>
       </c>
       <c r="H20" s="11">
-        <f t="shared" si="150"/>
+        <f t="shared" si="146"/>
         <v>-0.10941960038058998</v>
       </c>
       <c r="I20" s="11">
-        <f t="shared" si="150"/>
+        <f t="shared" si="146"/>
         <v>-5.8439061899269465E-2</v>
       </c>
       <c r="J20" s="11">
-        <f t="shared" si="150"/>
+        <f t="shared" si="146"/>
         <v>-8.4296397008837565E-2</v>
       </c>
       <c r="K20" s="11">
-        <f t="shared" si="150"/>
+        <f t="shared" si="146"/>
         <v>0.12008539405799684</v>
       </c>
       <c r="L20" s="11">
-        <f t="shared" si="150"/>
+        <f t="shared" si="146"/>
         <v>-0.30382638492290115</v>
       </c>
       <c r="M20" s="11">
-        <f t="shared" si="150"/>
+        <f t="shared" si="146"/>
         <v>-0.22864019253910939</v>
       </c>
       <c r="N20" s="11">
-        <f t="shared" si="150"/>
+        <f t="shared" si="146"/>
         <v>4.5320776927604486E-2</v>
       </c>
       <c r="O20" s="11">
-        <f t="shared" ref="O20:R20" si="151">O10/O3</f>
+        <f t="shared" ref="O20:R20" si="147">O10/O3</f>
         <v>0.21298017348203224</v>
       </c>
       <c r="P20" s="11">
-        <f t="shared" si="151"/>
+        <f t="shared" si="147"/>
         <v>3.6948032442174865E-2</v>
       </c>
       <c r="Q20" s="11">
-        <f t="shared" si="151"/>
+        <f t="shared" si="147"/>
         <v>4.4362292051755889E-2</v>
       </c>
       <c r="R20" s="11">
-        <f t="shared" si="151"/>
+        <f t="shared" si="147"/>
         <v>-3.2554257095158648E-2</v>
       </c>
       <c r="S20" s="11">
-        <f t="shared" ref="S20:AH20" si="152">S10/S3</f>
+        <f t="shared" ref="S20:AH20" si="148">S10/S3</f>
         <v>0.19969902182091798</v>
       </c>
       <c r="T20" s="11">
-        <f t="shared" si="152"/>
+        <f t="shared" si="148"/>
         <v>2.5262631315657886E-2</v>
       </c>
       <c r="U20" s="11">
-        <f t="shared" si="152"/>
+        <f t="shared" si="148"/>
         <v>1.8827326519634213E-2</v>
       </c>
       <c r="V20" s="11">
-        <f t="shared" si="152"/>
+        <f t="shared" si="148"/>
         <v>-0.18969332911792583</v>
       </c>
       <c r="W20" s="11">
-        <f t="shared" si="152"/>
+        <f t="shared" si="148"/>
         <v>0.12845673505798394</v>
       </c>
       <c r="X20" s="11">
-        <f t="shared" si="152"/>
+        <f t="shared" si="148"/>
         <v>-0.18803418803418809</v>
       </c>
       <c r="Y20" s="11">
-        <f t="shared" si="152"/>
+        <f t="shared" si="148"/>
         <v>-5.7043385109801781E-2</v>
       </c>
       <c r="Z20" s="11">
-        <f t="shared" si="152"/>
+        <f t="shared" si="148"/>
         <v>-9.3084234677154862E-2</v>
       </c>
       <c r="AA20" s="11">
-        <f t="shared" si="152"/>
+        <f t="shared" si="148"/>
         <v>0.13003752651329742</v>
       </c>
       <c r="AB20" s="11">
-        <f t="shared" si="152"/>
+        <f t="shared" si="148"/>
         <v>-0.28017411950929949</v>
       </c>
       <c r="AC20" s="11">
-        <f t="shared" si="152"/>
+        <f t="shared" si="148"/>
         <v>3.1730042810375274E-2</v>
       </c>
       <c r="AD20" s="11">
-        <f t="shared" si="152"/>
+        <f t="shared" si="148"/>
         <v>-0.27173061863743148</v>
       </c>
       <c r="AE20" s="11">
-        <f t="shared" si="152"/>
+        <f t="shared" si="148"/>
         <v>8.7493192956979465E-2</v>
       </c>
       <c r="AF20" s="11">
-        <f t="shared" si="152"/>
-        <v>-0.29199300189532007</v>
+        <f t="shared" si="148"/>
+        <v>-0.23518090839107003</v>
       </c>
       <c r="AG20" s="11">
-        <f t="shared" si="152"/>
-        <v>-2.2350725555979681E-2</v>
+        <f t="shared" si="148"/>
+        <v>-8.4106728538283233E-3</v>
       </c>
       <c r="AH20" s="11">
-        <f t="shared" si="152"/>
-        <v>-0.3293286073445163</v>
+        <f t="shared" si="148"/>
+        <v>-0.2712432810516151</v>
       </c>
       <c r="AI20" s="11"/>
       <c r="AK20" s="11">
-        <f t="shared" ref="AK20:AM20" si="153">AK10/AK3</f>
+        <f t="shared" ref="AK20:AM20" si="149">AK10/AK3</f>
         <v>-7.8276165347405252E-3</v>
       </c>
       <c r="AL20" s="11">
-        <f t="shared" si="153"/>
+        <f t="shared" si="149"/>
         <v>4.3619636767387475E-3</v>
       </c>
       <c r="AM20" s="11">
-        <f t="shared" si="153"/>
+        <f t="shared" si="149"/>
         <v>-2.0583578375933186E-2</v>
       </c>
       <c r="AN20" s="11">
-        <f t="shared" ref="AN20:AW20" si="154">AN10/AN3</f>
+        <f t="shared" ref="AN20:AW20" si="150">AN10/AN3</f>
         <v>9.02365140393801E-2</v>
       </c>
       <c r="AO20" s="11">
-        <f t="shared" si="154"/>
+        <f t="shared" si="150"/>
         <v>5.1244008217301962E-2</v>
       </c>
       <c r="AP20" s="11">
-        <f t="shared" si="154"/>
+        <f t="shared" si="150"/>
         <v>-1.2384462031051981E-2</v>
       </c>
       <c r="AQ20" s="11">
-        <f t="shared" si="154"/>
+        <f t="shared" si="150"/>
         <v>-3.1552598643040629E-2</v>
       </c>
       <c r="AR20" s="11">
-        <f t="shared" si="154"/>
-        <v>-7.8449388337569745E-2</v>
+        <f t="shared" si="150"/>
+        <v>-6.1438132418604387E-2</v>
       </c>
       <c r="AS20" s="11">
-        <f t="shared" si="154"/>
-        <v>-4.9165665847206406E-2</v>
+        <f t="shared" si="150"/>
+        <v>3.3498581531730175E-3</v>
       </c>
       <c r="AT20" s="11">
-        <f t="shared" si="154"/>
-        <v>-2.6261144819563671E-2</v>
+        <f t="shared" si="150"/>
+        <v>3.274605403305219E-2</v>
       </c>
       <c r="AU20" s="11">
-        <f t="shared" si="154"/>
-        <v>-6.2611448195637551E-3</v>
+        <f t="shared" si="150"/>
+        <v>5.7352926770274426E-2</v>
       </c>
       <c r="AV20" s="11">
-        <f t="shared" si="154"/>
-        <v>1.5832611455649976E-2</v>
+        <f t="shared" si="150"/>
+        <v>7.9633780429389373E-2</v>
       </c>
       <c r="AW20" s="11">
-        <f t="shared" si="154"/>
-        <v>2.8716605460986703E-2</v>
+        <f t="shared" si="150"/>
+        <v>9.1892272778120912E-2</v>
       </c>
       <c r="AX20" s="11">
-        <f t="shared" ref="AX20:BB20" si="155">AX10/AX3</f>
-        <v>2.8716605460986745E-2</v>
+        <f t="shared" ref="AX20:BB20" si="151">AX10/AX3</f>
+        <v>9.4128623045001983E-2</v>
       </c>
       <c r="AY20" s="11">
-        <f t="shared" si="155"/>
-        <v>2.8716605460986842E-2</v>
+        <f t="shared" si="151"/>
+        <v>9.6343048309266655E-2</v>
       </c>
       <c r="AZ20" s="11">
-        <f t="shared" si="155"/>
-        <v>2.8716605460986765E-2</v>
+        <f t="shared" si="151"/>
+        <v>9.8535763521920963E-2</v>
       </c>
       <c r="BA20" s="11">
-        <f t="shared" si="155"/>
-        <v>2.8716605460986793E-2</v>
+        <f t="shared" si="151"/>
+        <v>0.10070698152660791</v>
       </c>
       <c r="BB20" s="11">
-        <f t="shared" si="155"/>
-        <v>2.8716605460986738E-2</v>
+        <f t="shared" si="151"/>
+        <v>0.10285691308026872</v>
       </c>
       <c r="BD20" t="s">
         <v>40</v>
@@ -4857,185 +4885,185 @@
       <c r="E21" s="11"/>
       <c r="F21" s="11"/>
       <c r="G21" s="11">
-        <f t="shared" ref="G21:R21" si="156">G6/C6-1</f>
+        <f t="shared" ref="G21:R21" si="152">G6/C6-1</f>
         <v>0.10746268656716418</v>
       </c>
       <c r="H21" s="11">
-        <f t="shared" si="156"/>
+        <f t="shared" si="152"/>
         <v>0.13920454545454541</v>
       </c>
       <c r="I21" s="11">
-        <f t="shared" si="156"/>
+        <f t="shared" si="152"/>
         <v>0.25423728813559321</v>
       </c>
       <c r="J21" s="11">
-        <f t="shared" si="156"/>
+        <f t="shared" si="152"/>
         <v>0.30870712401055411</v>
       </c>
       <c r="K21" s="11">
-        <f t="shared" si="156"/>
+        <f t="shared" si="152"/>
         <v>0.41509433962264142</v>
       </c>
       <c r="L21" s="11">
-        <f t="shared" si="156"/>
+        <f t="shared" si="152"/>
         <v>0.23690773067331672</v>
       </c>
       <c r="M21" s="11">
-        <f t="shared" si="156"/>
+        <f t="shared" si="152"/>
         <v>0.30180180180180183</v>
       </c>
       <c r="N21" s="11">
-        <f t="shared" si="156"/>
+        <f t="shared" si="152"/>
         <v>0.10483870967741926</v>
       </c>
       <c r="O21" s="11">
-        <f t="shared" si="156"/>
+        <f t="shared" si="152"/>
         <v>-3.8095238095238182E-3</v>
       </c>
       <c r="P21" s="11">
-        <f t="shared" si="156"/>
+        <f t="shared" si="152"/>
         <v>0.13709677419354827</v>
       </c>
       <c r="Q21" s="11">
-        <f t="shared" si="156"/>
+        <f t="shared" si="152"/>
         <v>-3.8062283737024138E-2</v>
       </c>
       <c r="R21" s="11">
-        <f t="shared" si="156"/>
+        <f t="shared" si="152"/>
         <v>0.2007299270072993</v>
       </c>
       <c r="S21" s="11">
-        <f t="shared" ref="S21" si="157">S6/O6-1</f>
+        <f t="shared" ref="S21" si="153">S6/O6-1</f>
         <v>0.17208413001912048</v>
       </c>
       <c r="T21" s="11">
-        <f t="shared" ref="T21" si="158">T6/P6-1</f>
+        <f t="shared" ref="T21" si="154">T6/P6-1</f>
         <v>0.15070921985815611</v>
       </c>
       <c r="U21" s="11">
-        <f t="shared" ref="U21" si="159">U6/Q6-1</f>
+        <f t="shared" ref="U21" si="155">U6/Q6-1</f>
         <v>0.12410071942446033</v>
       </c>
       <c r="V21" s="11">
-        <f t="shared" ref="V21" si="160">V6/R6-1</f>
+        <f t="shared" ref="V21" si="156">V6/R6-1</f>
         <v>2.2796352583586588E-2</v>
       </c>
       <c r="W21" s="11">
-        <f t="shared" ref="W21" si="161">W6/S6-1</f>
+        <f t="shared" ref="W21" si="157">W6/S6-1</f>
         <v>0.25448613376835261</v>
       </c>
       <c r="X21" s="11">
-        <f t="shared" ref="X21" si="162">X6/T6-1</f>
+        <f t="shared" ref="X21" si="158">X6/T6-1</f>
         <v>0.24499229583975324</v>
       </c>
       <c r="Y21" s="11">
-        <f t="shared" ref="Y21" si="163">Y6/U6-1</f>
+        <f t="shared" ref="Y21" si="159">Y6/U6-1</f>
         <v>0.24479999999999991</v>
       </c>
       <c r="Z21" s="11">
-        <f t="shared" ref="Z21" si="164">Z6/V6-1</f>
+        <f t="shared" ref="Z21" si="160">Z6/V6-1</f>
         <v>-2.6745913818722045E-2</v>
       </c>
       <c r="AA21" s="11">
-        <f t="shared" ref="AA21" si="165">AA6/W6-1</f>
+        <f t="shared" ref="AA21" si="161">AA6/W6-1</f>
         <v>2.9908972691807589E-2</v>
       </c>
       <c r="AB21" s="11">
-        <f t="shared" ref="AB21" si="166">AB6/X6-1</f>
+        <f t="shared" ref="AB21" si="162">AB6/X6-1</f>
         <v>-6.1881188118811936E-3</v>
       </c>
       <c r="AC21" s="11">
-        <f t="shared" ref="AC21" si="167">AC6/Y6-1</f>
+        <f t="shared" ref="AC21" si="163">AC6/Y6-1</f>
         <v>-4.6272493573264684E-2</v>
       </c>
       <c r="AD21" s="11">
-        <f t="shared" ref="AD21" si="168">AD6/Z6-1</f>
+        <f t="shared" ref="AD21" si="164">AD6/Z6-1</f>
         <v>8.0916030534351036E-2</v>
       </c>
       <c r="AE21" s="11">
-        <f t="shared" ref="AE21" si="169">AE6/AA6-1</f>
+        <f t="shared" ref="AE21" si="165">AE6/AA6-1</f>
         <v>2.020202020202011E-2</v>
       </c>
       <c r="AF21" s="11">
-        <f t="shared" ref="AF21" si="170">AF6/AB6-1</f>
-        <v>3.0000000000000027E-2</v>
+        <f t="shared" ref="AF21" si="166">AF6/AB6-1</f>
+        <v>-3.6114570361145626E-2</v>
       </c>
       <c r="AG21" s="11">
-        <f t="shared" ref="AG21" si="171">AG6/AC6-1</f>
-        <v>3.0000000000000027E-2</v>
+        <f t="shared" ref="AG21" si="167">AG6/AC6-1</f>
+        <v>-0.19407008086253374</v>
       </c>
       <c r="AH21" s="11">
-        <f t="shared" ref="AH21" si="172">AH6/AD6-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="AH21" si="168">AH6/AD6-1</f>
+        <v>-8.1920903954802227E-2</v>
       </c>
       <c r="AI21" s="11"/>
       <c r="AK21" s="11"/>
       <c r="AL21" s="11">
-        <f t="shared" ref="AL21:AW21" si="173">AL6/AK6-1</f>
+        <f t="shared" ref="AL21:AW21" si="169">AL6/AK6-1</f>
         <v>0.20563380281690136</v>
       </c>
       <c r="AM21" s="11">
-        <f t="shared" si="173"/>
+        <f t="shared" si="169"/>
         <v>0.25408878504672905</v>
       </c>
       <c r="AN21" s="11">
-        <f t="shared" si="173"/>
+        <f t="shared" si="169"/>
         <v>7.1727992547740982E-2</v>
       </c>
       <c r="AO21" s="11">
-        <f t="shared" si="173"/>
+        <f t="shared" si="169"/>
         <v>0.11255975662755335</v>
       </c>
       <c r="AP21" s="11">
-        <f t="shared" si="173"/>
+        <f t="shared" si="169"/>
         <v>0.17578125</v>
       </c>
       <c r="AQ21" s="11">
-        <f t="shared" si="173"/>
+        <f t="shared" si="169"/>
         <v>1.1627906976744207E-2</v>
       </c>
       <c r="AR21" s="11">
-        <f t="shared" si="173"/>
-        <v>2.2801313628899811E-2</v>
+        <f t="shared" si="169"/>
+        <v>-7.0607553366174081E-2</v>
       </c>
       <c r="AS21" s="11">
-        <f t="shared" si="173"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="169"/>
+        <v>-9.9999999999999978E-2</v>
       </c>
       <c r="AT21" s="11">
-        <f t="shared" si="173"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="169"/>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="AU21" s="11">
-        <f t="shared" si="173"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="169"/>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="AV21" s="11">
-        <f t="shared" si="173"/>
+        <f t="shared" si="169"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AW21" s="11">
-        <f t="shared" si="173"/>
+        <f t="shared" si="169"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AX21" s="11">
-        <f t="shared" ref="AX21" si="174">AX6/AW6-1</f>
+        <f t="shared" ref="AX21" si="170">AX6/AW6-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AY21" s="11">
-        <f t="shared" ref="AY21" si="175">AY6/AX6-1</f>
+        <f t="shared" ref="AY21" si="171">AY6/AX6-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AZ21" s="11">
-        <f t="shared" ref="AZ21" si="176">AZ6/AY6-1</f>
+        <f t="shared" ref="AZ21" si="172">AZ6/AY6-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BA21" s="11">
-        <f t="shared" ref="BA21" si="177">BA6/AZ6-1</f>
+        <f t="shared" ref="BA21" si="173">BA6/AZ6-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BB21" s="11">
-        <f t="shared" ref="BB21" si="178">BB6/BA6-1</f>
+        <f t="shared" ref="BB21" si="174">BB6/BA6-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BD21" t="s">
@@ -5054,208 +5082,208 @@
         <v>0.20042643923240938</v>
       </c>
       <c r="D22" s="11">
-        <f t="shared" ref="D22:N22" si="179">D7/D3</f>
+        <f t="shared" ref="D22:N22" si="175">D7/D3</f>
         <v>0.31708623460096413</v>
       </c>
       <c r="E22" s="11">
-        <f t="shared" si="179"/>
+        <f t="shared" si="175"/>
         <v>0.29174664107485604</v>
       </c>
       <c r="F22" s="11">
-        <f t="shared" si="179"/>
+        <f t="shared" si="175"/>
         <v>0.20813484792964457</v>
       </c>
       <c r="G22" s="11">
-        <f t="shared" si="179"/>
+        <f t="shared" si="175"/>
         <v>0.13275584206285257</v>
       </c>
       <c r="H22" s="11">
-        <f t="shared" si="179"/>
+        <f t="shared" si="175"/>
         <v>0.23501427212178877</v>
       </c>
       <c r="I22" s="11">
-        <f t="shared" si="179"/>
+        <f t="shared" si="175"/>
         <v>0.23644752018454437</v>
       </c>
       <c r="J22" s="11">
-        <f t="shared" si="179"/>
+        <f t="shared" si="175"/>
         <v>0.24099252209381375</v>
       </c>
       <c r="K22" s="11">
-        <f t="shared" si="179"/>
+        <f t="shared" si="175"/>
         <v>0.13769791851983634</v>
       </c>
       <c r="L22" s="11">
-        <f t="shared" si="179"/>
+        <f t="shared" si="175"/>
         <v>0.28840662478583667</v>
       </c>
       <c r="M22" s="11">
-        <f t="shared" si="179"/>
+        <f t="shared" si="175"/>
         <v>0.31006819093461691</v>
       </c>
       <c r="N22" s="11">
-        <f t="shared" si="179"/>
+        <f t="shared" si="175"/>
         <v>0.17157151265450263</v>
       </c>
       <c r="O22" s="11">
-        <f t="shared" ref="O22:R22" si="180">O7/O3</f>
+        <f t="shared" ref="O22:R22" si="176">O7/O3</f>
         <v>0.11524163568773235</v>
       </c>
       <c r="P22" s="11">
-        <f t="shared" si="180"/>
+        <f t="shared" si="176"/>
         <v>0.17182337038149598</v>
       </c>
       <c r="Q22" s="11">
-        <f t="shared" si="180"/>
+        <f t="shared" si="176"/>
         <v>0.17744916820702406</v>
       </c>
       <c r="R22" s="11">
-        <f t="shared" si="180"/>
+        <f t="shared" si="176"/>
         <v>0.20367278797996663</v>
       </c>
       <c r="S22" s="11">
-        <f t="shared" ref="S22:AH22" si="181">S7/S3</f>
+        <f t="shared" ref="S22:AH22" si="177">S7/S3</f>
         <v>0.12595936794582394</v>
       </c>
       <c r="T22" s="11">
-        <f t="shared" si="181"/>
+        <f t="shared" si="177"/>
         <v>0.15007503751875936</v>
       </c>
       <c r="U22" s="11">
-        <f t="shared" si="181"/>
+        <f t="shared" si="177"/>
         <v>0.17213555675094136</v>
       </c>
       <c r="V22" s="11">
-        <f t="shared" si="181"/>
+        <f t="shared" si="177"/>
         <v>0.22952892823269047</v>
       </c>
       <c r="W22" s="11">
-        <f t="shared" si="181"/>
+        <f t="shared" si="177"/>
         <v>0.11700862325304788</v>
       </c>
       <c r="X22" s="11">
-        <f t="shared" si="181"/>
+        <f t="shared" si="177"/>
         <v>0.20907297830374755</v>
       </c>
       <c r="Y22" s="11">
-        <f t="shared" si="181"/>
+        <f t="shared" si="177"/>
         <v>0.1783610069630423</v>
       </c>
       <c r="Z22" s="11">
-        <f t="shared" si="181"/>
+        <f t="shared" si="177"/>
         <v>0.19206817436905932</v>
       </c>
       <c r="AA22" s="11">
-        <f t="shared" si="181"/>
+        <f t="shared" si="177"/>
         <v>0.13705335291238374</v>
       </c>
       <c r="AB22" s="11">
-        <f t="shared" si="181"/>
+        <f t="shared" si="177"/>
         <v>0.24455876533438861</v>
       </c>
       <c r="AC22" s="11">
-        <f t="shared" si="181"/>
+        <f t="shared" si="177"/>
         <v>0.18030722739864011</v>
       </c>
       <c r="AD22" s="11">
-        <f t="shared" si="181"/>
+        <f t="shared" si="177"/>
         <v>0.28660924040720437</v>
       </c>
       <c r="AE22" s="11">
-        <f t="shared" si="181"/>
+        <f t="shared" si="177"/>
         <v>0.15719731348702123</v>
       </c>
       <c r="AF22" s="11">
-        <f t="shared" si="181"/>
-        <v>0.26</v>
+        <f t="shared" si="177"/>
+        <v>0.24711316397228639</v>
       </c>
       <c r="AG22" s="11">
-        <f t="shared" si="181"/>
-        <v>0.19</v>
+        <f t="shared" si="177"/>
+        <v>0.18155452436194897</v>
       </c>
       <c r="AH22" s="11">
-        <f t="shared" si="181"/>
+        <f t="shared" si="177"/>
         <v>0.3</v>
       </c>
       <c r="AI22" s="11"/>
       <c r="AK22" s="11">
-        <f t="shared" ref="AK22:AM22" si="182">AK7/AK3</f>
+        <f t="shared" ref="AK22:AM22" si="178">AK7/AK3</f>
         <v>0.23817062445030784</v>
       </c>
       <c r="AL22" s="11">
-        <f t="shared" si="182"/>
+        <f t="shared" si="178"/>
         <v>0.19644698231422003</v>
       </c>
       <c r="AM22" s="11">
-        <f t="shared" si="182"/>
+        <f t="shared" si="178"/>
         <v>0.19867300007539773</v>
       </c>
       <c r="AN22" s="11">
-        <f t="shared" ref="AN22:AW22" si="183">AN7/AN3</f>
+        <f t="shared" ref="AN22:AW22" si="179">AN7/AN3</f>
         <v>0.15845275544681348</v>
       </c>
       <c r="AO22" s="11">
-        <f t="shared" si="183"/>
+        <f t="shared" si="179"/>
         <v>0.15995206573841586</v>
       </c>
       <c r="AP22" s="11">
-        <f t="shared" si="183"/>
+        <f t="shared" si="179"/>
         <v>0.16160212650274877</v>
       </c>
       <c r="AQ22" s="11">
-        <f t="shared" si="183"/>
+        <f t="shared" si="179"/>
         <v>0.19142348988867666</v>
       </c>
       <c r="AR22" s="11">
-        <f t="shared" si="183"/>
-        <v>0.20812166672131543</v>
+        <f t="shared" si="179"/>
+        <v>0.20606684797703592</v>
       </c>
       <c r="AS22" s="11">
-        <f t="shared" si="183"/>
+        <f t="shared" si="179"/>
         <v>0.19999999999999998</v>
       </c>
       <c r="AT22" s="11">
-        <f t="shared" si="183"/>
-        <v>0.18999999999999997</v>
+        <f t="shared" si="179"/>
+        <v>0.19</v>
       </c>
       <c r="AU22" s="11">
-        <f t="shared" si="183"/>
-        <v>0.18000000000000002</v>
+        <f t="shared" si="179"/>
+        <v>0.18</v>
       </c>
       <c r="AV22" s="11">
-        <f t="shared" si="183"/>
+        <f t="shared" si="179"/>
         <v>0.17</v>
       </c>
       <c r="AW22" s="11">
-        <f t="shared" si="183"/>
+        <f t="shared" si="179"/>
         <v>0.16</v>
       </c>
       <c r="AX22" s="11">
-        <f t="shared" ref="AX22:BB22" si="184">AX7/AX3</f>
+        <f t="shared" ref="AX22:BB22" si="180">AX7/AX3</f>
         <v>0.16</v>
       </c>
       <c r="AY22" s="11">
-        <f t="shared" si="184"/>
-        <v>0.15999999999999998</v>
+        <f t="shared" si="180"/>
+        <v>0.16</v>
       </c>
       <c r="AZ22" s="11">
-        <f t="shared" si="184"/>
+        <f t="shared" si="180"/>
         <v>0.16</v>
       </c>
       <c r="BA22" s="11">
-        <f t="shared" si="184"/>
+        <f t="shared" si="180"/>
         <v>0.16</v>
       </c>
       <c r="BB22" s="11">
-        <f t="shared" si="184"/>
-        <v>0.15999999999999998</v>
+        <f t="shared" si="180"/>
+        <v>0.16</v>
       </c>
       <c r="BD22" t="s">
         <v>42</v>
       </c>
       <c r="BE22" s="4">
-        <f>NPV(BE21,AN14:FT14)</f>
-        <v>219.09939250457418</v>
+        <f>NPV(BE21,AR14:FT14)</f>
+        <v>953.27066289012998</v>
       </c>
     </row>
     <row r="23" spans="2:57" x14ac:dyDescent="0.3">
@@ -5267,185 +5295,185 @@
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
       <c r="G23" s="11">
-        <f t="shared" ref="G23:R23" si="185">G8/C8-1</f>
+        <f t="shared" ref="G23:R23" si="181">G8/C8-1</f>
         <v>6.25E-2</v>
       </c>
       <c r="H23" s="11">
-        <f t="shared" si="185"/>
+        <f t="shared" si="181"/>
         <v>0.16019417475728148</v>
       </c>
       <c r="I23" s="11">
-        <f t="shared" si="185"/>
+        <f t="shared" si="181"/>
         <v>0.27272727272727293</v>
       </c>
       <c r="J23" s="11">
-        <f t="shared" si="185"/>
+        <f t="shared" si="181"/>
         <v>0.33644859813084138</v>
       </c>
       <c r="K23" s="11">
-        <f t="shared" si="185"/>
+        <f t="shared" si="181"/>
         <v>0.26890756302521002</v>
       </c>
       <c r="L23" s="11">
-        <f t="shared" si="185"/>
+        <f t="shared" si="181"/>
         <v>9.205020920502105E-2</v>
       </c>
       <c r="M23" s="11">
-        <f t="shared" si="185"/>
+        <f t="shared" si="181"/>
         <v>0.19172932330827064</v>
       </c>
       <c r="N23" s="11">
-        <f t="shared" si="185"/>
+        <f t="shared" si="181"/>
         <v>0.15384615384615374</v>
       </c>
       <c r="O23" s="11">
-        <f t="shared" si="185"/>
+        <f t="shared" si="181"/>
         <v>0.16556291390728495</v>
       </c>
       <c r="P23" s="11">
-        <f t="shared" si="185"/>
+        <f t="shared" si="181"/>
         <v>0.52490421455938674</v>
       </c>
       <c r="Q23" s="11">
-        <f t="shared" si="185"/>
+        <f t="shared" si="181"/>
         <v>0.20820189274447953</v>
       </c>
       <c r="R23" s="11">
-        <f t="shared" si="185"/>
+        <f t="shared" si="181"/>
         <v>0.19696969696969702</v>
       </c>
       <c r="S23" s="11">
-        <f t="shared" ref="S23" si="186">S8/O8-1</f>
+        <f t="shared" ref="S23" si="182">S8/O8-1</f>
         <v>0.12784090909090917</v>
       </c>
       <c r="T23" s="11">
-        <f t="shared" ref="T23" si="187">T8/P8-1</f>
+        <f t="shared" ref="T23" si="183">T8/P8-1</f>
         <v>0.1080402010050252</v>
       </c>
       <c r="U23" s="11">
-        <f t="shared" ref="U23" si="188">U8/Q8-1</f>
+        <f t="shared" ref="U23" si="184">U8/Q8-1</f>
         <v>0.10704960835509136</v>
       </c>
       <c r="V23" s="11">
-        <f t="shared" ref="V23" si="189">V8/R8-1</f>
+        <f t="shared" ref="V23" si="185">V8/R8-1</f>
         <v>0.11898734177215187</v>
       </c>
       <c r="W23" s="11">
-        <f t="shared" ref="W23" si="190">W8/S8-1</f>
+        <f t="shared" ref="W23" si="186">W8/S8-1</f>
         <v>8.5642317380352662E-2</v>
       </c>
       <c r="X23" s="11">
-        <f t="shared" ref="X23" si="191">X8/T8-1</f>
+        <f t="shared" ref="X23" si="187">X8/T8-1</f>
         <v>6.8027210884353817E-3</v>
       </c>
       <c r="Y23" s="11">
-        <f t="shared" ref="Y23" si="192">Y8/U8-1</f>
+        <f t="shared" ref="Y23" si="188">Y8/U8-1</f>
         <v>0.14858490566037741</v>
       </c>
       <c r="Z23" s="11">
-        <f t="shared" ref="Z23" si="193">Z8/V8-1</f>
+        <f t="shared" ref="Z23" si="189">Z8/V8-1</f>
         <v>-0.26923076923076938</v>
       </c>
       <c r="AA23" s="11">
-        <f t="shared" ref="AA23" si="194">AA8/W8-1</f>
+        <f t="shared" ref="AA23" si="190">AA8/W8-1</f>
         <v>-7.6566125290023268E-2</v>
       </c>
       <c r="AB23" s="11">
-        <f t="shared" ref="AB23" si="195">AB8/X8-1</f>
+        <f t="shared" ref="AB23" si="191">AB8/X8-1</f>
         <v>-8.1081081081081141E-2</v>
       </c>
       <c r="AC23" s="11">
-        <f t="shared" ref="AC23" si="196">AC8/Y8-1</f>
+        <f t="shared" ref="AC23" si="192">AC8/Y8-1</f>
         <v>-0.31827515400410678</v>
       </c>
       <c r="AD23" s="11">
-        <f t="shared" ref="AD23" si="197">AD8/Z8-1</f>
+        <f t="shared" ref="AD23" si="193">AD8/Z8-1</f>
         <v>-0.12074303405572751</v>
       </c>
       <c r="AE23" s="11">
-        <f t="shared" ref="AE23" si="198">AE8/AA8-1</f>
+        <f t="shared" ref="AE23" si="194">AE8/AA8-1</f>
         <v>-0.35175879396984921</v>
       </c>
       <c r="AF23" s="11">
-        <f t="shared" ref="AF23" si="199">AF8/AB8-1</f>
-        <v>-0.25</v>
+        <f t="shared" ref="AF23" si="195">AF8/AB8-1</f>
+        <v>-0.18627450980392146</v>
       </c>
       <c r="AG23" s="11">
-        <f t="shared" ref="AG23" si="200">AG8/AC8-1</f>
-        <v>-5.0000000000000044E-2</v>
+        <f t="shared" ref="AG23" si="196">AG8/AC8-1</f>
+        <v>-8.7349397590361533E-2</v>
       </c>
       <c r="AH23" s="11">
-        <f t="shared" ref="AH23" si="201">AH8/AD8-1</f>
+        <f t="shared" ref="AH23" si="197">AH8/AD8-1</f>
         <v>0.14999999999999991</v>
       </c>
       <c r="AI23" s="11"/>
       <c r="AK23" s="11"/>
       <c r="AL23" s="11">
-        <f t="shared" ref="AL23:AW23" si="202">AL8/AK8-1</f>
+        <f t="shared" ref="AL23:AW23" si="198">AL8/AK8-1</f>
         <v>0.2063305978898009</v>
       </c>
       <c r="AM23" s="11">
-        <f t="shared" si="202"/>
+        <f t="shared" si="198"/>
         <v>0.17589893100097176</v>
       </c>
       <c r="AN23" s="11">
-        <f t="shared" si="202"/>
+        <f t="shared" si="198"/>
         <v>0.26280991735537196</v>
       </c>
       <c r="AO23" s="11">
-        <f t="shared" si="202"/>
+        <f t="shared" si="198"/>
         <v>0.11518324607329866</v>
       </c>
       <c r="AP23" s="11">
-        <f t="shared" si="202"/>
+        <f t="shared" si="198"/>
         <v>-1.1150234741784226E-2</v>
       </c>
       <c r="AQ23" s="11">
-        <f t="shared" si="202"/>
+        <f t="shared" si="198"/>
         <v>-0.15608308605341248</v>
       </c>
       <c r="AR23" s="11">
-        <f t="shared" si="202"/>
-        <v>-0.15189873417721511</v>
+        <f t="shared" si="198"/>
+        <v>-0.14233473980309419</v>
       </c>
       <c r="AS23" s="11">
-        <f t="shared" si="202"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="198"/>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="AT23" s="11">
-        <f t="shared" si="202"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="198"/>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="AU23" s="11">
-        <f t="shared" si="202"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="198"/>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="AV23" s="11">
-        <f t="shared" si="202"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="198"/>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="AW23" s="11">
-        <f t="shared" si="202"/>
+        <f t="shared" si="198"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AX23" s="11">
-        <f t="shared" ref="AX23" si="203">AX8/AW8-1</f>
+        <f t="shared" ref="AX23" si="199">AX8/AW8-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AY23" s="11">
-        <f t="shared" ref="AY23" si="204">AY8/AX8-1</f>
+        <f t="shared" ref="AY23" si="200">AY8/AX8-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AZ23" s="11">
-        <f t="shared" ref="AZ23" si="205">AZ8/AY8-1</f>
+        <f t="shared" ref="AZ23" si="201">AZ8/AY8-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BA23" s="11">
-        <f t="shared" ref="BA23" si="206">BA8/AZ8-1</f>
+        <f t="shared" ref="BA23" si="202">BA8/AZ8-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BB23" s="11">
-        <f t="shared" ref="BB23" si="207">BB8/BA8-1</f>
+        <f t="shared" ref="BB23" si="203">BB8/BA8-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BD23" t="s">
@@ -5453,7 +5481,7 @@
       </c>
       <c r="BE23" s="4">
         <f>Main!D8</f>
-        <v>327.9</v>
+        <v>254</v>
       </c>
     </row>
     <row r="24" spans="2:57" x14ac:dyDescent="0.3">
@@ -5465,200 +5493,200 @@
         <v>0</v>
       </c>
       <c r="D24" s="11">
-        <f t="shared" ref="D24:N24" si="208">D13/D12</f>
+        <f t="shared" ref="D24:N24" si="204">D13/D12</f>
         <v>-1.8749999999999992E-2</v>
       </c>
       <c r="E24" s="11">
-        <f t="shared" si="208"/>
+        <f t="shared" si="204"/>
         <v>-1.8867924528301893E-2</v>
       </c>
       <c r="F24" s="11">
-        <f t="shared" si="208"/>
+        <f t="shared" si="204"/>
         <v>5.2631578947368265E-2</v>
       </c>
       <c r="G24" s="11">
-        <f t="shared" si="208"/>
+        <f t="shared" si="204"/>
         <v>3.9001560062402525E-2</v>
       </c>
       <c r="H24" s="11">
-        <f t="shared" si="208"/>
+        <f t="shared" si="204"/>
         <v>8.6580086580086528E-3</v>
       </c>
       <c r="I24" s="11">
-        <f t="shared" si="208"/>
+        <f t="shared" si="204"/>
         <v>-6.0150375939849683E-2</v>
       </c>
       <c r="J24" s="11">
-        <f t="shared" si="208"/>
+        <f t="shared" si="204"/>
         <v>-2.0689655172413786E-2</v>
       </c>
       <c r="K24" s="11">
-        <f t="shared" si="208"/>
+        <f t="shared" si="204"/>
         <v>2.3448275862068955E-2</v>
       </c>
       <c r="L24" s="11">
-        <f t="shared" si="208"/>
+        <f t="shared" si="204"/>
         <v>3.3271719038817017E-2</v>
       </c>
       <c r="M24" s="11">
-        <f t="shared" si="208"/>
+        <f t="shared" si="204"/>
         <v>-3.5149384885764519E-3</v>
       </c>
       <c r="N24" s="11">
-        <f t="shared" si="208"/>
+        <f t="shared" si="204"/>
         <v>0</v>
       </c>
       <c r="O24" s="11">
-        <f t="shared" ref="O24:R24" si="209">O13/O12</f>
+        <f t="shared" ref="O24:R24" si="205">O13/O12</f>
         <v>6.4310954063604223E-2</v>
       </c>
       <c r="P24" s="11">
-        <f t="shared" si="209"/>
+        <f t="shared" si="205"/>
         <v>-0.60747663551401798</v>
       </c>
       <c r="Q24" s="11">
-        <f t="shared" si="209"/>
+        <f t="shared" si="205"/>
         <v>4.7872340425532033E-2</v>
       </c>
       <c r="R24" s="11">
-        <f t="shared" si="209"/>
+        <f t="shared" si="205"/>
         <v>0.36428571428571382</v>
       </c>
       <c r="S24" s="11">
-        <f t="shared" ref="S24:AH24" si="210">S13/S12</f>
+        <f t="shared" ref="S24:AH24" si="206">S13/S12</f>
         <v>5.7926829268292686E-2</v>
       </c>
       <c r="T24" s="11">
-        <f t="shared" si="210"/>
+        <f t="shared" si="206"/>
         <v>-0.10126582278480985</v>
       </c>
       <c r="U24" s="11">
-        <f t="shared" si="210"/>
+        <f t="shared" si="206"/>
         <v>0.80769230769230782</v>
       </c>
       <c r="V24" s="11">
-        <f t="shared" si="210"/>
+        <f t="shared" si="206"/>
         <v>5.1851851851851899E-2</v>
       </c>
       <c r="W24" s="11">
-        <f t="shared" si="210"/>
+        <f t="shared" si="206"/>
         <v>0.32647584973166366</v>
       </c>
       <c r="X24" s="11">
-        <f t="shared" si="210"/>
+        <f t="shared" si="206"/>
         <v>0.46315789473684199</v>
       </c>
       <c r="Y24" s="11">
-        <f t="shared" si="210"/>
+        <f t="shared" si="206"/>
         <v>-0.33146067415730368</v>
       </c>
       <c r="Z24" s="11">
-        <f t="shared" si="210"/>
+        <f t="shared" si="206"/>
         <v>3.9877300613496994E-2</v>
       </c>
       <c r="AA24" s="11">
-        <f t="shared" si="210"/>
+        <f t="shared" si="206"/>
         <v>0.12917115177610336</v>
       </c>
       <c r="AB24" s="11">
-        <f t="shared" si="210"/>
+        <f t="shared" si="206"/>
         <v>9.9573257467994326E-3</v>
       </c>
       <c r="AC24" s="11">
-        <f t="shared" si="210"/>
+        <f t="shared" si="206"/>
         <v>0.70634920634920506</v>
       </c>
       <c r="AD24" s="11">
-        <f t="shared" si="210"/>
+        <f t="shared" si="206"/>
         <v>0.14767255216693417</v>
       </c>
       <c r="AE24" s="11">
-        <f t="shared" si="210"/>
+        <f t="shared" si="206"/>
         <v>-0.1454545454545455</v>
       </c>
       <c r="AF24" s="11">
-        <f t="shared" si="210"/>
-        <v>0.1</v>
+        <f t="shared" si="206"/>
+        <v>-0.18644067796610173</v>
       </c>
       <c r="AG24" s="11">
-        <f t="shared" si="210"/>
-        <v>0.1</v>
+        <f t="shared" si="206"/>
+        <v>-3.2499999999999774</v>
       </c>
       <c r="AH24" s="11">
-        <f t="shared" si="210"/>
+        <f t="shared" si="206"/>
         <v>0.1</v>
       </c>
       <c r="AI24" s="11"/>
       <c r="AK24" s="11">
-        <f t="shared" ref="AK24:AM24" si="211">AK13/AK12</f>
+        <f t="shared" ref="AK24:AM24" si="207">AK13/AK12</f>
         <v>-6.8493150684931614E-2</v>
       </c>
       <c r="AL24" s="11">
-        <f t="shared" si="211"/>
+        <f t="shared" si="207"/>
         <v>-2.8461538461535953</v>
       </c>
       <c r="AM24" s="11">
-        <f t="shared" si="211"/>
+        <f t="shared" si="207"/>
         <v>-4.9751243781094041E-3</v>
       </c>
       <c r="AN24" s="11">
-        <f t="shared" ref="AN24:AW24" si="212">AN13/AN12</f>
+        <f t="shared" ref="AN24:AW24" si="208">AN13/AN12</f>
         <v>-1.0191082802547781E-2</v>
       </c>
       <c r="AO24" s="11">
-        <f t="shared" si="212"/>
+        <f t="shared" si="208"/>
         <v>1.7391304347826087E-2</v>
       </c>
       <c r="AP24" s="11">
-        <f t="shared" si="212"/>
+        <f t="shared" si="208"/>
         <v>3.3409090909093506</v>
       </c>
       <c r="AQ24" s="11">
-        <f t="shared" si="212"/>
+        <f t="shared" si="208"/>
         <v>-0.40590405904059085</v>
       </c>
       <c r="AR24" s="11">
-        <f t="shared" si="212"/>
-        <v>0.19452417101208</v>
+        <f t="shared" si="208"/>
+        <v>-7.4144787720100845E-4</v>
       </c>
       <c r="AS24" s="11">
-        <f t="shared" si="212"/>
+        <f t="shared" si="208"/>
         <v>0.2</v>
       </c>
       <c r="AT24" s="11">
-        <f t="shared" si="212"/>
+        <f t="shared" si="208"/>
+        <v>0.20000000000000004</v>
+      </c>
+      <c r="AU24" s="11">
+        <f t="shared" si="208"/>
         <v>0.2</v>
       </c>
-      <c r="AU24" s="11">
-        <f t="shared" si="212"/>
+      <c r="AV24" s="11">
+        <f t="shared" si="208"/>
         <v>0.2</v>
       </c>
-      <c r="AV24" s="11">
-        <f t="shared" si="212"/>
+      <c r="AW24" s="11">
+        <f t="shared" si="208"/>
         <v>0.2</v>
       </c>
-      <c r="AW24" s="11">
-        <f t="shared" si="212"/>
+      <c r="AX24" s="11">
+        <f t="shared" ref="AX24:BB24" si="209">AX13/AX12</f>
+        <v>0.2</v>
+      </c>
+      <c r="AY24" s="11">
+        <f t="shared" si="209"/>
+        <v>0.2</v>
+      </c>
+      <c r="AZ24" s="11">
+        <f t="shared" si="209"/>
         <v>0.19999999999999998</v>
       </c>
-      <c r="AX24" s="11">
-        <f t="shared" ref="AX24:BB24" si="213">AX13/AX12</f>
+      <c r="BA24" s="11">
+        <f t="shared" si="209"/>
         <v>0.2</v>
       </c>
-      <c r="AY24" s="11">
-        <f t="shared" si="213"/>
-        <v>0.19999999999999998</v>
-      </c>
-      <c r="AZ24" s="11">
-        <f t="shared" si="213"/>
-        <v>0.2</v>
-      </c>
-      <c r="BA24" s="11">
-        <f t="shared" si="213"/>
-        <v>0.2</v>
-      </c>
       <c r="BB24" s="11">
-        <f t="shared" si="213"/>
+        <f t="shared" si="209"/>
         <v>0.2</v>
       </c>
       <c r="BD24" t="s">
@@ -5666,7 +5694,7 @@
       </c>
       <c r="BE24" s="4">
         <f>BE22+BE23</f>
-        <v>546.99939250457419</v>
+        <v>1207.2706628901301</v>
       </c>
     </row>
     <row r="25" spans="2:57" x14ac:dyDescent="0.3">
@@ -5678,208 +5706,208 @@
         <v>9.7654584221748358E-2</v>
       </c>
       <c r="D25" s="11">
-        <f t="shared" ref="D25:AW25" si="214">D14/D3</f>
+        <f t="shared" ref="D25:AW25" si="210">D14/D3</f>
         <v>-0.17461167648634182</v>
       </c>
       <c r="E25" s="11">
-        <f t="shared" si="214"/>
+        <f t="shared" si="210"/>
         <v>-0.12955854126679459</v>
       </c>
       <c r="F25" s="11">
-        <f t="shared" si="214"/>
+        <f t="shared" si="210"/>
         <v>-6.5958226456577715E-3</v>
       </c>
       <c r="G25" s="11">
-        <f t="shared" si="214"/>
+        <f t="shared" si="210"/>
         <v>0.12409347300564053</v>
       </c>
       <c r="H25" s="11">
-        <f t="shared" si="214"/>
+        <f t="shared" si="210"/>
         <v>-0.10894386298763091</v>
       </c>
       <c r="I25" s="11">
-        <f t="shared" si="214"/>
+        <f t="shared" si="210"/>
         <v>-5.420991926182233E-2</v>
       </c>
       <c r="J25" s="11">
-        <f t="shared" si="214"/>
+        <f t="shared" si="210"/>
         <v>-0.10061182868796742</v>
       </c>
       <c r="K25" s="11">
-        <f t="shared" si="214"/>
+        <f t="shared" si="210"/>
         <v>0.12595623554527668</v>
       </c>
       <c r="L25" s="11">
-        <f t="shared" si="214"/>
+        <f t="shared" si="210"/>
         <v>-0.29868646487721295</v>
       </c>
       <c r="M25" s="11">
-        <f t="shared" si="214"/>
+        <f t="shared" si="210"/>
         <v>-0.22904131568391484</v>
       </c>
       <c r="N25" s="11">
-        <f t="shared" si="214"/>
+        <f t="shared" si="210"/>
         <v>5.4149499705709259E-2</v>
       </c>
       <c r="O25" s="11">
-        <f t="shared" si="214"/>
+        <f t="shared" si="210"/>
         <v>0.20508054522924415</v>
       </c>
       <c r="P25" s="11">
-        <f t="shared" si="214"/>
+        <f t="shared" si="210"/>
         <v>5.1667167317512801E-2</v>
       </c>
       <c r="Q25" s="11">
-        <f t="shared" si="214"/>
+        <f t="shared" si="210"/>
         <v>4.7266965936097062E-2</v>
       </c>
       <c r="R25" s="11">
-        <f t="shared" si="214"/>
+        <f t="shared" si="210"/>
         <v>-2.4763494713411292E-2</v>
       </c>
       <c r="S25" s="11">
-        <f t="shared" ref="S25:AH25" si="215">S14/S3</f>
+        <f t="shared" ref="S25:AH25" si="211">S14/S3</f>
         <v>0.18600451467268622</v>
       </c>
       <c r="T25" s="11">
-        <f t="shared" si="215"/>
+        <f t="shared" si="211"/>
         <v>2.1760880440220166E-2</v>
       </c>
       <c r="U25" s="11">
-        <f t="shared" si="215"/>
+        <f t="shared" si="211"/>
         <v>-1.3448090371167283E-3</v>
       </c>
       <c r="V25" s="11">
-        <f t="shared" si="215"/>
+        <f t="shared" si="211"/>
         <v>-0.20233955105912091</v>
       </c>
       <c r="W25" s="11">
-        <f t="shared" si="215"/>
+        <f t="shared" si="211"/>
         <v>0.11195361284567353</v>
       </c>
       <c r="X25" s="11">
-        <f t="shared" si="215"/>
+        <f t="shared" si="211"/>
         <v>-0.10059171597633142</v>
       </c>
       <c r="Y25" s="11">
-        <f t="shared" si="215"/>
+        <f t="shared" si="211"/>
         <v>-6.3470808784145641E-2</v>
       </c>
       <c r="Z25" s="11">
-        <f t="shared" si="215"/>
+        <f t="shared" si="211"/>
         <v>-0.10258931497869535</v>
       </c>
       <c r="AA25" s="11">
-        <f t="shared" si="215"/>
+        <f t="shared" si="211"/>
         <v>0.1319954315549029</v>
       </c>
       <c r="AB25" s="11">
-        <f t="shared" si="215"/>
+        <f t="shared" si="211"/>
         <v>-0.27542540561931139</v>
       </c>
       <c r="AC25" s="11">
-        <f t="shared" si="215"/>
+        <f t="shared" si="211"/>
         <v>9.3175522538403981E-3</v>
       </c>
       <c r="AD25" s="11">
-        <f t="shared" si="215"/>
+        <f t="shared" si="211"/>
         <v>-0.20790916209866878</v>
       </c>
       <c r="AE25" s="11">
-        <f t="shared" si="215"/>
+        <f t="shared" si="211"/>
         <v>9.1486658195679776E-2</v>
       </c>
       <c r="AF25" s="11">
-        <f t="shared" si="215"/>
-        <v>-0.26279370170578803</v>
+        <f t="shared" si="211"/>
+        <v>-0.26943802925327176</v>
       </c>
       <c r="AG25" s="11">
-        <f t="shared" si="215"/>
-        <v>-2.0115653000381713E-2</v>
+        <f t="shared" si="211"/>
+        <v>-9.8607888631090657E-3</v>
       </c>
       <c r="AH25" s="11">
-        <f t="shared" si="215"/>
-        <v>-0.29639574661006468</v>
+        <f t="shared" si="211"/>
+        <v>-0.24411895294645361</v>
       </c>
       <c r="AI25" s="11"/>
       <c r="AK25" s="11">
-        <f t="shared" si="214"/>
+        <f t="shared" si="210"/>
         <v>-1.3720316622691272E-2</v>
       </c>
       <c r="AL25" s="11">
-        <f t="shared" si="214"/>
+        <f t="shared" si="210"/>
         <v>-3.9654215243081249E-3</v>
       </c>
       <c r="AM25" s="11">
-        <f t="shared" si="214"/>
+        <f t="shared" si="210"/>
         <v>-1.5230340043730818E-2</v>
       </c>
       <c r="AN25" s="11">
-        <f t="shared" si="214"/>
+        <f t="shared" si="210"/>
         <v>9.2391937550972775E-2</v>
       </c>
       <c r="AO25" s="11">
-        <f t="shared" si="214"/>
+        <f t="shared" si="210"/>
         <v>3.8689796850034215E-2</v>
       </c>
       <c r="AP25" s="11">
-        <f t="shared" si="214"/>
+        <f t="shared" si="210"/>
         <v>-6.222437020479879E-3</v>
       </c>
       <c r="AQ25" s="11">
-        <f t="shared" si="214"/>
+        <f t="shared" si="210"/>
         <v>-2.509716092484025E-2</v>
       </c>
       <c r="AR25" s="11">
-        <f t="shared" si="214"/>
-        <v>-6.5600521919626328E-2</v>
+        <f t="shared" si="210"/>
+        <v>-6.1483685591465359E-2</v>
       </c>
       <c r="AS25" s="11">
-        <f t="shared" si="214"/>
-        <v>-3.9832346178105132E-2</v>
+        <f t="shared" si="210"/>
+        <v>2.2244518144534852E-3</v>
       </c>
       <c r="AT25" s="11">
-        <f t="shared" si="214"/>
-        <v>-2.1318293301694474E-2</v>
+        <f t="shared" si="210"/>
+        <v>2.6213791430742352E-2</v>
       </c>
       <c r="AU25" s="11">
-        <f t="shared" si="214"/>
-        <v>-5.1761181560564511E-3</v>
+        <f t="shared" si="210"/>
+        <v>4.6085943679759288E-2</v>
       </c>
       <c r="AV25" s="11">
-        <f t="shared" si="214"/>
-        <v>1.2625492159374441E-2</v>
+        <f t="shared" si="210"/>
+        <v>6.4068482725313541E-2</v>
       </c>
       <c r="AW25" s="11">
-        <f t="shared" si="214"/>
-        <v>2.3072307836706024E-2</v>
+        <f t="shared" si="210"/>
+        <v>7.4016316126224682E-2</v>
       </c>
       <c r="AX25" s="11">
-        <f t="shared" ref="AX25:BB25" si="216">AX14/AX3</f>
-        <v>2.3156035321951422E-2</v>
+        <f t="shared" ref="AX25:BB25" si="212">AX14/AX3</f>
+        <v>7.5883418562481791E-2</v>
       </c>
       <c r="AY25" s="11">
-        <f t="shared" si="216"/>
-        <v>2.3156698509953444E-2</v>
+        <f t="shared" si="212"/>
+        <v>7.7669602714570046E-2</v>
       </c>
       <c r="AZ25" s="11">
-        <f t="shared" si="216"/>
-        <v>2.3156703762927659E-2</v>
+        <f t="shared" si="212"/>
+        <v>7.9437784172160839E-2</v>
       </c>
       <c r="BA25" s="11">
-        <f t="shared" si="216"/>
-        <v>2.3156703804535397E-2</v>
+        <f t="shared" si="212"/>
+        <v>8.1188626665773866E-2</v>
       </c>
       <c r="BB25" s="11">
-        <f t="shared" si="216"/>
-        <v>2.3156703804864915E-2</v>
+        <f t="shared" si="212"/>
+        <v>8.2922304006691622E-2</v>
       </c>
       <c r="BD25" t="s">
         <v>45</v>
       </c>
       <c r="BE25" s="5">
         <f>BE24/AW15</f>
-        <v>4.5927740764447877</v>
+        <v>10.05221201407269</v>
       </c>
     </row>
     <row r="26" spans="2:57" x14ac:dyDescent="0.3">
@@ -5888,7 +5916,7 @@
       </c>
       <c r="BE26" s="5">
         <f>Main!D3</f>
-        <v>8.9</v>
+        <v>15.22</v>
       </c>
     </row>
     <row r="27" spans="2:57" x14ac:dyDescent="0.3">
@@ -5897,7 +5925,7 @@
       </c>
       <c r="BE27" s="8">
         <f>BE25/BE26-1</f>
-        <v>-0.48395796893878795</v>
+        <v>-0.33953928948274048</v>
       </c>
     </row>
     <row r="28" spans="2:57" x14ac:dyDescent="0.3">

--- a/Financial Analysis/SONO.xlsx
+++ b/Financial Analysis/SONO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFB8AFD7-F0BC-49B9-A8D4-EBC5C27CF584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A01BF07-9EF0-4139-9D7C-E11E85D3D04A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{AE038E36-4BE5-4CF0-B4AF-8B96610ED707}"/>
   </bookViews>
@@ -768,14 +768,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="5">
-        <v>15.22</v>
+        <v>17.809999999999999</v>
       </c>
       <c r="E3" s="3">
-        <v>45918</v>
+        <v>45937</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45918</v>
+        <v>45937</v>
       </c>
       <c r="G3" s="3">
         <v>45973</v>
@@ -799,7 +799,7 @@
       </c>
       <c r="D5" s="4">
         <f>D3*D4</f>
-        <v>1840.0980000000002</v>
+        <v>2153.2289999999998</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -840,7 +840,7 @@
       </c>
       <c r="D9" s="4">
         <f>D5-D8</f>
-        <v>1586.0980000000002</v>
+        <v>1899.2289999999998</v>
       </c>
     </row>
   </sheetData>
@@ -5916,7 +5916,7 @@
       </c>
       <c r="BE26" s="5">
         <f>Main!D3</f>
-        <v>15.22</v>
+        <v>17.809999999999999</v>
       </c>
     </row>
     <row r="27" spans="2:57" x14ac:dyDescent="0.3">
@@ -5925,7 +5925,7 @@
       </c>
       <c r="BE27" s="8">
         <f>BE25/BE26-1</f>
-        <v>-0.33953928948274048</v>
+        <v>-0.4355860744484733</v>
       </c>
     </row>
     <row r="28" spans="2:57" x14ac:dyDescent="0.3">

--- a/Financial Analysis/SONO.xlsx
+++ b/Financial Analysis/SONO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8815E01D-9525-4A21-B78F-F77A2F6BBB60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20BD8729-0AC8-4906-BB6B-687184A2A93B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{AE038E36-4BE5-4CF0-B4AF-8B96610ED707}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{AE038E36-4BE5-4CF0-B4AF-8B96610ED707}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -452,7 +452,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -471,17 +471,13 @@
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -503,14 +499,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>15240</xdr:colOff>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>15240</xdr:colOff>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
       <xdr:row>43</xdr:row>
       <xdr:rowOff>83820</xdr:rowOff>
     </xdr:to>
@@ -527,8 +523,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25008840" y="0"/>
-          <a:ext cx="0" cy="6301740"/>
+          <a:off x="25885140" y="0"/>
+          <a:ext cx="0" cy="7947660"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -926,17 +922,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="5">
-        <v>16.64</v>
+        <v>16.41</v>
       </c>
       <c r="E3" s="3">
-        <v>45967</v>
+        <v>46057</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45967</v>
+        <v>46057</v>
       </c>
       <c r="G3" s="3">
-        <v>46064</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -957,7 +953,7 @@
       </c>
       <c r="D5" s="4">
         <f>D3*D4</f>
-        <v>2006.7839999999999</v>
+        <v>1979.0459999999998</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -965,11 +961,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="4">
-        <f>174.7+52.9</f>
-        <v>227.6</v>
+        <f>312.5+51</f>
+        <v>363.5</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -989,7 +985,7 @@
       </c>
       <c r="D8" s="4">
         <f>D6+D7</f>
-        <v>227.6</v>
+        <v>363.5</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -998,7 +994,7 @@
       </c>
       <c r="D9" s="4">
         <f>D5-D8</f>
-        <v>1779.184</v>
+        <v>1615.5459999999998</v>
       </c>
     </row>
   </sheetData>
@@ -1386,30 +1382,34 @@
       <c r="AA3" s="6"/>
       <c r="AB3" s="6"/>
       <c r="AC3" s="6"/>
-      <c r="AD3" s="17">
+      <c r="AD3" s="15">
         <v>178.2</v>
       </c>
-      <c r="AE3" s="17"/>
+      <c r="AE3" s="15">
+        <v>467.1</v>
+      </c>
       <c r="AF3" s="6"/>
       <c r="AG3" s="6"/>
-      <c r="AH3" s="17">
+      <c r="AH3" s="15">
         <v>206.5</v>
       </c>
-      <c r="AI3" s="17"/>
+      <c r="AI3" s="15">
+        <v>459.2</v>
+      </c>
       <c r="AJ3" s="6"/>
       <c r="AK3" s="6"/>
       <c r="AL3" s="6"/>
       <c r="AM3" s="6"/>
-      <c r="AS3" s="17">
+      <c r="AS3" s="15">
         <v>1368.9</v>
       </c>
-      <c r="AT3" s="17">
+      <c r="AT3" s="15">
         <v>1293.4000000000001</v>
       </c>
-      <c r="AU3" s="17">
+      <c r="AU3" s="15">
         <v>1169.5999999999999</v>
       </c>
-      <c r="AV3" s="17">
+      <c r="AV3" s="15">
         <v>1121.8</v>
       </c>
     </row>
@@ -1444,30 +1444,34 @@
       <c r="AA4" s="6"/>
       <c r="AB4" s="6"/>
       <c r="AC4" s="6"/>
-      <c r="AD4" s="17">
+      <c r="AD4" s="15">
         <v>58.7</v>
       </c>
-      <c r="AE4" s="17"/>
+      <c r="AE4" s="15">
+        <v>60.3</v>
+      </c>
       <c r="AF4" s="6"/>
       <c r="AG4" s="6"/>
-      <c r="AH4" s="17">
+      <c r="AH4" s="15">
         <v>65.2</v>
       </c>
-      <c r="AI4" s="17"/>
+      <c r="AI4" s="15">
+        <v>65.099999999999994</v>
+      </c>
       <c r="AJ4" s="6"/>
       <c r="AK4" s="6"/>
       <c r="AL4" s="6"/>
       <c r="AM4" s="6"/>
-      <c r="AS4" s="17">
+      <c r="AS4" s="15">
         <v>297.10000000000002</v>
       </c>
-      <c r="AT4" s="17">
+      <c r="AT4" s="15">
         <v>285.10000000000002</v>
       </c>
-      <c r="AU4" s="17">
+      <c r="AU4" s="15">
         <v>267.7</v>
       </c>
-      <c r="AV4" s="17">
+      <c r="AV4" s="15">
         <v>249.2</v>
       </c>
     </row>
@@ -1502,30 +1506,34 @@
       <c r="AA5" s="6"/>
       <c r="AB5" s="6"/>
       <c r="AC5" s="6"/>
-      <c r="AD5" s="17">
+      <c r="AD5" s="15">
         <v>18.399999999999999</v>
       </c>
-      <c r="AE5" s="17"/>
+      <c r="AE5" s="15">
+        <v>23.4</v>
+      </c>
       <c r="AF5" s="6"/>
       <c r="AG5" s="6"/>
-      <c r="AH5" s="17">
+      <c r="AH5" s="15">
         <v>16.2</v>
       </c>
-      <c r="AI5" s="17"/>
+      <c r="AI5" s="15">
+        <v>21.4</v>
+      </c>
       <c r="AJ5" s="6"/>
       <c r="AK5" s="6"/>
       <c r="AL5" s="6"/>
       <c r="AM5" s="6"/>
-      <c r="AS5" s="17">
+      <c r="AS5" s="15">
         <v>86.3</v>
       </c>
-      <c r="AT5" s="17">
+      <c r="AT5" s="15">
         <v>76.8</v>
       </c>
-      <c r="AU5" s="17">
+      <c r="AU5" s="15">
         <v>80.7</v>
       </c>
-      <c r="AV5" s="17">
+      <c r="AV5" s="15">
         <v>72.2</v>
       </c>
     </row>
@@ -1630,7 +1638,8 @@
         <v>287.89999999999998</v>
       </c>
       <c r="AI6" s="7">
-        <v>535</v>
+        <f>SUM(AI3:AI5)</f>
+        <v>545.69999999999993</v>
       </c>
       <c r="AJ6" s="7">
         <f>AF6*0.99</f>
@@ -1679,47 +1688,47 @@
       </c>
       <c r="AW6" s="7">
         <f>SUM(AI6:AL6)</f>
-        <v>1474.9489999999998</v>
+        <v>1485.6489999999999</v>
       </c>
       <c r="AX6" s="7">
         <f>AW6*1.08</f>
-        <v>1592.9449199999999</v>
+        <v>1604.50092</v>
       </c>
       <c r="AY6" s="7">
         <f>AX6*1.05</f>
-        <v>1672.5921659999999</v>
+        <v>1684.725966</v>
       </c>
       <c r="AZ6" s="7">
         <f>AY6*1.03</f>
-        <v>1722.76993098</v>
+        <v>1735.2677449800001</v>
       </c>
       <c r="BA6" s="7">
         <f>AZ6*1.02</f>
-        <v>1757.2253295995999</v>
+        <v>1769.9730998796001</v>
       </c>
       <c r="BB6" s="7">
         <f t="shared" ref="BB6:BG6" si="0">BA6*1.02</f>
-        <v>1792.369836191592</v>
+        <v>1805.3725618771921</v>
       </c>
       <c r="BC6" s="7">
         <f t="shared" si="0"/>
-        <v>1828.2172329154239</v>
+        <v>1841.480013114736</v>
       </c>
       <c r="BD6" s="7">
         <f t="shared" si="0"/>
-        <v>1864.7815775737324</v>
+        <v>1878.3096133770307</v>
       </c>
       <c r="BE6" s="7">
         <f t="shared" si="0"/>
-        <v>1902.077209125207</v>
+        <v>1915.8758056445713</v>
       </c>
       <c r="BF6" s="7">
         <f t="shared" si="0"/>
-        <v>1940.1187533077111</v>
+        <v>1954.1933217574629</v>
       </c>
       <c r="BG6" s="7">
         <f t="shared" si="0"/>
-        <v>1978.9211283738655</v>
+        <v>1993.2771881926121</v>
       </c>
     </row>
     <row r="7" spans="2:59" x14ac:dyDescent="0.3">
@@ -1823,8 +1832,7 @@
         <v>162.1</v>
       </c>
       <c r="AI7" s="4">
-        <f>AI6-AI8</f>
-        <v>294.25</v>
+        <v>292.2</v>
       </c>
       <c r="AJ7" s="4">
         <f>AJ6-AJ8</f>
@@ -1871,49 +1879,49 @@
         <f>SUM(AE7:AH7)</f>
         <v>812.7</v>
       </c>
-      <c r="AW7" s="18">
+      <c r="AW7" s="4">
         <f>SUM(AI7:AL7)</f>
-        <v>820.62144000000001</v>
+        <v>818.57143999999994</v>
       </c>
       <c r="AX7" s="4">
-        <f t="shared" ref="AW7:BA7" si="2">AX6-AX8</f>
-        <v>860.19025679999993</v>
+        <f t="shared" ref="AX7:BA7" si="2">AX6-AX8</f>
+        <v>866.4304967999999</v>
       </c>
       <c r="AY7" s="4">
         <f t="shared" si="2"/>
-        <v>886.47384797999996</v>
+        <v>892.90476197999999</v>
       </c>
       <c r="AZ7" s="4">
         <f t="shared" si="2"/>
-        <v>913.0680634194</v>
+        <v>919.69190483940008</v>
       </c>
       <c r="BA7" s="4">
         <f t="shared" si="2"/>
-        <v>931.32942468778799</v>
+        <v>938.08574293618813</v>
       </c>
       <c r="BB7" s="4">
         <f t="shared" ref="BB7:BF7" si="3">BB6-BB8</f>
-        <v>949.95601318154377</v>
+        <v>956.84745779491186</v>
       </c>
       <c r="BC7" s="4">
         <f t="shared" si="3"/>
-        <v>968.95513344517474</v>
+        <v>975.98440695081013</v>
       </c>
       <c r="BD7" s="4">
         <f t="shared" si="3"/>
-        <v>988.33423611407818</v>
+        <v>995.50409508982636</v>
       </c>
       <c r="BE7" s="4">
         <f t="shared" si="3"/>
-        <v>1008.1009208363597</v>
+        <v>1015.4141769916229</v>
       </c>
       <c r="BF7" s="4">
         <f t="shared" si="3"/>
-        <v>1028.2629392530871</v>
+        <v>1035.7224605314555</v>
       </c>
       <c r="BG7" s="4">
         <f t="shared" ref="BG7" si="4">BG6-BG8</f>
-        <v>1048.8281980381489</v>
+        <v>1056.4369097420845</v>
       </c>
     </row>
     <row r="8" spans="2:59" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2029,7 +2037,7 @@
         <v>191.60000000000002</v>
       </c>
       <c r="AD8" s="7">
-        <f t="shared" ref="AD8:AH8" si="15">AD6-AD7</f>
+        <f t="shared" ref="AD8:AI8" si="15">AD6-AD7</f>
         <v>103</v>
       </c>
       <c r="AE8" s="7">
@@ -2049,8 +2057,8 @@
         <v>125.79999999999998</v>
       </c>
       <c r="AI8" s="7">
-        <f>AI6*0.45</f>
-        <v>240.75</v>
+        <f t="shared" si="15"/>
+        <v>253.49999999999994</v>
       </c>
       <c r="AJ8" s="7">
         <f>AJ6*0.44</f>
@@ -2099,47 +2107,47 @@
       </c>
       <c r="AW8" s="7">
         <f>AW6*0.45</f>
-        <v>663.72704999999996</v>
+        <v>668.54205000000002</v>
       </c>
       <c r="AX8" s="7">
         <f>AX6*0.46</f>
-        <v>732.75466319999998</v>
+        <v>738.07042320000005</v>
       </c>
       <c r="AY8" s="7">
         <f t="shared" ref="AY8:BG8" si="18">AY6*0.47</f>
-        <v>786.11831801999995</v>
+        <v>791.82120401999998</v>
       </c>
       <c r="AZ8" s="7">
         <f t="shared" si="18"/>
-        <v>809.70186756060002</v>
+        <v>815.57584014060001</v>
       </c>
       <c r="BA8" s="7">
         <f t="shared" si="18"/>
-        <v>825.89590491181195</v>
+        <v>831.88735694341199</v>
       </c>
       <c r="BB8" s="7">
         <f t="shared" si="18"/>
-        <v>842.41382301004819</v>
+        <v>848.52510408228022</v>
       </c>
       <c r="BC8" s="7">
         <f t="shared" si="18"/>
-        <v>859.26209947024915</v>
+        <v>865.49560616392591</v>
       </c>
       <c r="BD8" s="7">
         <f t="shared" si="18"/>
-        <v>876.44734145965424</v>
+        <v>882.80551828720434</v>
       </c>
       <c r="BE8" s="7">
         <f t="shared" si="18"/>
-        <v>893.97628828884729</v>
+        <v>900.46162865294843</v>
       </c>
       <c r="BF8" s="7">
         <f t="shared" si="18"/>
-        <v>911.85581405462415</v>
+        <v>918.47086122600751</v>
       </c>
       <c r="BG8" s="7">
         <f t="shared" si="18"/>
-        <v>930.09293033571669</v>
+        <v>936.84027845052765</v>
       </c>
     </row>
     <row r="9" spans="2:59" x14ac:dyDescent="0.3">
@@ -2243,8 +2251,7 @@
         <v>62</v>
       </c>
       <c r="AI9" s="4">
-        <f>AE9*0.86</f>
-        <v>69.488</v>
+        <v>59.8</v>
       </c>
       <c r="AJ9" s="4">
         <f>AF9*0.95</f>
@@ -2291,49 +2298,49 @@
         <f>SUM(AE9:AH9)</f>
         <v>280</v>
       </c>
-      <c r="AW9" s="18">
+      <c r="AW9" s="4">
         <f t="shared" ref="AW9:AW11" si="19">SUM(AI9:AL9)</f>
-        <v>270.952</v>
+        <v>261.26400000000001</v>
       </c>
       <c r="AX9" s="4">
         <f t="shared" ref="AX9:AZ9" si="20">AW9*1.01</f>
-        <v>273.66152</v>
+        <v>263.87664000000001</v>
       </c>
       <c r="AY9" s="4">
         <f t="shared" si="20"/>
-        <v>276.39813520000001</v>
+        <v>266.51540640000002</v>
       </c>
       <c r="AZ9" s="4">
         <f t="shared" si="20"/>
-        <v>279.16211655200004</v>
+        <v>269.180560464</v>
       </c>
       <c r="BA9" s="4">
         <f t="shared" ref="BA9" si="21">AZ9*1.01</f>
-        <v>281.95373771752003</v>
+        <v>271.87236606864002</v>
       </c>
       <c r="BB9" s="4">
         <f t="shared" ref="BB9" si="22">BA9*1.01</f>
-        <v>284.77327509469524</v>
+        <v>274.59108972932643</v>
       </c>
       <c r="BC9" s="4">
         <f t="shared" ref="BC9" si="23">BB9*1.01</f>
-        <v>287.62100784564217</v>
+        <v>277.33700062661967</v>
       </c>
       <c r="BD9" s="4">
         <f t="shared" ref="BD9" si="24">BC9*1.01</f>
-        <v>290.49721792409861</v>
+        <v>280.11037063288586</v>
       </c>
       <c r="BE9" s="4">
         <f t="shared" ref="BE9" si="25">BD9*1.01</f>
-        <v>293.40219010333959</v>
+        <v>282.91147433921475</v>
       </c>
       <c r="BF9" s="4">
         <f t="shared" ref="BF9:BG9" si="26">BE9*1.01</f>
-        <v>296.33621200437301</v>
+        <v>285.7405890826069</v>
       </c>
       <c r="BG9" s="4">
         <f t="shared" si="26"/>
-        <v>299.29957412441672</v>
+        <v>288.59799497343295</v>
       </c>
     </row>
     <row r="10" spans="2:59" x14ac:dyDescent="0.3">
@@ -2437,7 +2444,7 @@
         <v>67.8</v>
       </c>
       <c r="AI10" s="4">
-        <v>75</v>
+        <v>65.3</v>
       </c>
       <c r="AJ10" s="4">
         <f>AJ6*0.24</f>
@@ -2484,49 +2491,49 @@
         <f>SUM(AE10:AH10)</f>
         <v>281.2</v>
       </c>
-      <c r="AW10" s="18">
+      <c r="AW10" s="4">
         <f t="shared" si="19"/>
-        <v>275.31349</v>
+        <v>265.61349000000001</v>
       </c>
       <c r="AX10" s="4">
         <f>AX6*0.19</f>
-        <v>302.65953479999996</v>
+        <v>304.85517479999999</v>
       </c>
       <c r="AY10" s="4">
         <f>AY6*0.18</f>
-        <v>301.06658987999998</v>
+        <v>303.25067387999997</v>
       </c>
       <c r="AZ10" s="4">
         <f>AZ6*0.17</f>
-        <v>292.87088826660005</v>
+        <v>294.99551664660004</v>
       </c>
       <c r="BA10" s="4">
         <f t="shared" ref="BA10" si="28">BA6*0.16</f>
-        <v>281.15605273593599</v>
+        <v>283.19569598073605</v>
       </c>
       <c r="BB10" s="4">
         <f t="shared" ref="BB10:BF10" si="29">BB6*0.16</f>
-        <v>286.77917379065474</v>
+        <v>288.85960990035073</v>
       </c>
       <c r="BC10" s="4">
         <f t="shared" si="29"/>
-        <v>292.51475726646783</v>
+        <v>294.63680209835775</v>
       </c>
       <c r="BD10" s="4">
         <f t="shared" si="29"/>
-        <v>298.36505241179719</v>
+        <v>300.52953814032492</v>
       </c>
       <c r="BE10" s="4">
         <f t="shared" si="29"/>
-        <v>304.33235346003312</v>
+        <v>306.5401289031314</v>
       </c>
       <c r="BF10" s="4">
         <f t="shared" si="29"/>
-        <v>310.41900052923381</v>
+        <v>312.67093148119409</v>
       </c>
       <c r="BG10" s="4">
         <f t="shared" ref="BG10" si="30">BG6*0.16</f>
-        <v>316.62738053981849</v>
+        <v>318.92435011081795</v>
       </c>
     </row>
     <row r="11" spans="2:59" x14ac:dyDescent="0.3">
@@ -2630,7 +2637,7 @@
         <v>30.5</v>
       </c>
       <c r="AI11" s="4">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AJ11" s="4">
         <f>AF11*0.95</f>
@@ -2677,49 +2684,49 @@
         <f>SUM(AE11:AH11)</f>
         <v>119.8</v>
       </c>
-      <c r="AW11" s="18">
+      <c r="AW11" s="4">
         <f t="shared" si="19"/>
-        <v>117.16400000000002</v>
+        <v>122.16400000000002</v>
       </c>
       <c r="AX11" s="4">
         <f t="shared" ref="AX11:BG11" si="32">AW11*1.01</f>
-        <v>118.33564000000001</v>
+        <v>123.38564000000002</v>
       </c>
       <c r="AY11" s="4">
         <f t="shared" si="32"/>
-        <v>119.51899640000002</v>
+        <v>124.61949640000003</v>
       </c>
       <c r="AZ11" s="4">
         <f t="shared" si="32"/>
-        <v>120.71418636400003</v>
+        <v>125.86569136400003</v>
       </c>
       <c r="BA11" s="4">
         <f t="shared" si="32"/>
-        <v>121.92132822764003</v>
+        <v>127.12434827764002</v>
       </c>
       <c r="BB11" s="4">
         <f t="shared" si="32"/>
-        <v>123.14054150991643</v>
+        <v>128.39559176041644</v>
       </c>
       <c r="BC11" s="4">
         <f t="shared" si="32"/>
-        <v>124.37194692501559</v>
+        <v>129.67954767802061</v>
       </c>
       <c r="BD11" s="4">
         <f t="shared" si="32"/>
-        <v>125.61566639426574</v>
+        <v>130.97634315480082</v>
       </c>
       <c r="BE11" s="4">
         <f t="shared" si="32"/>
-        <v>126.87182305820841</v>
+        <v>132.28610658634884</v>
       </c>
       <c r="BF11" s="4">
         <f t="shared" si="32"/>
-        <v>128.1405412887905</v>
+        <v>133.60896765221233</v>
       </c>
       <c r="BG11" s="4">
         <f t="shared" si="32"/>
-        <v>129.42194670167839</v>
+        <v>134.94505732873446</v>
       </c>
     </row>
     <row r="12" spans="2:59" x14ac:dyDescent="0.3">
@@ -2856,7 +2863,7 @@
       </c>
       <c r="AI12" s="4">
         <f t="shared" ref="AI12:AL12" si="46">AI9+AI10+AI11</f>
-        <v>167.488</v>
+        <v>153.1</v>
       </c>
       <c r="AJ12" s="4">
         <f t="shared" si="46"/>
@@ -2905,47 +2912,47 @@
       </c>
       <c r="AW12" s="4">
         <f t="shared" si="47"/>
-        <v>663.42948999999999</v>
+        <v>649.04149000000007</v>
       </c>
       <c r="AX12" s="4">
         <f t="shared" si="47"/>
-        <v>694.65669479999997</v>
+        <v>692.1174547999999</v>
       </c>
       <c r="AY12" s="4">
         <f t="shared" si="47"/>
-        <v>696.98372147999999</v>
+        <v>694.38557667999999</v>
       </c>
       <c r="AZ12" s="4">
         <f t="shared" si="47"/>
-        <v>692.7471911826002</v>
+        <v>690.04176847460008</v>
       </c>
       <c r="BA12" s="4">
         <f t="shared" si="47"/>
-        <v>685.03111868109613</v>
+        <v>682.19241032701609</v>
       </c>
       <c r="BB12" s="4">
         <f t="shared" ref="BB12:BF12" si="48">BB9+BB10+BB11</f>
-        <v>694.69299039526641</v>
+        <v>691.8462913900936</v>
       </c>
       <c r="BC12" s="4">
         <f t="shared" si="48"/>
-        <v>704.50771203712554</v>
+        <v>701.65335040299806</v>
       </c>
       <c r="BD12" s="4">
         <f t="shared" si="48"/>
-        <v>714.47793673016156</v>
+        <v>711.61625192801159</v>
       </c>
       <c r="BE12" s="4">
         <f t="shared" si="48"/>
-        <v>724.60636662158106</v>
+        <v>721.73770982869507</v>
       </c>
       <c r="BF12" s="4">
         <f t="shared" si="48"/>
-        <v>734.8957538223973</v>
+        <v>732.02048821601329</v>
       </c>
       <c r="BG12" s="4">
         <f t="shared" ref="BG12" si="49">BG9+BG10+BG11</f>
-        <v>745.34890136591355</v>
+        <v>742.46740241298539</v>
       </c>
     </row>
     <row r="13" spans="2:59" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3082,7 +3089,7 @@
       </c>
       <c r="AI13" s="7">
         <f t="shared" ref="AI13:AL13" si="63">AI8-AI12</f>
-        <v>73.262</v>
+        <v>100.39999999999995</v>
       </c>
       <c r="AJ13" s="7">
         <f t="shared" si="63"/>
@@ -3131,47 +3138,47 @@
       </c>
       <c r="AW13" s="7">
         <f t="shared" si="64"/>
-        <v>0.29755999999997584</v>
+        <v>19.50055999999995</v>
       </c>
       <c r="AX13" s="7">
         <f t="shared" si="64"/>
-        <v>38.097968400000013</v>
+        <v>45.952968400000145</v>
       </c>
       <c r="AY13" s="7">
         <f t="shared" si="64"/>
-        <v>89.134596539999961</v>
+        <v>97.435627339999996</v>
       </c>
       <c r="AZ13" s="7">
         <f t="shared" si="64"/>
-        <v>116.95467637799982</v>
+        <v>125.53407166599993</v>
       </c>
       <c r="BA13" s="7">
         <f t="shared" si="64"/>
-        <v>140.86478623071582</v>
+        <v>149.6949466163959</v>
       </c>
       <c r="BB13" s="7">
         <f t="shared" ref="BB13:BF13" si="65">BB8-BB12</f>
-        <v>147.72083261478178</v>
+        <v>156.67881269218663</v>
       </c>
       <c r="BC13" s="7">
         <f t="shared" si="65"/>
-        <v>154.75438743312361</v>
+        <v>163.84225576092786</v>
       </c>
       <c r="BD13" s="7">
         <f t="shared" si="65"/>
-        <v>161.96940472949268</v>
+        <v>171.18926635919274</v>
       </c>
       <c r="BE13" s="7">
         <f t="shared" si="65"/>
-        <v>169.36992166726623</v>
+        <v>178.72391882425336</v>
       </c>
       <c r="BF13" s="7">
         <f t="shared" si="65"/>
-        <v>176.96006023222685</v>
+        <v>186.45037300999422</v>
       </c>
       <c r="BG13" s="7">
         <f t="shared" ref="BG13" si="66">BG8-BG12</f>
-        <v>184.74402896980314</v>
+        <v>194.37287603754226</v>
       </c>
     </row>
     <row r="14" spans="2:59" x14ac:dyDescent="0.3">
@@ -3276,7 +3283,8 @@
         <v>-0.1</v>
       </c>
       <c r="AI14" s="4">
-        <v>-0.1</v>
+        <f>-1.3+0.1-0.4</f>
+        <v>-1.6</v>
       </c>
       <c r="AJ14" s="4">
         <v>0</v>
@@ -3320,49 +3328,49 @@
         <f>SUM(AE14:AH14)</f>
         <v>-0.1</v>
       </c>
-      <c r="AW14" s="18">
+      <c r="AW14" s="4">
         <f>SUM(AI14:AL14)</f>
-        <v>-0.1</v>
+        <v>-1.6</v>
       </c>
       <c r="AX14" s="4">
-        <f t="shared" ref="AW14:BA14" si="67">-AW17*0.01</f>
-        <v>-3.6339529999999683E-2</v>
+        <f t="shared" ref="AX14:BA14" si="67">-AW17*0.01</f>
+        <v>-0.21036952999999944</v>
       </c>
       <c r="AY14" s="4">
         <f t="shared" si="67"/>
-        <v>-0.30507446344000011</v>
+        <v>-0.36930670344000122</v>
       </c>
       <c r="AZ14" s="4">
         <f t="shared" si="67"/>
-        <v>-0.71551736802751964</v>
+        <v>-0.78243947234751998</v>
       </c>
       <c r="BA14" s="4">
         <f t="shared" si="67"/>
-        <v>-0.94136154996821875</v>
+        <v>-1.0105320891067797</v>
       </c>
       <c r="BB14" s="4">
         <f t="shared" ref="BB14" si="68">-BA17*0.01</f>
-        <v>-1.1344491822454723</v>
+        <v>-1.2056438296440215</v>
       </c>
       <c r="BC14" s="4">
         <f t="shared" ref="BC14" si="69">-BB17*0.01</f>
-        <v>-1.190842254376218</v>
+        <v>-1.2630756521746453</v>
       </c>
       <c r="BD14" s="4">
         <f t="shared" ref="BD14" si="70">-BC17*0.01</f>
-        <v>-1.2475618374999986</v>
+        <v>-1.3208426513048201</v>
       </c>
       <c r="BE14" s="4">
         <f t="shared" ref="BE14" si="71">-BD17*0.01</f>
-        <v>-1.3057357325359413</v>
+        <v>-1.3800808720839806</v>
       </c>
       <c r="BF14" s="4">
         <f t="shared" ref="BF14:BG14" si="72">-BE17*0.01</f>
-        <v>-1.3654052591984174</v>
+        <v>-1.4408319975706989</v>
       </c>
       <c r="BG14" s="4">
         <f t="shared" si="72"/>
-        <v>-1.4266037239314022</v>
+        <v>-1.5031296400605194</v>
       </c>
     </row>
     <row r="15" spans="2:59" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3499,7 +3507,7 @@
       </c>
       <c r="AI15" s="7">
         <f t="shared" ref="AI15:AL15" si="85">AI13-AI14</f>
-        <v>73.361999999999995</v>
+        <v>101.99999999999994</v>
       </c>
       <c r="AJ15" s="7">
         <f t="shared" si="85"/>
@@ -3548,47 +3556,47 @@
       </c>
       <c r="AW15" s="7">
         <f t="shared" si="86"/>
-        <v>0.39755999999997582</v>
+        <v>21.100559999999952</v>
       </c>
       <c r="AX15" s="7">
         <f t="shared" si="86"/>
-        <v>38.134307930000013</v>
+        <v>46.163337930000147</v>
       </c>
       <c r="AY15" s="7">
         <f t="shared" si="86"/>
-        <v>89.439671003439955</v>
+        <v>97.804934043439999</v>
       </c>
       <c r="AZ15" s="7">
         <f t="shared" si="86"/>
-        <v>117.67019374602734</v>
+        <v>126.31651113834745</v>
       </c>
       <c r="BA15" s="7">
         <f t="shared" si="86"/>
-        <v>141.80614778068403</v>
+        <v>150.70547870550268</v>
       </c>
       <c r="BB15" s="7">
         <f t="shared" ref="BB15:BF15" si="87">BB13-BB14</f>
-        <v>148.85528179702726</v>
+        <v>157.88445652183066</v>
       </c>
       <c r="BC15" s="7">
         <f t="shared" si="87"/>
-        <v>155.94522968749982</v>
+        <v>165.1053314131025</v>
       </c>
       <c r="BD15" s="7">
         <f t="shared" si="87"/>
-        <v>163.21696656699268</v>
+        <v>172.51010901049756</v>
       </c>
       <c r="BE15" s="7">
         <f t="shared" si="87"/>
-        <v>170.67565739980216</v>
+        <v>180.10399969633735</v>
       </c>
       <c r="BF15" s="7">
         <f t="shared" si="87"/>
-        <v>178.32546549142526</v>
+        <v>187.89120500756493</v>
       </c>
       <c r="BG15" s="7">
         <f t="shared" ref="BG15" si="88">BG13-BG14</f>
-        <v>186.17063269373455</v>
+        <v>195.87600567760276</v>
       </c>
     </row>
     <row r="16" spans="2:59" x14ac:dyDescent="0.3">
@@ -3692,7 +3700,7 @@
         <v>3.5</v>
       </c>
       <c r="AI16" s="4">
-        <v>5</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="AJ16" s="4">
         <f>AJ15*0.1</f>
@@ -3739,49 +3747,49 @@
         <f>SUM(AE16:AH16)</f>
         <v>10.7</v>
       </c>
-      <c r="AW16" s="18">
+      <c r="AW16" s="4">
         <f>SUM(AI16:AL16)</f>
-        <v>-3.2363929999999925</v>
+        <v>6.3607000000008185E-2</v>
       </c>
       <c r="AX16" s="4">
         <f t="shared" ref="AX16:BA16" si="90">AX15*0.2</f>
-        <v>7.6268615860000031</v>
+        <v>9.23266758600003</v>
       </c>
       <c r="AY16" s="4">
         <f t="shared" si="90"/>
-        <v>17.88793420068799</v>
+        <v>19.560986808688</v>
       </c>
       <c r="AZ16" s="4">
         <f t="shared" si="90"/>
-        <v>23.534038749205468</v>
+        <v>25.263302227669492</v>
       </c>
       <c r="BA16" s="4">
         <f t="shared" si="90"/>
-        <v>28.361229556136806</v>
+        <v>30.141095741100539</v>
       </c>
       <c r="BB16" s="4">
         <f t="shared" ref="BB16:BF16" si="91">BB15*0.2</f>
-        <v>29.771056359405453</v>
+        <v>31.576891304366132</v>
       </c>
       <c r="BC16" s="4">
         <f t="shared" si="91"/>
-        <v>31.189045937499966</v>
+        <v>33.021066282620502</v>
       </c>
       <c r="BD16" s="4">
         <f t="shared" si="91"/>
-        <v>32.643393313398541</v>
+        <v>34.502021802099513</v>
       </c>
       <c r="BE16" s="4">
         <f t="shared" si="91"/>
-        <v>34.135131479960435</v>
+        <v>36.020799939267469</v>
       </c>
       <c r="BF16" s="4">
         <f t="shared" si="91"/>
-        <v>35.665093098285055</v>
+        <v>37.578241001512986</v>
       </c>
       <c r="BG16" s="4">
         <f t="shared" ref="BG16" si="92">BG15*0.2</f>
-        <v>37.234126538746914</v>
+        <v>39.175201135520552</v>
       </c>
     </row>
     <row r="17" spans="2:181" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3918,7 +3926,7 @@
       </c>
       <c r="AI17" s="7">
         <f t="shared" ref="AI17:AL17" si="106">AI15-AI16</f>
-        <v>68.361999999999995</v>
+        <v>93.699999999999946</v>
       </c>
       <c r="AJ17" s="7">
         <f t="shared" si="106"/>
@@ -3968,535 +3976,535 @@
       </c>
       <c r="AW17" s="7">
         <f t="shared" si="107"/>
-        <v>3.6339529999999685</v>
+        <v>21.036952999999944</v>
       </c>
       <c r="AX17" s="7">
         <f t="shared" si="107"/>
-        <v>30.507446344000009</v>
+        <v>36.93067034400012</v>
       </c>
       <c r="AY17" s="7">
         <f t="shared" si="107"/>
-        <v>71.551736802751961</v>
+        <v>78.243947234752</v>
       </c>
       <c r="AZ17" s="7">
         <f t="shared" si="107"/>
-        <v>94.136154996821872</v>
+        <v>101.05320891067797</v>
       </c>
       <c r="BA17" s="7">
         <f t="shared" si="107"/>
-        <v>113.44491822454722</v>
+        <v>120.56438296440214</v>
       </c>
       <c r="BB17" s="7">
         <f t="shared" ref="BB17:BF17" si="108">BB15-BB16</f>
-        <v>119.08422543762181</v>
+        <v>126.30756521746453</v>
       </c>
       <c r="BC17" s="7">
         <f t="shared" si="108"/>
-        <v>124.75618374999985</v>
+        <v>132.08426513048201</v>
       </c>
       <c r="BD17" s="7">
         <f t="shared" si="108"/>
-        <v>130.57357325359413</v>
+        <v>138.00808720839805</v>
       </c>
       <c r="BE17" s="7">
         <f t="shared" si="108"/>
-        <v>136.54052591984174</v>
+        <v>144.08319975706988</v>
       </c>
       <c r="BF17" s="7">
         <f t="shared" si="108"/>
-        <v>142.66037239314022</v>
+        <v>150.31296400605194</v>
       </c>
       <c r="BG17" s="7">
         <f t="shared" ref="BG17" si="109">BG15-BG16</f>
-        <v>148.93650615498763</v>
+        <v>156.70080454208221</v>
       </c>
       <c r="BH17" s="1">
         <f>BF17*(1+$BJ$26)</f>
-        <v>141.23376866920881</v>
+        <v>148.80983436599143</v>
       </c>
       <c r="BI17" s="1">
         <f t="shared" ref="BI17:DT17" si="110">BH17*(1+$BJ$26)</f>
-        <v>139.82143098251672</v>
+        <v>147.32173602233152</v>
       </c>
       <c r="BJ17" s="1">
         <f t="shared" si="110"/>
-        <v>138.42321667269155</v>
+        <v>145.84851866210821</v>
       </c>
       <c r="BK17" s="1">
         <f t="shared" si="110"/>
-        <v>137.03898450596463</v>
+        <v>144.39003347548712</v>
       </c>
       <c r="BL17" s="1">
         <f t="shared" si="110"/>
-        <v>135.668594660905</v>
+        <v>142.94613314073223</v>
       </c>
       <c r="BM17" s="1">
         <f t="shared" si="110"/>
-        <v>134.31190871429595</v>
+        <v>141.51667180932492</v>
       </c>
       <c r="BN17" s="1">
         <f t="shared" si="110"/>
-        <v>132.968789627153</v>
+        <v>140.10150509123167</v>
       </c>
       <c r="BO17" s="1">
         <f t="shared" si="110"/>
-        <v>131.63910173088146</v>
+        <v>138.70049004031935</v>
       </c>
       <c r="BP17" s="1">
         <f t="shared" si="110"/>
-        <v>130.32271071357266</v>
+        <v>137.31348513991617</v>
       </c>
       <c r="BQ17" s="1">
         <f t="shared" si="110"/>
-        <v>129.01948360643692</v>
+        <v>135.94035028851701</v>
       </c>
       <c r="BR17" s="1">
         <f t="shared" si="110"/>
-        <v>127.72928877037255</v>
+        <v>134.58094678563185</v>
       </c>
       <c r="BS17" s="1">
         <f t="shared" si="110"/>
-        <v>126.45199588266883</v>
+        <v>133.23513731777552</v>
       </c>
       <c r="BT17" s="1">
         <f t="shared" si="110"/>
-        <v>125.18747592384213</v>
+        <v>131.90278594459778</v>
       </c>
       <c r="BU17" s="1">
         <f t="shared" si="110"/>
-        <v>123.93560116460371</v>
+        <v>130.5837580851518</v>
       </c>
       <c r="BV17" s="1">
         <f t="shared" si="110"/>
-        <v>122.69624515295767</v>
+        <v>129.27792050430028</v>
       </c>
       <c r="BW17" s="1">
         <f t="shared" si="110"/>
-        <v>121.4692827014281</v>
+        <v>127.98514129925728</v>
       </c>
       <c r="BX17" s="1">
         <f t="shared" si="110"/>
-        <v>120.25458987441382</v>
+        <v>126.70528988626471</v>
       </c>
       <c r="BY17" s="1">
         <f t="shared" si="110"/>
-        <v>119.05204397566969</v>
+        <v>125.43823698740206</v>
       </c>
       <c r="BZ17" s="1">
         <f t="shared" si="110"/>
-        <v>117.86152353591299</v>
+        <v>124.18385461752804</v>
       </c>
       <c r="CA17" s="1">
         <f t="shared" si="110"/>
-        <v>116.68290830055386</v>
+        <v>122.94201607135275</v>
       </c>
       <c r="CB17" s="1">
         <f t="shared" si="110"/>
-        <v>115.51607921754832</v>
+        <v>121.71259591063922</v>
       </c>
       <c r="CC17" s="1">
         <f t="shared" si="110"/>
-        <v>114.36091842537284</v>
+        <v>120.49546995153283</v>
       </c>
       <c r="CD17" s="1">
         <f t="shared" si="110"/>
-        <v>113.21730924111911</v>
+        <v>119.2905152520175</v>
       </c>
       <c r="CE17" s="1">
         <f t="shared" si="110"/>
-        <v>112.08513614870792</v>
+        <v>118.09761009949732</v>
       </c>
       <c r="CF17" s="1">
         <f t="shared" si="110"/>
-        <v>110.96428478722083</v>
+        <v>116.91663399850235</v>
       </c>
       <c r="CG17" s="1">
         <f t="shared" si="110"/>
-        <v>109.85464193934862</v>
+        <v>115.74746765851732</v>
       </c>
       <c r="CH17" s="1">
         <f t="shared" si="110"/>
-        <v>108.75609551995514</v>
+        <v>114.58999298193214</v>
       </c>
       <c r="CI17" s="1">
         <f t="shared" si="110"/>
-        <v>107.66853456475559</v>
+        <v>113.44409305211282</v>
       </c>
       <c r="CJ17" s="1">
         <f t="shared" si="110"/>
-        <v>106.59184921910803</v>
+        <v>112.3096521215917</v>
       </c>
       <c r="CK17" s="1">
         <f t="shared" si="110"/>
-        <v>105.52593072691694</v>
+        <v>111.18655560037578</v>
       </c>
       <c r="CL17" s="1">
         <f t="shared" si="110"/>
-        <v>104.47067141964777</v>
+        <v>110.07469004437202</v>
       </c>
       <c r="CM17" s="1">
         <f t="shared" si="110"/>
-        <v>103.42596470545129</v>
+        <v>108.9739431439283</v>
       </c>
       <c r="CN17" s="1">
         <f t="shared" si="110"/>
-        <v>102.39170505839678</v>
+        <v>107.88420371248901</v>
       </c>
       <c r="CO17" s="1">
         <f t="shared" si="110"/>
-        <v>101.36778800781281</v>
+        <v>106.80536167536413</v>
       </c>
       <c r="CP17" s="1">
         <f t="shared" si="110"/>
-        <v>100.35411012773467</v>
+        <v>105.73730805861048</v>
       </c>
       <c r="CQ17" s="1">
         <f t="shared" si="110"/>
-        <v>99.350569026457322</v>
+        <v>104.67993497802438</v>
       </c>
       <c r="CR17" s="1">
         <f t="shared" si="110"/>
-        <v>98.357063336192752</v>
+        <v>103.63313562824413</v>
       </c>
       <c r="CS17" s="1">
         <f t="shared" si="110"/>
-        <v>97.373492702830831</v>
+        <v>102.59680427196169</v>
       </c>
       <c r="CT17" s="1">
         <f t="shared" si="110"/>
-        <v>96.399757775802527</v>
+        <v>101.57083622924208</v>
       </c>
       <c r="CU17" s="1">
         <f t="shared" si="110"/>
-        <v>95.435760198044505</v>
+        <v>100.55512786694966</v>
       </c>
       <c r="CV17" s="1">
         <f t="shared" si="110"/>
-        <v>94.481402596064058</v>
+        <v>99.549576588280161</v>
       </c>
       <c r="CW17" s="1">
         <f t="shared" si="110"/>
-        <v>93.536588570103419</v>
+        <v>98.554080822397353</v>
       </c>
       <c r="CX17" s="1">
         <f t="shared" si="110"/>
-        <v>92.601222684402387</v>
+        <v>97.568540014173379</v>
       </c>
       <c r="CY17" s="1">
         <f t="shared" si="110"/>
-        <v>91.675210457558364</v>
+        <v>96.592854614031651</v>
       </c>
       <c r="CZ17" s="1">
         <f t="shared" si="110"/>
-        <v>90.758458352982785</v>
+        <v>95.626926067891333</v>
       </c>
       <c r="DA17" s="1">
         <f t="shared" si="110"/>
-        <v>89.85087376945296</v>
+        <v>94.670656807212424</v>
       </c>
       <c r="DB17" s="1">
         <f t="shared" si="110"/>
-        <v>88.952365031758433</v>
+        <v>93.723950239140294</v>
       </c>
       <c r="DC17" s="1">
         <f t="shared" si="110"/>
-        <v>88.062841381440847</v>
+        <v>92.786710736748887</v>
       </c>
       <c r="DD17" s="1">
         <f t="shared" si="110"/>
-        <v>87.182212967626441</v>
+        <v>91.858843629381397</v>
       </c>
       <c r="DE17" s="1">
         <f t="shared" si="110"/>
-        <v>86.31039083795018</v>
+        <v>90.94025519308758</v>
       </c>
       <c r="DF17" s="1">
         <f t="shared" si="110"/>
-        <v>85.44728692957068</v>
+        <v>90.030852641156699</v>
       </c>
       <c r="DG17" s="1">
         <f t="shared" si="110"/>
-        <v>84.592814060274975</v>
+        <v>89.130544114745135</v>
       </c>
       <c r="DH17" s="1">
         <f t="shared" si="110"/>
-        <v>83.746885919672224</v>
+        <v>88.239238673597683</v>
       </c>
       <c r="DI17" s="1">
         <f t="shared" si="110"/>
-        <v>82.909417060475505</v>
+        <v>87.35684628686171</v>
       </c>
       <c r="DJ17" s="1">
         <f t="shared" si="110"/>
-        <v>82.080322889870743</v>
+        <v>86.483277823993092</v>
       </c>
       <c r="DK17" s="1">
         <f t="shared" si="110"/>
-        <v>81.259519660972032</v>
+        <v>85.618445045753163</v>
       </c>
       <c r="DL17" s="1">
         <f t="shared" si="110"/>
-        <v>80.446924464362311</v>
+        <v>84.762260595295629</v>
       </c>
       <c r="DM17" s="1">
         <f t="shared" si="110"/>
-        <v>79.642455219718684</v>
+        <v>83.914637989342665</v>
       </c>
       <c r="DN17" s="1">
         <f t="shared" si="110"/>
-        <v>78.846030667521489</v>
+        <v>83.075491609449244</v>
       </c>
       <c r="DO17" s="1">
         <f t="shared" si="110"/>
-        <v>78.05757036084627</v>
+        <v>82.244736693354753</v>
       </c>
       <c r="DP17" s="1">
         <f t="shared" si="110"/>
-        <v>77.276994657237807</v>
+        <v>81.422289326421208</v>
       </c>
       <c r="DQ17" s="1">
         <f t="shared" si="110"/>
-        <v>76.504224710665426</v>
+        <v>80.608066433156992</v>
       </c>
       <c r="DR17" s="1">
         <f t="shared" si="110"/>
-        <v>75.739182463558777</v>
+        <v>79.801985768825418</v>
       </c>
       <c r="DS17" s="1">
         <f t="shared" si="110"/>
-        <v>74.981790638923187</v>
+        <v>79.003965911137158</v>
       </c>
       <c r="DT17" s="1">
         <f t="shared" si="110"/>
-        <v>74.231972732533947</v>
+        <v>78.213926252025786</v>
       </c>
       <c r="DU17" s="1">
         <f t="shared" ref="DU17:FY17" si="111">DT17*(1+$BJ$26)</f>
-        <v>73.489653005208609</v>
+        <v>77.431786989505525</v>
       </c>
       <c r="DV17" s="1">
         <f t="shared" si="111"/>
-        <v>72.754756475156526</v>
+        <v>76.657469119610468</v>
       </c>
       <c r="DW17" s="1">
         <f t="shared" si="111"/>
-        <v>72.027208910404966</v>
+        <v>75.890894428414356</v>
       </c>
       <c r="DX17" s="1">
         <f t="shared" si="111"/>
-        <v>71.306936821300908</v>
+        <v>75.131985484130212</v>
       </c>
       <c r="DY17" s="1">
         <f t="shared" si="111"/>
-        <v>70.593867453087896</v>
+        <v>74.380665629288913</v>
       </c>
       <c r="DZ17" s="1">
         <f t="shared" si="111"/>
-        <v>69.887928778557011</v>
+        <v>73.636858972996023</v>
       </c>
       <c r="EA17" s="1">
         <f t="shared" si="111"/>
-        <v>69.189049490771438</v>
+        <v>72.90049038326606</v>
       </c>
       <c r="EB17" s="1">
         <f t="shared" si="111"/>
-        <v>68.497158995863728</v>
+        <v>72.1714854794334</v>
       </c>
       <c r="EC17" s="1">
         <f t="shared" si="111"/>
-        <v>67.812187405905092</v>
+        <v>71.449770624639072</v>
       </c>
       <c r="ED17" s="1">
         <f t="shared" si="111"/>
-        <v>67.134065531846048</v>
+        <v>70.735272918392681</v>
       </c>
       <c r="EE17" s="1">
         <f t="shared" si="111"/>
-        <v>66.462724876527588</v>
+        <v>70.027920189208757</v>
       </c>
       <c r="EF17" s="1">
         <f t="shared" si="111"/>
-        <v>65.798097627762317</v>
+        <v>69.32764098731667</v>
       </c>
       <c r="EG17" s="1">
         <f t="shared" si="111"/>
-        <v>65.140116651484689</v>
+        <v>68.634364577443506</v>
       </c>
       <c r="EH17" s="1">
         <f t="shared" si="111"/>
-        <v>64.488715484969845</v>
+        <v>67.948020931669063</v>
       </c>
       <c r="EI17" s="1">
         <f t="shared" si="111"/>
-        <v>63.843828330120147</v>
+        <v>67.26854072235237</v>
       </c>
       <c r="EJ17" s="1">
         <f t="shared" si="111"/>
-        <v>63.205390046818941</v>
+        <v>66.595855315128844</v>
       </c>
       <c r="EK17" s="1">
         <f t="shared" si="111"/>
-        <v>62.573336146350748</v>
+        <v>65.92989676197756</v>
       </c>
       <c r="EL17" s="1">
         <f t="shared" si="111"/>
-        <v>61.947602784887238</v>
+        <v>65.270597794357784</v>
       </c>
       <c r="EM17" s="1">
         <f t="shared" si="111"/>
-        <v>61.328126757038362</v>
+        <v>64.6178918164142</v>
       </c>
       <c r="EN17" s="1">
         <f t="shared" si="111"/>
-        <v>60.714845489467976</v>
+        <v>63.971712898250061</v>
       </c>
       <c r="EO17" s="1">
         <f t="shared" si="111"/>
-        <v>60.107697034573299</v>
+        <v>63.331995769267557</v>
       </c>
       <c r="EP17" s="1">
         <f t="shared" si="111"/>
-        <v>59.506620064227562</v>
+        <v>62.69867581157488</v>
       </c>
       <c r="EQ17" s="1">
         <f t="shared" si="111"/>
-        <v>58.911553863585283</v>
+        <v>62.071689053459131</v>
       </c>
       <c r="ER17" s="1">
         <f t="shared" si="111"/>
-        <v>58.322438324949431</v>
+        <v>61.450972162924536</v>
       </c>
       <c r="ES17" s="1">
         <f t="shared" si="111"/>
-        <v>57.739213941699937</v>
+        <v>60.836462441295289</v>
       </c>
       <c r="ET17" s="1">
         <f t="shared" si="111"/>
-        <v>57.161821802282937</v>
+        <v>60.228097816882332</v>
       </c>
       <c r="EU17" s="1">
         <f t="shared" si="111"/>
-        <v>56.590203584260109</v>
+        <v>59.625816838713511</v>
       </c>
       <c r="EV17" s="1">
         <f t="shared" si="111"/>
-        <v>56.024301548417505</v>
+        <v>59.029558670326374</v>
       </c>
       <c r="EW17" s="1">
         <f t="shared" si="111"/>
-        <v>55.464058532933329</v>
+        <v>58.439263083623111</v>
       </c>
       <c r="EX17" s="1">
         <f t="shared" si="111"/>
-        <v>54.909417947603998</v>
+        <v>57.854870452786876</v>
       </c>
       <c r="EY17" s="1">
         <f t="shared" si="111"/>
-        <v>54.360323768127955</v>
+        <v>57.276321748259008</v>
       </c>
       <c r="EZ17" s="1">
         <f t="shared" si="111"/>
-        <v>53.816720530446673</v>
+        <v>56.703558530776419</v>
       </c>
       <c r="FA17" s="1">
         <f t="shared" si="111"/>
-        <v>53.278553325142205</v>
+        <v>56.136522945468656</v>
       </c>
       <c r="FB17" s="1">
         <f t="shared" si="111"/>
-        <v>52.745767791890785</v>
+        <v>55.575157716013969</v>
       </c>
       <c r="FC17" s="1">
         <f t="shared" si="111"/>
-        <v>52.218310113971874</v>
+        <v>55.019406138853832</v>
       </c>
       <c r="FD17" s="1">
         <f t="shared" si="111"/>
-        <v>51.696127012832157</v>
+        <v>54.469212077465293</v>
       </c>
       <c r="FE17" s="1">
         <f t="shared" si="111"/>
-        <v>51.179165742703837</v>
+        <v>53.924519956690638</v>
       </c>
       <c r="FF17" s="1">
         <f t="shared" si="111"/>
-        <v>50.667374085276798</v>
+        <v>53.385274757123732</v>
       </c>
       <c r="FG17" s="1">
         <f t="shared" si="111"/>
-        <v>50.160700344424029</v>
+        <v>52.851422009552493</v>
       </c>
       <c r="FH17" s="1">
         <f t="shared" si="111"/>
-        <v>49.659093340979787</v>
+        <v>52.32290778945697</v>
       </c>
       <c r="FI17" s="1">
         <f t="shared" si="111"/>
-        <v>49.162502407569988</v>
+        <v>51.7996787115624</v>
       </c>
       <c r="FJ17" s="1">
         <f t="shared" si="111"/>
-        <v>48.670877383494286</v>
+        <v>51.281681924446772</v>
       </c>
       <c r="FK17" s="1">
         <f t="shared" si="111"/>
-        <v>48.184168609659345</v>
+        <v>50.768865105202302</v>
       </c>
       <c r="FL17" s="1">
         <f t="shared" si="111"/>
-        <v>47.702326923562751</v>
+        <v>50.261176454150281</v>
       </c>
       <c r="FM17" s="1">
         <f t="shared" si="111"/>
-        <v>47.225303654327121</v>
+        <v>49.758564689608775</v>
       </c>
       <c r="FN17" s="1">
         <f t="shared" si="111"/>
-        <v>46.753050617783849</v>
+        <v>49.260979042712684</v>
       </c>
       <c r="FO17" s="1">
         <f t="shared" si="111"/>
-        <v>46.285520111606012</v>
+        <v>48.768369252285559</v>
       </c>
       <c r="FP17" s="1">
         <f t="shared" si="111"/>
-        <v>45.822664910489948</v>
+        <v>48.280685559762702</v>
       </c>
       <c r="FQ17" s="1">
         <f t="shared" si="111"/>
-        <v>45.364438261385047</v>
+        <v>47.797878704165072</v>
       </c>
       <c r="FR17" s="1">
         <f t="shared" si="111"/>
-        <v>44.910793878771194</v>
+        <v>47.319899917123422</v>
       </c>
       <c r="FS17" s="1">
         <f t="shared" si="111"/>
-        <v>44.461685939983482</v>
+        <v>46.846700917952191</v>
       </c>
       <c r="FT17" s="1">
         <f t="shared" si="111"/>
-        <v>44.017069080583646</v>
+        <v>46.378233908772671</v>
       </c>
       <c r="FU17" s="1">
         <f t="shared" si="111"/>
-        <v>43.57689838977781</v>
+        <v>45.914451569684942</v>
       </c>
       <c r="FV17" s="1">
         <f t="shared" si="111"/>
-        <v>43.141129405880029</v>
+        <v>45.455307053988093</v>
       </c>
       <c r="FW17" s="1">
         <f t="shared" si="111"/>
-        <v>42.709718111821232</v>
+        <v>45.000753983448213</v>
       </c>
       <c r="FX17" s="1">
         <f t="shared" si="111"/>
-        <v>42.282620930703018</v>
+        <v>44.550746443613733</v>
       </c>
       <c r="FY17" s="1">
         <f t="shared" si="111"/>
-        <v>41.859794721395986</v>
+        <v>44.105238979177592</v>
       </c>
     </row>
     <row r="18" spans="2:181" x14ac:dyDescent="0.3">
@@ -4640,51 +4648,51 @@
         <v>121.4</v>
       </c>
       <c r="AV18" s="4">
-        <f>120.6</f>
+        <f t="shared" ref="AV18:BG18" si="113">120.6</f>
         <v>120.6</v>
       </c>
       <c r="AW18" s="4">
-        <f>120.6</f>
+        <f t="shared" si="113"/>
         <v>120.6</v>
       </c>
       <c r="AX18" s="4">
-        <f>120.6</f>
+        <f t="shared" si="113"/>
         <v>120.6</v>
       </c>
       <c r="AY18" s="4">
-        <f>120.6</f>
+        <f t="shared" si="113"/>
         <v>120.6</v>
       </c>
       <c r="AZ18" s="4">
-        <f>120.6</f>
+        <f t="shared" si="113"/>
         <v>120.6</v>
       </c>
       <c r="BA18" s="4">
-        <f>120.6</f>
+        <f t="shared" si="113"/>
         <v>120.6</v>
       </c>
       <c r="BB18" s="4">
-        <f>120.6</f>
+        <f t="shared" si="113"/>
         <v>120.6</v>
       </c>
       <c r="BC18" s="4">
-        <f>120.6</f>
+        <f t="shared" si="113"/>
         <v>120.6</v>
       </c>
       <c r="BD18" s="4">
-        <f>120.6</f>
+        <f t="shared" si="113"/>
         <v>120.6</v>
       </c>
       <c r="BE18" s="4">
-        <f>120.6</f>
+        <f t="shared" si="113"/>
         <v>120.6</v>
       </c>
       <c r="BF18" s="4">
-        <f>120.6</f>
+        <f t="shared" si="113"/>
         <v>120.6</v>
       </c>
       <c r="BG18" s="4">
-        <f>120.6</f>
+        <f t="shared" si="113"/>
         <v>120.6</v>
       </c>
     </row>
@@ -4693,147 +4701,147 @@
         <v>34</v>
       </c>
       <c r="C19" s="9">
-        <f t="shared" ref="C19:M19" si="113">C17/C18</f>
+        <f t="shared" ref="C19:M19" si="114">C17/C18</f>
         <v>0.41261261261261245</v>
       </c>
       <c r="D19" s="9">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>-0.29369369369369386</v>
       </c>
       <c r="E19" s="9">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>-0.24324324324324317</v>
       </c>
       <c r="F19" s="9">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>-1.6216216216216266E-2</v>
       </c>
       <c r="G19" s="9">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>0.5549549549549545</v>
       </c>
       <c r="H19" s="9">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>-0.20630630630630645</v>
       </c>
       <c r="I19" s="9">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>-0.12702702702702692</v>
       </c>
       <c r="J19" s="9">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>-0.26666666666666677</v>
       </c>
       <c r="K19" s="9">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>0.6378378378378381</v>
       </c>
       <c r="L19" s="9">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>-0.47117117117117108</v>
       </c>
       <c r="M19" s="9">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>-0.51441441441441416</v>
       </c>
       <c r="N19" s="9">
-        <f t="shared" ref="N19:O19" si="114">N17/N18</f>
+        <f t="shared" ref="N19:O19" si="115">N17/N18</f>
         <v>0.1628318584070797</v>
       </c>
       <c r="O19" s="9">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>1.1716814159292039</v>
       </c>
       <c r="P19" s="9">
-        <f t="shared" ref="P19:Q19" si="115">P17/P18</f>
+        <f t="shared" ref="P19:Q19" si="116">P17/P18</f>
         <v>0.15221238938053105</v>
       </c>
       <c r="Q19" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>0.14744645799011497</v>
       </c>
       <c r="R19" s="9">
-        <f t="shared" ref="R19" si="116">R17/R18</f>
+        <f t="shared" ref="R19" si="117">R17/R18</f>
         <v>-7.331136738056028E-2</v>
       </c>
       <c r="S19" s="9">
-        <f t="shared" ref="S19:T19" si="117">S17/S18</f>
+        <f t="shared" ref="S19:T19" si="118">S17/S18</f>
         <v>1.0181219110378912</v>
       </c>
       <c r="T19" s="9">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>7.1663920922570193E-2</v>
       </c>
       <c r="U19" s="9">
-        <f t="shared" ref="U19" si="118">U17/U18</f>
+        <f t="shared" ref="U19" si="119">U17/U18</f>
         <v>-4.1186161449752847E-3</v>
       </c>
       <c r="V19" s="9">
-        <f t="shared" ref="V19:W19" si="119">V17/V18</f>
+        <f t="shared" ref="V19:W19" si="120">V17/V18</f>
         <v>-0.52718286655683644</v>
       </c>
       <c r="W19" s="9">
-        <f t="shared" si="119"/>
+        <f t="shared" si="120"/>
         <v>0.62026359143327847</v>
       </c>
       <c r="X19" s="9">
-        <f t="shared" ref="X19" si="120">X17/X18</f>
+        <f t="shared" ref="X19" si="121">X17/X18</f>
         <v>-0.25205930807248778</v>
       </c>
       <c r="Y19" s="9">
-        <f t="shared" ref="Y19" si="121">Y17/Y18</f>
+        <f t="shared" ref="Y19" si="122">Y17/Y18</f>
         <v>-0.19522240527182849</v>
       </c>
       <c r="Z19" s="9">
-        <f t="shared" ref="Z19:AA19" si="122">Z17/Z18</f>
+        <f t="shared" ref="Z19:AA19" si="123">Z17/Z18</f>
         <v>-0.25782537067545264</v>
       </c>
       <c r="AA19" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>0.66639209225700158</v>
       </c>
       <c r="AB19" s="9">
-        <f t="shared" ref="AB19" si="123">AB17/AB18</f>
+        <f t="shared" ref="AB19" si="124">AB17/AB18</f>
         <v>-0.57331136738055999</v>
       </c>
       <c r="AC19" s="9">
-        <f t="shared" ref="AC19" si="124">AC17/AC18</f>
+        <f t="shared" ref="AC19" si="125">AC17/AC18</f>
         <v>3.0477759472817317E-2</v>
       </c>
       <c r="AD19" s="9">
-        <f t="shared" ref="AD19:AH19" si="125">AD17/AD18</f>
+        <f t="shared" ref="AD19:AH19" si="126">AD17/AD18</f>
         <v>-0.43739703459637569</v>
       </c>
       <c r="AE19" s="9">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>0.42317380352644823</v>
       </c>
       <c r="AF19" s="9">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>-0.5828476269775188</v>
       </c>
       <c r="AG19" s="9">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>-2.8309741881765244E-2</v>
       </c>
       <c r="AH19" s="9">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>-0.31426202321724733</v>
       </c>
       <c r="AI19" s="9">
-        <f t="shared" ref="AI19:AL19" si="126">AI17/AI18</f>
-        <v>0.56684908789386401</v>
+        <f t="shared" ref="AI19:AL19" si="127">AI17/AI18</f>
+        <v>0.77694859038142583</v>
       </c>
       <c r="AJ19" s="9">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>-0.40022089552238793</v>
       </c>
       <c r="AK19" s="9">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>2.3286268656716669E-2</v>
       </c>
       <c r="AL19" s="9">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>-0.23772156716417894</v>
       </c>
       <c r="AM19" s="9"/>
@@ -4850,84 +4858,92 @@
         <v>-0.17876106194690428</v>
       </c>
       <c r="AR19" s="9">
-        <f t="shared" ref="AR19:BA19" si="127">AR17/AR18</f>
+        <f t="shared" ref="AR19:BA19" si="128">AR17/AR18</f>
         <v>1.4035398230088483</v>
       </c>
       <c r="AS19" s="9">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>0.59999999999999964</v>
       </c>
       <c r="AT19" s="9">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>-9.1150442477879137E-2</v>
       </c>
       <c r="AU19" s="9">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>-0.31383855024711677</v>
       </c>
       <c r="AV19" s="9">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>-0.5049751243781091</v>
       </c>
       <c r="AW19" s="9">
-        <f t="shared" si="127"/>
-        <v>3.0132280265339706E-2</v>
+        <f t="shared" si="128"/>
+        <v>0.1744357628524042</v>
       </c>
       <c r="AX19" s="9">
-        <f t="shared" si="127"/>
-        <v>0.2529639000331676</v>
+        <f t="shared" si="128"/>
+        <v>0.30622446388059804</v>
       </c>
       <c r="AY19" s="9">
-        <f t="shared" si="127"/>
-        <v>0.59329798343907103</v>
+        <f t="shared" si="128"/>
+        <v>0.64878894887854066</v>
       </c>
       <c r="AZ19" s="9">
-        <f t="shared" si="127"/>
-        <v>0.78056513264363081</v>
+        <f t="shared" si="128"/>
+        <v>0.83792047189616892</v>
       </c>
       <c r="BA19" s="9">
-        <f t="shared" si="127"/>
-        <v>0.94067096371929704</v>
+        <f t="shared" si="128"/>
+        <v>0.99970466802986857</v>
       </c>
       <c r="BB19" s="9">
-        <f t="shared" ref="BB19:BF19" si="128">BB17/BB18</f>
-        <v>0.98743138837165689</v>
+        <f t="shared" ref="BB19:BF19" si="129">BB17/BB18</f>
+        <v>1.0473264114217624</v>
       </c>
       <c r="BC19" s="9">
-        <f t="shared" si="128"/>
-        <v>1.034462551824211</v>
+        <f t="shared" si="129"/>
+        <v>1.0952260790255557</v>
       </c>
       <c r="BD19" s="9">
-        <f t="shared" si="128"/>
-        <v>1.0826996123846944</v>
+        <f t="shared" si="129"/>
+        <v>1.1443456650779276</v>
       </c>
       <c r="BE19" s="9">
-        <f t="shared" si="128"/>
-        <v>1.1321768318394838</v>
+        <f t="shared" si="129"/>
+        <v>1.1947197326456873</v>
       </c>
       <c r="BF19" s="9">
-        <f t="shared" si="128"/>
-        <v>1.1829218274721411</v>
+        <f t="shared" si="129"/>
+        <v>1.2463761526206629</v>
       </c>
       <c r="BG19" s="9">
-        <f t="shared" ref="BG19" si="129">BG17/BG18</f>
-        <v>1.2349627376035459</v>
+        <f t="shared" ref="BG19" si="130">BG17/BG18</f>
+        <v>1.2993433212444627</v>
       </c>
     </row>
     <row r="21" spans="2:181" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>100</v>
       </c>
+      <c r="AH21" s="16">
+        <f t="shared" ref="AH21:AI23" si="131">AH3/AD3-1</f>
+        <v>0.15881032547699214</v>
+      </c>
+      <c r="AI21" s="16">
+        <f t="shared" si="131"/>
+        <v>-1.6912866623849387E-2</v>
+      </c>
       <c r="AT21" s="11">
-        <f t="shared" ref="AT21:AT23" si="130">AT3/AS3-1</f>
+        <f t="shared" ref="AT21:AT23" si="132">AT3/AS3-1</f>
         <v>-5.5153773102491033E-2</v>
       </c>
       <c r="AU21" s="11">
-        <f t="shared" ref="AU21:AU23" si="131">AU3/AT3-1</f>
+        <f t="shared" ref="AU21:AU23" si="133">AU3/AT3-1</f>
         <v>-9.5716715633214933E-2</v>
       </c>
       <c r="AV21" s="11">
-        <f t="shared" ref="AV21" si="132">AV3/AU3-1</f>
+        <f t="shared" ref="AV21" si="134">AV3/AU3-1</f>
         <v>-4.0868673050615589E-2</v>
       </c>
     </row>
@@ -4935,16 +4951,24 @@
       <c r="B22" t="s">
         <v>101</v>
       </c>
+      <c r="AH22" s="16">
+        <f t="shared" si="131"/>
+        <v>0.11073253833049401</v>
+      </c>
+      <c r="AI22" s="16">
+        <f t="shared" si="131"/>
+        <v>7.9601990049751103E-2</v>
+      </c>
       <c r="AT22" s="11">
-        <f t="shared" si="130"/>
+        <f t="shared" si="132"/>
         <v>-4.0390440928980142E-2</v>
       </c>
       <c r="AU22" s="11">
-        <f t="shared" si="131"/>
+        <f t="shared" si="133"/>
         <v>-6.1031217116801262E-2</v>
       </c>
       <c r="AV22" s="11">
-        <f t="shared" ref="AV22:AV23" si="133">AV4/AU4-1</f>
+        <f t="shared" ref="AV22:AV23" si="135">AV4/AU4-1</f>
         <v>-6.9107209562943583E-2</v>
       </c>
     </row>
@@ -4952,16 +4976,24 @@
       <c r="B23" t="s">
         <v>102</v>
       </c>
+      <c r="AH23" s="16">
+        <f t="shared" si="131"/>
+        <v>-0.11956521739130432</v>
+      </c>
+      <c r="AI23" s="16">
+        <f t="shared" si="131"/>
+        <v>-8.54700854700855E-2</v>
+      </c>
       <c r="AT23" s="11">
-        <f t="shared" si="130"/>
+        <f t="shared" si="132"/>
         <v>-0.11008111239860952</v>
       </c>
       <c r="AU23" s="11">
-        <f t="shared" si="131"/>
+        <f t="shared" si="133"/>
         <v>5.078125E-2</v>
       </c>
       <c r="AV23" s="11">
-        <f t="shared" si="133"/>
+        <f t="shared" si="135"/>
         <v>-0.10532837670384143</v>
       </c>
     </row>
@@ -4974,127 +5006,127 @@
         <v>5.8422174840085273E-2</v>
       </c>
       <c r="H24" s="8">
-        <f t="shared" ref="H24:N24" si="134">H6/D6-1</f>
+        <f t="shared" ref="H24:N24" si="136">H6/D6-1</f>
         <v>0.12587038028923403</v>
       </c>
       <c r="I24" s="8">
-        <f t="shared" si="134"/>
+        <f t="shared" si="136"/>
         <v>0.24808061420345506</v>
       </c>
       <c r="J24" s="8">
-        <f t="shared" si="134"/>
+        <f t="shared" si="136"/>
         <v>7.8050567973616758E-2</v>
       </c>
       <c r="K24" s="8">
-        <f t="shared" si="134"/>
+        <f t="shared" si="136"/>
         <v>0.13235294117647078</v>
       </c>
       <c r="L24" s="8">
-        <f t="shared" si="134"/>
+        <f t="shared" si="136"/>
         <v>-0.16698382492863939</v>
       </c>
       <c r="M24" s="8">
-        <f t="shared" si="134"/>
+        <f t="shared" si="136"/>
         <v>-4.152249134948105E-2</v>
       </c>
       <c r="N24" s="8">
-        <f t="shared" si="134"/>
+        <f t="shared" si="136"/>
         <v>0.15499660095173362</v>
       </c>
       <c r="O24" s="8">
-        <f t="shared" ref="O24" si="135">O6/K6-1</f>
+        <f t="shared" ref="O24" si="137">O6/K6-1</f>
         <v>0.14855008005692927</v>
       </c>
       <c r="P24" s="8">
-        <f t="shared" ref="P24" si="136">P6/L6-1</f>
+        <f t="shared" ref="P24" si="138">P6/L6-1</f>
         <v>0.90119931467732717</v>
       </c>
       <c r="Q24" s="8">
-        <f t="shared" ref="Q24" si="137">Q6/M6-1</f>
+        <f t="shared" ref="Q24" si="139">Q6/M6-1</f>
         <v>0.51905334937825898</v>
       </c>
       <c r="R24" s="8">
-        <f t="shared" ref="R24" si="138">R6/N6-1</f>
+        <f t="shared" ref="R24" si="140">R6/N6-1</f>
         <v>5.768098881695094E-2</v>
       </c>
       <c r="S24" s="8">
-        <f t="shared" ref="S24" si="139">S6/O6-1</f>
+        <f t="shared" ref="S24" si="141">S6/O6-1</f>
         <v>2.927509293680286E-2</v>
       </c>
       <c r="T24" s="8">
-        <f t="shared" ref="T24" si="140">T6/P6-1</f>
+        <f t="shared" ref="T24" si="142">T6/P6-1</f>
         <v>0.2009612496245119</v>
       </c>
       <c r="U24" s="8">
-        <f t="shared" ref="U24" si="141">U6/Q6-1</f>
+        <f t="shared" ref="U24" si="143">U6/Q6-1</f>
         <v>-1.8220227092685448E-2</v>
       </c>
       <c r="V24" s="8">
-        <f t="shared" ref="V24" si="142">V6/R6-1</f>
+        <f t="shared" ref="V24" si="144">V6/R6-1</f>
         <v>-0.11992209237618245</v>
       </c>
       <c r="W24" s="8">
-        <f t="shared" ref="W24" si="143">W6/S6-1</f>
+        <f t="shared" ref="W24" si="145">W6/S6-1</f>
         <v>1.2189616252821667E-2</v>
       </c>
       <c r="X24" s="8">
-        <f t="shared" ref="X24" si="144">X6/T6-1</f>
+        <f t="shared" ref="X24" si="146">X6/T6-1</f>
         <v>-0.23911955977988997</v>
       </c>
       <c r="Y24" s="8">
-        <f t="shared" ref="Y24" si="145">Y6/U6-1</f>
+        <f t="shared" ref="Y24" si="147">Y6/U6-1</f>
         <v>4.3033889187733543E-3</v>
       </c>
       <c r="Z24" s="8">
-        <f t="shared" ref="Z24" si="146">Z6/V6-1</f>
+        <f t="shared" ref="Z24" si="148">Z6/V6-1</f>
         <v>-3.54094214353462E-2</v>
       </c>
       <c r="AA24" s="8">
-        <f t="shared" ref="AA24" si="147">AA6/W6-1</f>
+        <f t="shared" ref="AA24" si="149">AA6/W6-1</f>
         <v>-8.8760035682426519E-2</v>
       </c>
       <c r="AB24" s="8">
-        <f t="shared" ref="AB24" si="148">AB6/X6-1</f>
+        <f t="shared" ref="AB24" si="150">AB6/X6-1</f>
         <v>-0.16929651545036162</v>
       </c>
       <c r="AC24" s="8">
-        <f t="shared" ref="AC24" si="149">AC6/Y6-1</f>
+        <f t="shared" ref="AC24" si="151">AC6/Y6-1</f>
         <v>6.3470808784145794E-2</v>
       </c>
       <c r="AD24" s="8">
-        <f t="shared" ref="AD24" si="150">AD6/Z6-1</f>
+        <f t="shared" ref="AD24" si="152">AD6/Z6-1</f>
         <v>-0.16289741068502139</v>
       </c>
       <c r="AE24" s="8">
-        <f t="shared" ref="AE24" si="151">AE6/AA6-1</f>
+        <f t="shared" ref="AE24" si="153">AE6/AA6-1</f>
         <v>-0.10115842714961654</v>
       </c>
       <c r="AF24" s="8">
-        <f t="shared" ref="AF24" si="152">AF6/AB6-1</f>
+        <f t="shared" ref="AF24" si="154">AF6/AB6-1</f>
         <v>2.8096557182429871E-2</v>
       </c>
       <c r="AG24" s="8">
-        <f t="shared" ref="AG24" si="153">AG6/AC6-1</f>
+        <f t="shared" ref="AG24" si="155">AG6/AC6-1</f>
         <v>-0.13170486023671624</v>
       </c>
       <c r="AH24" s="8">
-        <f t="shared" ref="AH24" si="154">AH6/AD6-1</f>
+        <f t="shared" ref="AH24" si="156">AH6/AD6-1</f>
         <v>0.1272513703993734</v>
       </c>
       <c r="AI24" s="8">
-        <f t="shared" ref="AI24" si="155">AI6/AE6-1</f>
-        <v>-2.8861862406970418E-2</v>
+        <f t="shared" ref="AI24" si="157">AI6/AE6-1</f>
+        <v>-9.4390996551099171E-3</v>
       </c>
       <c r="AJ24" s="8">
-        <f t="shared" ref="AJ24" si="156">AJ6/AF6-1</f>
+        <f t="shared" ref="AJ24" si="158">AJ6/AF6-1</f>
         <v>-1.0000000000000009E-2</v>
       </c>
       <c r="AK24" s="8">
-        <f t="shared" ref="AK24" si="157">AK6/AG6-1</f>
+        <f t="shared" ref="AK24" si="159">AK6/AG6-1</f>
         <v>7.0000000000000062E-2</v>
       </c>
       <c r="AL24" s="8">
-        <f t="shared" ref="AL24" si="158">AL6/AH6-1</f>
+        <f t="shared" ref="AL24" si="160">AL6/AH6-1</f>
         <v>9.000000000000008E-2</v>
       </c>
       <c r="AM24" s="8"/>
@@ -5107,67 +5139,67 @@
         <v>5.1867713537949056E-2</v>
       </c>
       <c r="AR24" s="8">
-        <f t="shared" ref="AR24:BA24" si="159">AR6/AQ6-1</f>
+        <f t="shared" ref="AR24:BA24" si="161">AR6/AQ6-1</f>
         <v>0.29427731282515257</v>
       </c>
       <c r="AS24" s="8">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>2.0855178841896693E-2</v>
       </c>
       <c r="AT24" s="8">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>-5.5409723807349986E-2</v>
       </c>
       <c r="AU24" s="8">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>-8.2885277593185425E-2</v>
       </c>
       <c r="AV24" s="8">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>-4.920624464791501E-2</v>
       </c>
       <c r="AW24" s="8">
-        <f t="shared" si="159"/>
-        <v>2.18574199806012E-2</v>
+        <f t="shared" si="161"/>
+        <v>2.9270472495496636E-2</v>
       </c>
       <c r="AX24" s="8">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="AY24" s="8">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AZ24" s="8">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="BA24" s="8">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BB24" s="8">
-        <f t="shared" ref="BB24" si="160">BB6/BA6-1</f>
+        <f t="shared" ref="BB24" si="162">BB6/BA6-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BC24" s="8">
-        <f t="shared" ref="BC24" si="161">BC6/BB6-1</f>
+        <f t="shared" ref="BC24" si="163">BC6/BB6-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BD24" s="8">
-        <f t="shared" ref="BD24" si="162">BD6/BC6-1</f>
+        <f t="shared" ref="BD24" si="164">BD6/BC6-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BE24" s="8">
-        <f t="shared" ref="BE24" si="163">BE6/BD6-1</f>
+        <f t="shared" ref="BE24" si="165">BE6/BD6-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BF24" s="8">
-        <f t="shared" ref="BF24:BG24" si="164">BF6/BE6-1</f>
+        <f t="shared" ref="BF24:BG24" si="166">BF6/BE6-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BG24" s="8">
-        <f t="shared" si="164"/>
+        <f t="shared" si="166"/>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
@@ -5180,220 +5212,220 @@
         <v>0.41833688699360339</v>
       </c>
       <c r="D25" s="11">
-        <f t="shared" ref="D25:N25" si="165">D8/D6</f>
+        <f t="shared" ref="D25:N25" si="167">D8/D6</f>
         <v>0.43545795393679693</v>
       </c>
       <c r="E25" s="11">
-        <f t="shared" si="165"/>
+        <f t="shared" si="167"/>
         <v>0.45825335892514396</v>
       </c>
       <c r="F25" s="11">
-        <f t="shared" si="165"/>
+        <f t="shared" si="167"/>
         <v>0.42579699523635028</v>
       </c>
       <c r="G25" s="11">
-        <f t="shared" si="165"/>
+        <f t="shared" si="167"/>
         <v>0.39343271555197412</v>
       </c>
       <c r="H25" s="11">
-        <f t="shared" si="165"/>
+        <f t="shared" si="167"/>
         <v>0.43006660323501428</v>
       </c>
       <c r="I25" s="11">
-        <f t="shared" si="165"/>
+        <f t="shared" si="167"/>
         <v>0.45098039215686275</v>
       </c>
       <c r="J25" s="11">
-        <f t="shared" si="165"/>
+        <f t="shared" si="167"/>
         <v>0.42250169952413319</v>
       </c>
       <c r="K25" s="11">
-        <f t="shared" si="165"/>
+        <f t="shared" si="167"/>
         <v>0.40491015833481592</v>
       </c>
       <c r="L25" s="11">
-        <f t="shared" si="165"/>
+        <f t="shared" si="167"/>
         <v>0.41690462592804112</v>
       </c>
       <c r="M25" s="11">
-        <f t="shared" si="165"/>
+        <f t="shared" si="167"/>
         <v>0.44043321299638993</v>
       </c>
       <c r="N25" s="11">
-        <f t="shared" si="165"/>
+        <f t="shared" si="167"/>
         <v>0.47527957622130662</v>
       </c>
       <c r="O25" s="11">
-        <f t="shared" ref="O25:R25" si="166">O8/O6</f>
+        <f t="shared" ref="O25:R25" si="168">O8/O6</f>
         <v>0.46375464684014872</v>
       </c>
       <c r="P25" s="11">
-        <f t="shared" si="166"/>
+        <f t="shared" si="168"/>
         <v>0.49774707119255029</v>
       </c>
       <c r="Q25" s="11">
-        <f t="shared" si="166"/>
+        <f t="shared" si="168"/>
         <v>0.46976498547663054</v>
       </c>
       <c r="R25" s="11">
-        <f t="shared" si="166"/>
+        <f t="shared" si="168"/>
         <v>0.46410684474123537</v>
       </c>
       <c r="S25" s="11">
-        <f t="shared" ref="S25:AH25" si="167">S8/S6</f>
+        <f t="shared" ref="S25:AH25" si="169">S8/S6</f>
         <v>0.47765237020316026</v>
       </c>
       <c r="T25" s="11">
-        <f t="shared" si="167"/>
+        <f t="shared" si="169"/>
         <v>0.44797398699349678</v>
       </c>
       <c r="U25" s="11">
-        <f t="shared" si="167"/>
+        <f t="shared" si="169"/>
         <v>0.47310381925766543</v>
       </c>
       <c r="V25" s="11">
-        <f t="shared" si="167"/>
+        <f t="shared" si="169"/>
         <v>0.39234903572557706</v>
       </c>
       <c r="W25" s="11">
-        <f t="shared" si="167"/>
+        <f t="shared" si="169"/>
         <v>0.42387749033600952</v>
       </c>
       <c r="X25" s="11">
-        <f t="shared" si="167"/>
+        <f t="shared" si="169"/>
         <v>0.4326101249178172</v>
       </c>
       <c r="Y25" s="11">
-        <f t="shared" si="167"/>
+        <f t="shared" si="169"/>
         <v>0.46009641135511514</v>
       </c>
       <c r="Z25" s="11">
-        <f t="shared" si="167"/>
+        <f t="shared" si="169"/>
         <v>0.41953457882661427</v>
       </c>
       <c r="AA25" s="11">
-        <f t="shared" si="167"/>
+        <f t="shared" si="169"/>
         <v>0.46124979605155819</v>
       </c>
       <c r="AB25" s="11">
-        <f t="shared" si="167"/>
+        <f t="shared" si="169"/>
         <v>0.44360902255639095</v>
       </c>
       <c r="AC25" s="11">
-        <f t="shared" si="167"/>
+        <f t="shared" si="169"/>
         <v>0.48249811130697562</v>
       </c>
       <c r="AD25" s="11">
-        <f t="shared" si="167"/>
+        <f t="shared" si="169"/>
         <v>0.40328895849647611</v>
       </c>
       <c r="AE25" s="11">
-        <f t="shared" si="167"/>
+        <f t="shared" si="169"/>
         <v>0.438192049373752</v>
       </c>
       <c r="AF25" s="11">
-        <f t="shared" si="167"/>
+        <f t="shared" si="169"/>
         <v>0.43764434180138573</v>
       </c>
       <c r="AG25" s="11">
-        <f t="shared" si="167"/>
+        <f t="shared" si="169"/>
         <v>0.43445475638051045</v>
       </c>
       <c r="AH25" s="11">
-        <f t="shared" si="167"/>
+        <f t="shared" si="169"/>
         <v>0.4369572768322334</v>
       </c>
       <c r="AI25" s="11">
-        <f t="shared" ref="AI25:AL25" si="168">AI8/AI6</f>
-        <v>0.45</v>
+        <f t="shared" ref="AI25:AL25" si="170">AI8/AI6</f>
+        <v>0.46454095656954364</v>
       </c>
       <c r="AJ25" s="11">
-        <f t="shared" si="168"/>
+        <f t="shared" si="170"/>
         <v>0.44</v>
       </c>
       <c r="AK25" s="11">
-        <f t="shared" si="168"/>
+        <f t="shared" si="170"/>
         <v>0.44000000000000006</v>
       </c>
       <c r="AL25" s="11">
-        <f t="shared" si="168"/>
+        <f t="shared" si="170"/>
         <v>0.44000000000000006</v>
       </c>
       <c r="AM25" s="11"/>
       <c r="AO25" s="11">
-        <f t="shared" ref="AO25:AQ25" si="169">AO8/AO6</f>
+        <f t="shared" ref="AO25:AQ25" si="171">AO8/AO6</f>
         <v>0.43025505716798595</v>
       </c>
       <c r="AP25" s="11">
-        <f t="shared" si="169"/>
+        <f t="shared" si="171"/>
         <v>0.41819335395352519</v>
       </c>
       <c r="AQ25" s="11">
-        <f t="shared" si="169"/>
+        <f t="shared" si="171"/>
         <v>0.4311995777727512</v>
       </c>
       <c r="AR25" s="11">
-        <f t="shared" ref="AR25:BA25" si="170">AR8/AR6</f>
+        <f t="shared" ref="AR25:BA25" si="172">AR8/AR6</f>
         <v>0.47174647559128502</v>
       </c>
       <c r="AS25" s="11">
-        <f t="shared" si="170"/>
+        <f t="shared" si="172"/>
         <v>0.45451951609221641</v>
       </c>
       <c r="AT25" s="11">
-        <f t="shared" si="170"/>
+        <f t="shared" si="172"/>
         <v>0.43285205098773621</v>
       </c>
       <c r="AU25" s="11">
-        <f t="shared" si="170"/>
+        <f t="shared" si="172"/>
         <v>0.45412028193136156</v>
       </c>
       <c r="AV25" s="11">
-        <f t="shared" si="170"/>
+        <f t="shared" si="172"/>
         <v>0.43695441319107664</v>
       </c>
       <c r="AW25" s="11">
-        <f t="shared" si="170"/>
-        <v>0.45</v>
+        <f t="shared" si="172"/>
+        <v>0.45000000000000007</v>
       </c>
       <c r="AX25" s="11">
-        <f t="shared" si="170"/>
+        <f t="shared" si="172"/>
         <v>0.46</v>
       </c>
       <c r="AY25" s="11">
-        <f t="shared" si="170"/>
+        <f t="shared" si="172"/>
         <v>0.47</v>
       </c>
       <c r="AZ25" s="11">
-        <f t="shared" si="170"/>
-        <v>0.47000000000000003</v>
+        <f t="shared" si="172"/>
+        <v>0.47</v>
       </c>
       <c r="BA25" s="11">
-        <f t="shared" si="170"/>
+        <f t="shared" si="172"/>
         <v>0.47</v>
       </c>
       <c r="BB25" s="11">
-        <f t="shared" ref="BB25:BF25" si="171">BB8/BB6</f>
+        <f t="shared" ref="BB25:BF25" si="173">BB8/BB6</f>
         <v>0.47</v>
       </c>
       <c r="BC25" s="11">
-        <f t="shared" si="171"/>
+        <f t="shared" si="173"/>
         <v>0.47</v>
       </c>
       <c r="BD25" s="11">
-        <f t="shared" si="171"/>
-        <v>0.47000000000000003</v>
+        <f t="shared" si="173"/>
+        <v>0.47</v>
       </c>
       <c r="BE25" s="11">
-        <f t="shared" si="171"/>
+        <f t="shared" si="173"/>
         <v>0.47</v>
       </c>
       <c r="BF25" s="11">
-        <f t="shared" si="171"/>
+        <f t="shared" si="173"/>
         <v>0.47</v>
       </c>
       <c r="BG25" s="11">
-        <f t="shared" ref="BG25" si="172">BG8/BG6</f>
+        <f t="shared" ref="BG25" si="174">BG8/BG6</f>
         <v>0.47</v>
       </c>
     </row>
@@ -5406,221 +5438,221 @@
         <v>9.8720682302771826E-2</v>
       </c>
       <c r="D26" s="11">
-        <f t="shared" ref="D26:N26" si="173">D13/D6</f>
+        <f t="shared" ref="D26:N26" si="175">D13/D6</f>
         <v>-0.18050348152115703</v>
       </c>
       <c r="E26" s="11">
-        <f t="shared" si="173"/>
+        <f t="shared" si="175"/>
         <v>-0.10364683301343568</v>
       </c>
       <c r="F26" s="11">
-        <f t="shared" si="173"/>
+        <f t="shared" si="175"/>
         <v>3.6643459142540974E-4</v>
       </c>
       <c r="G26" s="11">
-        <f t="shared" si="173"/>
+        <f t="shared" si="175"/>
         <v>0.1379935535858178</v>
       </c>
       <c r="H26" s="11">
-        <f t="shared" si="173"/>
+        <f t="shared" si="175"/>
         <v>-0.10941960038058998</v>
       </c>
       <c r="I26" s="11">
-        <f t="shared" si="173"/>
+        <f t="shared" si="175"/>
         <v>-5.8439061899269465E-2</v>
       </c>
       <c r="J26" s="11">
-        <f t="shared" si="173"/>
+        <f t="shared" si="175"/>
         <v>-8.4296397008837565E-2</v>
       </c>
       <c r="K26" s="11">
-        <f t="shared" si="173"/>
+        <f t="shared" si="175"/>
         <v>0.12008539405799684</v>
       </c>
       <c r="L26" s="11">
-        <f t="shared" si="173"/>
+        <f t="shared" si="175"/>
         <v>-0.30382638492290115</v>
       </c>
       <c r="M26" s="11">
-        <f t="shared" si="173"/>
+        <f t="shared" si="175"/>
         <v>-0.22864019253910939</v>
       </c>
       <c r="N26" s="11">
-        <f t="shared" si="173"/>
+        <f t="shared" si="175"/>
         <v>4.5320776927604486E-2</v>
       </c>
       <c r="O26" s="11">
-        <f t="shared" ref="O26:R26" si="174">O13/O6</f>
+        <f t="shared" ref="O26:R26" si="176">O13/O6</f>
         <v>0.21298017348203224</v>
       </c>
       <c r="P26" s="11">
-        <f t="shared" si="174"/>
+        <f t="shared" si="176"/>
         <v>3.6948032442174865E-2</v>
       </c>
       <c r="Q26" s="11">
-        <f t="shared" si="174"/>
+        <f t="shared" si="176"/>
         <v>4.4362292051755889E-2</v>
       </c>
       <c r="R26" s="11">
-        <f t="shared" si="174"/>
+        <f t="shared" si="176"/>
         <v>-3.2554257095158648E-2</v>
       </c>
       <c r="S26" s="11">
-        <f t="shared" ref="S26:AH26" si="175">S13/S6</f>
+        <f t="shared" ref="S26:AH26" si="177">S13/S6</f>
         <v>0.19969902182091798</v>
       </c>
       <c r="T26" s="11">
-        <f t="shared" si="175"/>
+        <f t="shared" si="177"/>
         <v>2.5262631315657886E-2</v>
       </c>
       <c r="U26" s="11">
-        <f t="shared" si="175"/>
+        <f t="shared" si="177"/>
         <v>1.8827326519634213E-2</v>
       </c>
       <c r="V26" s="11">
-        <f t="shared" si="175"/>
+        <f t="shared" si="177"/>
         <v>-0.18969332911792583</v>
       </c>
       <c r="W26" s="11">
-        <f t="shared" si="175"/>
+        <f t="shared" si="177"/>
         <v>0.12845673505798394</v>
       </c>
       <c r="X26" s="11">
-        <f t="shared" si="175"/>
+        <f t="shared" si="177"/>
         <v>-0.18803418803418809</v>
       </c>
       <c r="Y26" s="11">
-        <f t="shared" si="175"/>
+        <f t="shared" si="177"/>
         <v>-5.7043385109801781E-2</v>
       </c>
       <c r="Z26" s="11">
-        <f t="shared" si="175"/>
+        <f t="shared" si="177"/>
         <v>-9.3084234677154862E-2</v>
       </c>
       <c r="AA26" s="11">
-        <f t="shared" si="175"/>
+        <f t="shared" si="177"/>
         <v>0.13003752651329742</v>
       </c>
       <c r="AB26" s="11">
-        <f t="shared" si="175"/>
+        <f t="shared" si="177"/>
         <v>-0.28017411950929949</v>
       </c>
       <c r="AC26" s="11">
-        <f t="shared" si="175"/>
+        <f t="shared" si="177"/>
         <v>3.1730042810375274E-2</v>
       </c>
       <c r="AD26" s="11">
-        <f t="shared" si="175"/>
+        <f t="shared" si="177"/>
         <v>-0.27173061863743148</v>
       </c>
       <c r="AE26" s="11">
-        <f t="shared" si="175"/>
+        <f t="shared" si="177"/>
         <v>8.7493192956979465E-2</v>
       </c>
       <c r="AF26" s="11">
-        <f t="shared" si="175"/>
+        <f t="shared" si="177"/>
         <v>-0.23518090839107003</v>
       </c>
       <c r="AG26" s="11">
-        <f t="shared" si="175"/>
+        <f t="shared" si="177"/>
         <v>-8.4106728538283233E-3</v>
       </c>
       <c r="AH26" s="11">
-        <f t="shared" si="175"/>
+        <f t="shared" si="177"/>
         <v>-0.11983327544286221</v>
       </c>
       <c r="AI26" s="11">
-        <f t="shared" ref="AI26:AL26" si="176">AI13/AI6</f>
-        <v>0.13693831775700935</v>
+        <f t="shared" ref="AI26:AL26" si="178">AI13/AI6</f>
+        <v>0.18398387392340107</v>
       </c>
       <c r="AJ26" s="11">
-        <f t="shared" si="176"/>
+        <f t="shared" si="178"/>
         <v>-0.20851159788804124</v>
       </c>
       <c r="AK26" s="11">
-        <f t="shared" si="176"/>
+        <f t="shared" si="178"/>
         <v>8.4577270854566469E-3</v>
       </c>
       <c r="AL26" s="11">
-        <f t="shared" si="176"/>
+        <f t="shared" si="178"/>
         <v>-0.10150915678545359</v>
       </c>
       <c r="AM26" s="11"/>
       <c r="AO26" s="11">
-        <f t="shared" ref="AO26:AQ26" si="177">AO13/AO6</f>
+        <f t="shared" ref="AO26:AQ26" si="179">AO13/AO6</f>
         <v>-7.8276165347405252E-3</v>
       </c>
       <c r="AP26" s="11">
-        <f t="shared" si="177"/>
+        <f t="shared" si="179"/>
         <v>4.3619636767387475E-3</v>
       </c>
       <c r="AQ26" s="11">
-        <f t="shared" si="177"/>
+        <f t="shared" si="179"/>
         <v>-2.0583578375933186E-2</v>
       </c>
       <c r="AR26" s="11">
-        <f t="shared" ref="AR26:BA26" si="178">AR13/AR6</f>
+        <f t="shared" ref="AR26:BA26" si="180">AR13/AR6</f>
         <v>9.02365140393801E-2</v>
       </c>
       <c r="AS26" s="11">
-        <f t="shared" si="178"/>
+        <f t="shared" si="180"/>
         <v>5.1244008217301962E-2</v>
       </c>
       <c r="AT26" s="11">
-        <f t="shared" si="178"/>
+        <f t="shared" si="180"/>
         <v>-1.2384462031051981E-2</v>
       </c>
       <c r="AU26" s="11">
-        <f t="shared" si="178"/>
+        <f t="shared" si="180"/>
         <v>-3.1552598643040629E-2</v>
       </c>
       <c r="AV26" s="11">
-        <f t="shared" si="178"/>
+        <f t="shared" si="180"/>
         <v>-3.48482749064708E-2</v>
       </c>
       <c r="AW26" s="11">
-        <f t="shared" si="178"/>
-        <v>2.0174256872608875E-4</v>
+        <f t="shared" si="180"/>
+        <v>1.3125953707773473E-2</v>
       </c>
       <c r="AX26" s="11">
-        <f t="shared" si="178"/>
-        <v>2.3916689096820758E-2</v>
+        <f t="shared" si="180"/>
+        <v>2.8640038673209453E-2</v>
       </c>
       <c r="AY26" s="11">
-        <f t="shared" si="178"/>
-        <v>5.329129141694184E-2</v>
+        <f t="shared" si="180"/>
+        <v>5.7834703866610909E-2</v>
       </c>
       <c r="AZ26" s="11">
-        <f t="shared" si="178"/>
-        <v>6.788757702049629E-2</v>
+        <f t="shared" si="180"/>
+        <v>7.234276786920095E-2</v>
       </c>
       <c r="BA26" s="11">
-        <f t="shared" si="178"/>
-        <v>8.0163189010491423E-2</v>
+        <f t="shared" si="180"/>
+        <v>8.4574701517542095E-2</v>
       </c>
       <c r="BB26" s="11">
-        <f t="shared" ref="BB26:BF26" si="179">BB13/BB6</f>
-        <v>8.2416491079016038E-2</v>
+        <f t="shared" ref="BB26:BF26" si="181">BB13/BB6</f>
+        <v>8.678475346344855E-2</v>
       </c>
       <c r="BC26" s="11">
-        <f t="shared" si="179"/>
-        <v>8.4647701950790424E-2</v>
+        <f t="shared" si="181"/>
+        <v>8.8973138233414767E-2</v>
       </c>
       <c r="BD26" s="11">
-        <f t="shared" si="179"/>
-        <v>8.6857038206174852E-2</v>
+        <f t="shared" si="181"/>
+        <v>9.1140068250734202E-2</v>
       </c>
       <c r="BE26" s="11">
-        <f t="shared" si="179"/>
-        <v>8.9044714302192768E-2</v>
+        <f t="shared" si="181"/>
+        <v>9.3285753856119105E-2</v>
       </c>
       <c r="BF26" s="11">
-        <f t="shared" si="179"/>
-        <v>9.1210942593347652E-2</v>
+        <f t="shared" si="181"/>
+        <v>9.541040332811801E-2</v>
       </c>
       <c r="BG26" s="11">
-        <f t="shared" ref="BG26" si="180">BG13/BG6</f>
-        <v>9.335593335223645E-2</v>
+        <f t="shared" ref="BG26" si="182">BG13/BG6</f>
+        <v>9.7514222903332518E-2</v>
       </c>
       <c r="BI26" t="s">
         <v>40</v>
@@ -5638,205 +5670,205 @@
       <c r="E27" s="11"/>
       <c r="F27" s="11"/>
       <c r="G27" s="11">
-        <f t="shared" ref="G27:R27" si="181">G9/C9-1</f>
+        <f t="shared" ref="G27:R27" si="183">G9/C9-1</f>
         <v>0.10746268656716418</v>
       </c>
       <c r="H27" s="11">
-        <f t="shared" si="181"/>
+        <f t="shared" si="183"/>
         <v>0.13920454545454541</v>
       </c>
       <c r="I27" s="11">
-        <f t="shared" si="181"/>
+        <f t="shared" si="183"/>
         <v>0.25423728813559321</v>
       </c>
       <c r="J27" s="11">
-        <f t="shared" si="181"/>
+        <f t="shared" si="183"/>
         <v>0.30870712401055411</v>
       </c>
       <c r="K27" s="11">
-        <f t="shared" si="181"/>
+        <f t="shared" si="183"/>
         <v>0.41509433962264142</v>
       </c>
       <c r="L27" s="11">
-        <f t="shared" si="181"/>
+        <f t="shared" si="183"/>
         <v>0.23690773067331672</v>
       </c>
       <c r="M27" s="11">
-        <f t="shared" si="181"/>
+        <f t="shared" si="183"/>
         <v>0.30180180180180183</v>
       </c>
       <c r="N27" s="11">
-        <f t="shared" si="181"/>
+        <f t="shared" si="183"/>
         <v>0.10483870967741926</v>
       </c>
       <c r="O27" s="11">
-        <f t="shared" si="181"/>
+        <f t="shared" si="183"/>
         <v>-3.8095238095238182E-3</v>
       </c>
       <c r="P27" s="11">
-        <f t="shared" si="181"/>
+        <f t="shared" si="183"/>
         <v>0.13709677419354827</v>
       </c>
       <c r="Q27" s="11">
-        <f t="shared" si="181"/>
+        <f t="shared" si="183"/>
         <v>-3.8062283737024138E-2</v>
       </c>
       <c r="R27" s="11">
-        <f t="shared" si="181"/>
+        <f t="shared" si="183"/>
         <v>0.2007299270072993</v>
       </c>
       <c r="S27" s="11">
-        <f t="shared" ref="S27" si="182">S9/O9-1</f>
+        <f t="shared" ref="S27" si="184">S9/O9-1</f>
         <v>0.17208413001912048</v>
       </c>
       <c r="T27" s="11">
-        <f t="shared" ref="T27" si="183">T9/P9-1</f>
+        <f t="shared" ref="T27" si="185">T9/P9-1</f>
         <v>0.15070921985815611</v>
       </c>
       <c r="U27" s="11">
-        <f t="shared" ref="U27" si="184">U9/Q9-1</f>
+        <f t="shared" ref="U27" si="186">U9/Q9-1</f>
         <v>0.12410071942446033</v>
       </c>
       <c r="V27" s="11">
-        <f t="shared" ref="V27" si="185">V9/R9-1</f>
+        <f t="shared" ref="V27" si="187">V9/R9-1</f>
         <v>2.2796352583586588E-2</v>
       </c>
       <c r="W27" s="11">
-        <f t="shared" ref="W27" si="186">W9/S9-1</f>
+        <f t="shared" ref="W27" si="188">W9/S9-1</f>
         <v>0.25448613376835261</v>
       </c>
       <c r="X27" s="11">
-        <f t="shared" ref="X27" si="187">X9/T9-1</f>
+        <f t="shared" ref="X27" si="189">X9/T9-1</f>
         <v>0.24499229583975324</v>
       </c>
       <c r="Y27" s="11">
-        <f t="shared" ref="Y27" si="188">Y9/U9-1</f>
+        <f t="shared" ref="Y27" si="190">Y9/U9-1</f>
         <v>0.24479999999999991</v>
       </c>
       <c r="Z27" s="11">
-        <f t="shared" ref="Z27" si="189">Z9/V9-1</f>
+        <f t="shared" ref="Z27" si="191">Z9/V9-1</f>
         <v>-2.6745913818722045E-2</v>
       </c>
       <c r="AA27" s="11">
-        <f t="shared" ref="AA27" si="190">AA9/W9-1</f>
+        <f t="shared" ref="AA27" si="192">AA9/W9-1</f>
         <v>2.9908972691807589E-2</v>
       </c>
       <c r="AB27" s="11">
-        <f t="shared" ref="AB27" si="191">AB9/X9-1</f>
+        <f t="shared" ref="AB27" si="193">AB9/X9-1</f>
         <v>-6.1881188118811936E-3</v>
       </c>
       <c r="AC27" s="11">
-        <f t="shared" ref="AC27" si="192">AC9/Y9-1</f>
+        <f t="shared" ref="AC27" si="194">AC9/Y9-1</f>
         <v>-4.6272493573264684E-2</v>
       </c>
       <c r="AD27" s="11">
-        <f t="shared" ref="AD27" si="193">AD9/Z9-1</f>
+        <f t="shared" ref="AD27" si="195">AD9/Z9-1</f>
         <v>8.0916030534351036E-2</v>
       </c>
       <c r="AE27" s="11">
-        <f t="shared" ref="AE27" si="194">AE9/AA9-1</f>
+        <f t="shared" ref="AE27" si="196">AE9/AA9-1</f>
         <v>2.020202020202011E-2</v>
       </c>
       <c r="AF27" s="11">
-        <f t="shared" ref="AF27" si="195">AF9/AB9-1</f>
+        <f t="shared" ref="AF27" si="197">AF9/AB9-1</f>
         <v>-3.6114570361145626E-2</v>
       </c>
       <c r="AG27" s="11">
-        <f t="shared" ref="AG27" si="196">AG9/AC9-1</f>
+        <f t="shared" ref="AG27" si="198">AG9/AC9-1</f>
         <v>-0.19407008086253374</v>
       </c>
       <c r="AH27" s="11">
-        <f t="shared" ref="AH27" si="197">AH9/AD9-1</f>
+        <f t="shared" ref="AH27" si="199">AH9/AD9-1</f>
         <v>-0.12429378531073443</v>
       </c>
       <c r="AI27" s="11">
-        <f t="shared" ref="AI27" si="198">AI9/AE9-1</f>
-        <v>-0.14000000000000001</v>
+        <f t="shared" ref="AI27" si="200">AI9/AE9-1</f>
+        <v>-0.25990099009900991</v>
       </c>
       <c r="AJ27" s="11">
-        <f t="shared" ref="AJ27" si="199">AJ9/AF9-1</f>
+        <f t="shared" ref="AJ27" si="201">AJ9/AF9-1</f>
         <v>-5.0000000000000044E-2</v>
       </c>
       <c r="AK27" s="11">
-        <f t="shared" ref="AK27" si="200">AK9/AG9-1</f>
+        <f t="shared" ref="AK27" si="202">AK9/AG9-1</f>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AL27" s="11">
-        <f t="shared" ref="AL27" si="201">AL9/AH9-1</f>
+        <f t="shared" ref="AL27" si="203">AL9/AH9-1</f>
         <v>7.0000000000000062E-2</v>
       </c>
       <c r="AM27" s="11"/>
       <c r="AO27" s="11"/>
       <c r="AP27" s="11">
-        <f t="shared" ref="AP27:BA27" si="202">AP9/AO9-1</f>
+        <f t="shared" ref="AP27:BA27" si="204">AP9/AO9-1</f>
         <v>0.20563380281690136</v>
       </c>
       <c r="AQ27" s="11">
-        <f t="shared" si="202"/>
+        <f t="shared" si="204"/>
         <v>0.25408878504672905</v>
       </c>
       <c r="AR27" s="11">
-        <f t="shared" si="202"/>
+        <f t="shared" si="204"/>
         <v>7.1727992547740982E-2</v>
       </c>
       <c r="AS27" s="11">
-        <f t="shared" si="202"/>
+        <f t="shared" si="204"/>
         <v>0.11255975662755335</v>
       </c>
       <c r="AT27" s="11">
-        <f t="shared" si="202"/>
+        <f t="shared" si="204"/>
         <v>0.17578125</v>
       </c>
       <c r="AU27" s="11">
-        <f t="shared" si="202"/>
+        <f t="shared" si="204"/>
         <v>1.1627906976744207E-2</v>
       </c>
       <c r="AV27" s="11">
-        <f t="shared" si="202"/>
+        <f t="shared" si="204"/>
         <v>-8.0459770114942541E-2</v>
       </c>
       <c r="AW27" s="11">
-        <f t="shared" si="202"/>
-        <v>-3.231428571428574E-2</v>
+        <f t="shared" si="204"/>
+        <v>-6.6914285714285704E-2</v>
       </c>
       <c r="AX27" s="11">
-        <f t="shared" si="202"/>
+        <f t="shared" si="204"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AY27" s="11">
-        <f t="shared" si="202"/>
+        <f t="shared" si="204"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AZ27" s="11">
-        <f t="shared" si="202"/>
+        <f t="shared" si="204"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BA27" s="11">
-        <f t="shared" si="202"/>
+        <f t="shared" si="204"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BB27" s="11">
-        <f t="shared" ref="BB27" si="203">BB9/BA9-1</f>
+        <f t="shared" ref="BB27" si="205">BB9/BA9-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BC27" s="11">
-        <f t="shared" ref="BC27" si="204">BC9/BB9-1</f>
+        <f t="shared" ref="BC27" si="206">BC9/BB9-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BD27" s="11">
-        <f t="shared" ref="BD27" si="205">BD9/BC9-1</f>
+        <f t="shared" ref="BD27" si="207">BD9/BC9-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BE27" s="11">
-        <f t="shared" ref="BE27" si="206">BE9/BD9-1</f>
+        <f t="shared" ref="BE27" si="208">BE9/BD9-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BF27" s="11">
-        <f t="shared" ref="BF27:BG27" si="207">BF9/BE9-1</f>
+        <f t="shared" ref="BF27:BG27" si="209">BF9/BE9-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BG27" s="11">
-        <f t="shared" si="207"/>
+        <f t="shared" si="209"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BI27" t="s">
@@ -5855,220 +5887,220 @@
         <v>0.20042643923240938</v>
       </c>
       <c r="D28" s="11">
-        <f t="shared" ref="D28:N28" si="208">D10/D6</f>
+        <f t="shared" ref="D28:N28" si="210">D10/D6</f>
         <v>0.31708623460096413</v>
       </c>
       <c r="E28" s="11">
-        <f t="shared" si="208"/>
+        <f t="shared" si="210"/>
         <v>0.29174664107485604</v>
       </c>
       <c r="F28" s="11">
-        <f t="shared" si="208"/>
+        <f t="shared" si="210"/>
         <v>0.20813484792964457</v>
       </c>
       <c r="G28" s="11">
-        <f t="shared" si="208"/>
+        <f t="shared" si="210"/>
         <v>0.13275584206285257</v>
       </c>
       <c r="H28" s="11">
-        <f t="shared" si="208"/>
+        <f t="shared" si="210"/>
         <v>0.23501427212178877</v>
       </c>
       <c r="I28" s="11">
-        <f t="shared" si="208"/>
+        <f t="shared" si="210"/>
         <v>0.23644752018454437</v>
       </c>
       <c r="J28" s="11">
-        <f t="shared" si="208"/>
+        <f t="shared" si="210"/>
         <v>0.24099252209381375</v>
       </c>
       <c r="K28" s="11">
-        <f t="shared" si="208"/>
+        <f t="shared" si="210"/>
         <v>0.13769791851983634</v>
       </c>
       <c r="L28" s="11">
-        <f t="shared" si="208"/>
+        <f t="shared" si="210"/>
         <v>0.28840662478583667</v>
       </c>
       <c r="M28" s="11">
-        <f t="shared" si="208"/>
+        <f t="shared" si="210"/>
         <v>0.31006819093461691</v>
       </c>
       <c r="N28" s="11">
-        <f t="shared" si="208"/>
+        <f t="shared" si="210"/>
         <v>0.17157151265450263</v>
       </c>
       <c r="O28" s="11">
-        <f t="shared" ref="O28:R28" si="209">O10/O6</f>
+        <f t="shared" ref="O28:R28" si="211">O10/O6</f>
         <v>0.11524163568773235</v>
       </c>
       <c r="P28" s="11">
-        <f t="shared" si="209"/>
+        <f t="shared" si="211"/>
         <v>0.17182337038149598</v>
       </c>
       <c r="Q28" s="11">
-        <f t="shared" si="209"/>
+        <f t="shared" si="211"/>
         <v>0.17744916820702406</v>
       </c>
       <c r="R28" s="11">
-        <f t="shared" si="209"/>
+        <f t="shared" si="211"/>
         <v>0.20367278797996663</v>
       </c>
       <c r="S28" s="11">
-        <f t="shared" ref="S28:AH28" si="210">S10/S6</f>
+        <f t="shared" ref="S28:AH28" si="212">S10/S6</f>
         <v>0.12595936794582394</v>
       </c>
       <c r="T28" s="11">
-        <f t="shared" si="210"/>
+        <f t="shared" si="212"/>
         <v>0.15007503751875936</v>
       </c>
       <c r="U28" s="11">
-        <f t="shared" si="210"/>
+        <f t="shared" si="212"/>
         <v>0.17213555675094136</v>
       </c>
       <c r="V28" s="11">
-        <f t="shared" si="210"/>
+        <f t="shared" si="212"/>
         <v>0.22952892823269047</v>
       </c>
       <c r="W28" s="11">
-        <f t="shared" si="210"/>
+        <f t="shared" si="212"/>
         <v>0.11700862325304788</v>
       </c>
       <c r="X28" s="11">
-        <f t="shared" si="210"/>
+        <f t="shared" si="212"/>
         <v>0.20907297830374755</v>
       </c>
       <c r="Y28" s="11">
-        <f t="shared" si="210"/>
+        <f t="shared" si="212"/>
         <v>0.1783610069630423</v>
       </c>
       <c r="Z28" s="11">
-        <f t="shared" si="210"/>
+        <f t="shared" si="212"/>
         <v>0.19206817436905932</v>
       </c>
       <c r="AA28" s="11">
-        <f t="shared" si="210"/>
+        <f t="shared" si="212"/>
         <v>0.13705335291238374</v>
       </c>
       <c r="AB28" s="11">
-        <f t="shared" si="210"/>
+        <f t="shared" si="212"/>
         <v>0.24455876533438861</v>
       </c>
       <c r="AC28" s="11">
-        <f t="shared" si="210"/>
+        <f t="shared" si="212"/>
         <v>0.18030722739864011</v>
       </c>
       <c r="AD28" s="11">
-        <f t="shared" si="210"/>
+        <f t="shared" si="212"/>
         <v>0.28660924040720437</v>
       </c>
       <c r="AE28" s="11">
-        <f t="shared" si="210"/>
+        <f t="shared" si="212"/>
         <v>0.15719731348702123</v>
       </c>
       <c r="AF28" s="11">
-        <f t="shared" si="210"/>
+        <f t="shared" si="212"/>
         <v>0.24711316397228639</v>
       </c>
       <c r="AG28" s="11">
-        <f t="shared" si="210"/>
+        <f t="shared" si="212"/>
         <v>0.18155452436194897</v>
       </c>
       <c r="AH28" s="11">
-        <f t="shared" si="210"/>
+        <f t="shared" si="212"/>
         <v>0.23549843695727685</v>
       </c>
       <c r="AI28" s="11">
-        <f t="shared" ref="AI28:AL28" si="211">AI10/AI6</f>
-        <v>0.14018691588785046</v>
+        <f t="shared" ref="AI28:AL28" si="213">AI10/AI6</f>
+        <v>0.1196628183983874</v>
       </c>
       <c r="AJ28" s="11">
-        <f t="shared" si="211"/>
+        <f t="shared" si="213"/>
         <v>0.24</v>
       </c>
       <c r="AK28" s="11">
-        <f t="shared" si="211"/>
+        <f t="shared" si="213"/>
         <v>0.17999999999999997</v>
       </c>
       <c r="AL28" s="11">
-        <f t="shared" si="211"/>
+        <f t="shared" si="213"/>
         <v>0.23</v>
       </c>
       <c r="AM28" s="11"/>
       <c r="AO28" s="11">
-        <f t="shared" ref="AO28:AQ28" si="212">AO10/AO6</f>
+        <f t="shared" ref="AO28:AQ28" si="214">AO10/AO6</f>
         <v>0.23817062445030784</v>
       </c>
       <c r="AP28" s="11">
-        <f t="shared" si="212"/>
+        <f t="shared" si="214"/>
         <v>0.19644698231422003</v>
       </c>
       <c r="AQ28" s="11">
-        <f t="shared" si="212"/>
+        <f t="shared" si="214"/>
         <v>0.19867300007539773</v>
       </c>
       <c r="AR28" s="11">
-        <f t="shared" ref="AR28:BA28" si="213">AR10/AR6</f>
+        <f t="shared" ref="AR28:BA28" si="215">AR10/AR6</f>
         <v>0.15845275544681348</v>
       </c>
       <c r="AS28" s="11">
-        <f t="shared" si="213"/>
+        <f t="shared" si="215"/>
         <v>0.15995206573841586</v>
       </c>
       <c r="AT28" s="11">
-        <f t="shared" si="213"/>
+        <f t="shared" si="215"/>
         <v>0.16160212650274877</v>
       </c>
       <c r="AU28" s="11">
-        <f t="shared" si="213"/>
+        <f t="shared" si="215"/>
         <v>0.19142348988867666</v>
       </c>
       <c r="AV28" s="11">
-        <f t="shared" si="213"/>
+        <f t="shared" si="215"/>
         <v>0.19481779132603572</v>
       </c>
       <c r="AW28" s="11">
-        <f t="shared" si="213"/>
-        <v>0.186659667554607</v>
+        <f t="shared" si="215"/>
+        <v>0.17878616685367812</v>
       </c>
       <c r="AX28" s="11">
-        <f t="shared" si="213"/>
-        <v>0.18999999999999997</v>
+        <f t="shared" si="215"/>
+        <v>0.19</v>
       </c>
       <c r="AY28" s="11">
-        <f t="shared" si="213"/>
+        <f t="shared" si="215"/>
         <v>0.18</v>
       </c>
       <c r="AZ28" s="11">
-        <f t="shared" si="213"/>
+        <f t="shared" si="215"/>
         <v>0.17</v>
       </c>
       <c r="BA28" s="11">
-        <f t="shared" si="213"/>
+        <f t="shared" si="215"/>
         <v>0.16</v>
       </c>
       <c r="BB28" s="11">
-        <f t="shared" ref="BB28:BF28" si="214">BB10/BB6</f>
+        <f t="shared" ref="BB28:BF28" si="216">BB10/BB6</f>
         <v>0.16</v>
       </c>
       <c r="BC28" s="11">
-        <f t="shared" si="214"/>
+        <f t="shared" si="216"/>
         <v>0.16</v>
       </c>
       <c r="BD28" s="11">
-        <f t="shared" si="214"/>
+        <f t="shared" si="216"/>
         <v>0.16</v>
       </c>
       <c r="BE28" s="11">
-        <f t="shared" si="214"/>
+        <f t="shared" si="216"/>
         <v>0.16</v>
       </c>
       <c r="BF28" s="11">
-        <f t="shared" si="214"/>
+        <f t="shared" si="216"/>
         <v>0.16</v>
       </c>
       <c r="BG28" s="11">
-        <f t="shared" ref="BG28" si="215">BG10/BG6</f>
+        <f t="shared" ref="BG28" si="217">BG10/BG6</f>
         <v>0.16</v>
       </c>
       <c r="BI28" t="s">
@@ -6076,7 +6108,7 @@
       </c>
       <c r="BJ28" s="4">
         <f>NPV(BJ27,AW17:FY17)</f>
-        <v>1024.2867249429244</v>
+        <v>1103.9054073126847</v>
       </c>
     </row>
     <row r="29" spans="2:181" x14ac:dyDescent="0.3">
@@ -6088,205 +6120,205 @@
       <c r="E29" s="11"/>
       <c r="F29" s="11"/>
       <c r="G29" s="11">
-        <f t="shared" ref="G29:R29" si="216">G11/C11-1</f>
+        <f t="shared" ref="G29:R29" si="218">G11/C11-1</f>
         <v>6.25E-2</v>
       </c>
       <c r="H29" s="11">
-        <f t="shared" si="216"/>
+        <f t="shared" si="218"/>
         <v>0.16019417475728148</v>
       </c>
       <c r="I29" s="11">
-        <f t="shared" si="216"/>
+        <f t="shared" si="218"/>
         <v>0.27272727272727293</v>
       </c>
       <c r="J29" s="11">
-        <f t="shared" si="216"/>
+        <f t="shared" si="218"/>
         <v>0.33644859813084138</v>
       </c>
       <c r="K29" s="11">
-        <f t="shared" si="216"/>
+        <f t="shared" si="218"/>
         <v>0.26890756302521002</v>
       </c>
       <c r="L29" s="11">
-        <f t="shared" si="216"/>
+        <f t="shared" si="218"/>
         <v>9.205020920502105E-2</v>
       </c>
       <c r="M29" s="11">
-        <f t="shared" si="216"/>
+        <f t="shared" si="218"/>
         <v>0.19172932330827064</v>
       </c>
       <c r="N29" s="11">
-        <f t="shared" si="216"/>
+        <f t="shared" si="218"/>
         <v>0.15384615384615374</v>
       </c>
       <c r="O29" s="11">
-        <f t="shared" si="216"/>
+        <f t="shared" si="218"/>
         <v>0.16556291390728495</v>
       </c>
       <c r="P29" s="11">
-        <f t="shared" si="216"/>
+        <f t="shared" si="218"/>
         <v>0.52490421455938674</v>
       </c>
       <c r="Q29" s="11">
-        <f t="shared" si="216"/>
+        <f t="shared" si="218"/>
         <v>0.20820189274447953</v>
       </c>
       <c r="R29" s="11">
-        <f t="shared" si="216"/>
+        <f t="shared" si="218"/>
         <v>0.19696969696969702</v>
       </c>
       <c r="S29" s="11">
-        <f t="shared" ref="S29" si="217">S11/O11-1</f>
+        <f t="shared" ref="S29" si="219">S11/O11-1</f>
         <v>0.12784090909090917</v>
       </c>
       <c r="T29" s="11">
-        <f t="shared" ref="T29" si="218">T11/P11-1</f>
+        <f t="shared" ref="T29" si="220">T11/P11-1</f>
         <v>0.1080402010050252</v>
       </c>
       <c r="U29" s="11">
-        <f t="shared" ref="U29" si="219">U11/Q11-1</f>
+        <f t="shared" ref="U29" si="221">U11/Q11-1</f>
         <v>0.10704960835509136</v>
       </c>
       <c r="V29" s="11">
-        <f t="shared" ref="V29" si="220">V11/R11-1</f>
+        <f t="shared" ref="V29" si="222">V11/R11-1</f>
         <v>0.11898734177215187</v>
       </c>
       <c r="W29" s="11">
-        <f t="shared" ref="W29" si="221">W11/S11-1</f>
+        <f t="shared" ref="W29" si="223">W11/S11-1</f>
         <v>8.5642317380352662E-2</v>
       </c>
       <c r="X29" s="11">
-        <f t="shared" ref="X29" si="222">X11/T11-1</f>
+        <f t="shared" ref="X29" si="224">X11/T11-1</f>
         <v>6.8027210884353817E-3</v>
       </c>
       <c r="Y29" s="11">
-        <f t="shared" ref="Y29" si="223">Y11/U11-1</f>
+        <f t="shared" ref="Y29" si="225">Y11/U11-1</f>
         <v>0.14858490566037741</v>
       </c>
       <c r="Z29" s="11">
-        <f t="shared" ref="Z29" si="224">Z11/V11-1</f>
+        <f t="shared" ref="Z29" si="226">Z11/V11-1</f>
         <v>-0.26923076923076938</v>
       </c>
       <c r="AA29" s="11">
-        <f t="shared" ref="AA29" si="225">AA11/W11-1</f>
+        <f t="shared" ref="AA29" si="227">AA11/W11-1</f>
         <v>-7.6566125290023268E-2</v>
       </c>
       <c r="AB29" s="11">
-        <f t="shared" ref="AB29" si="226">AB11/X11-1</f>
+        <f t="shared" ref="AB29" si="228">AB11/X11-1</f>
         <v>-8.1081081081081141E-2</v>
       </c>
       <c r="AC29" s="11">
-        <f t="shared" ref="AC29" si="227">AC11/Y11-1</f>
+        <f t="shared" ref="AC29" si="229">AC11/Y11-1</f>
         <v>-0.31827515400410678</v>
       </c>
       <c r="AD29" s="11">
-        <f t="shared" ref="AD29" si="228">AD11/Z11-1</f>
+        <f t="shared" ref="AD29" si="230">AD11/Z11-1</f>
         <v>-0.12074303405572751</v>
       </c>
       <c r="AE29" s="11">
-        <f t="shared" ref="AE29" si="229">AE11/AA11-1</f>
+        <f t="shared" ref="AE29" si="231">AE11/AA11-1</f>
         <v>-0.35175879396984921</v>
       </c>
       <c r="AF29" s="11">
-        <f t="shared" ref="AF29" si="230">AF11/AB11-1</f>
+        <f t="shared" ref="AF29" si="232">AF11/AB11-1</f>
         <v>-0.18627450980392146</v>
       </c>
       <c r="AG29" s="11">
-        <f t="shared" ref="AG29" si="231">AG11/AC11-1</f>
+        <f t="shared" ref="AG29" si="233">AG11/AC11-1</f>
         <v>-8.7349397590361533E-2</v>
       </c>
       <c r="AH29" s="11">
-        <f t="shared" ref="AH29" si="232">AH11/AD11-1</f>
+        <f t="shared" ref="AH29" si="234">AH11/AD11-1</f>
         <v>7.3943661971830998E-2</v>
       </c>
       <c r="AI29" s="11">
-        <f t="shared" ref="AI29" si="233">AI11/AE11-1</f>
-        <v>-0.10852713178294571</v>
+        <f t="shared" ref="AI29" si="235">AI11/AE11-1</f>
+        <v>8.5271317829457294E-2</v>
       </c>
       <c r="AJ29" s="11">
-        <f t="shared" ref="AJ29" si="234">AJ11/AF11-1</f>
+        <f t="shared" ref="AJ29" si="236">AJ11/AF11-1</f>
         <v>-5.0000000000000044E-2</v>
       </c>
       <c r="AK29" s="11">
-        <f t="shared" ref="AK29" si="235">AK11/AG11-1</f>
+        <f t="shared" ref="AK29" si="237">AK11/AG11-1</f>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AL29" s="11">
-        <f t="shared" ref="AL29" si="236">AL11/AH11-1</f>
+        <f t="shared" ref="AL29" si="238">AL11/AH11-1</f>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AM29" s="11"/>
       <c r="AO29" s="11"/>
       <c r="AP29" s="11">
-        <f t="shared" ref="AP29:BA29" si="237">AP11/AO11-1</f>
+        <f t="shared" ref="AP29:BA29" si="239">AP11/AO11-1</f>
         <v>0.2063305978898009</v>
       </c>
       <c r="AQ29" s="11">
-        <f t="shared" si="237"/>
+        <f t="shared" si="239"/>
         <v>0.17589893100097176</v>
       </c>
       <c r="AR29" s="11">
-        <f t="shared" si="237"/>
+        <f t="shared" si="239"/>
         <v>0.26280991735537196</v>
       </c>
       <c r="AS29" s="11">
-        <f t="shared" si="237"/>
+        <f t="shared" si="239"/>
         <v>0.11518324607329866</v>
       </c>
       <c r="AT29" s="11">
-        <f t="shared" si="237"/>
+        <f t="shared" si="239"/>
         <v>-1.1150234741784226E-2</v>
       </c>
       <c r="AU29" s="11">
-        <f t="shared" si="237"/>
+        <f t="shared" si="239"/>
         <v>-0.15608308605341248</v>
       </c>
       <c r="AV29" s="11">
-        <f t="shared" si="237"/>
+        <f t="shared" si="239"/>
         <v>-0.15752461322081568</v>
       </c>
       <c r="AW29" s="11">
-        <f t="shared" si="237"/>
-        <v>-2.2003338898163416E-2</v>
+        <f t="shared" si="239"/>
+        <v>1.9732888146911653E-2</v>
       </c>
       <c r="AX29" s="11">
-        <f t="shared" si="237"/>
+        <f t="shared" si="239"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AY29" s="11">
-        <f t="shared" si="237"/>
+        <f t="shared" si="239"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AZ29" s="11">
-        <f t="shared" si="237"/>
+        <f t="shared" si="239"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BA29" s="11">
-        <f t="shared" si="237"/>
+        <f t="shared" si="239"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BB29" s="11">
-        <f t="shared" ref="BB29" si="238">BB11/BA11-1</f>
+        <f t="shared" ref="BB29" si="240">BB11/BA11-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BC29" s="11">
-        <f t="shared" ref="BC29" si="239">BC11/BB11-1</f>
+        <f t="shared" ref="BC29" si="241">BC11/BB11-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BD29" s="11">
-        <f t="shared" ref="BD29" si="240">BD11/BC11-1</f>
+        <f t="shared" ref="BD29" si="242">BD11/BC11-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BE29" s="11">
-        <f t="shared" ref="BE29" si="241">BE11/BD11-1</f>
+        <f t="shared" ref="BE29" si="243">BE11/BD11-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BF29" s="11">
-        <f t="shared" ref="BF29:BG29" si="242">BF11/BE11-1</f>
+        <f t="shared" ref="BF29:BG29" si="244">BF11/BE11-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BG29" s="11">
-        <f t="shared" si="242"/>
+        <f t="shared" si="244"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BI29" t="s">
@@ -6294,7 +6326,7 @@
       </c>
       <c r="BJ29" s="4">
         <f>Main!D8</f>
-        <v>227.6</v>
+        <v>363.5</v>
       </c>
     </row>
     <row r="30" spans="2:181" x14ac:dyDescent="0.3">
@@ -6306,220 +6338,220 @@
         <v>0</v>
       </c>
       <c r="D30" s="11">
-        <f t="shared" ref="D30:N30" si="243">D16/D15</f>
+        <f t="shared" ref="D30:N30" si="245">D16/D15</f>
         <v>-1.8749999999999992E-2</v>
       </c>
       <c r="E30" s="11">
-        <f t="shared" si="243"/>
+        <f t="shared" si="245"/>
         <v>-1.8867924528301893E-2</v>
       </c>
       <c r="F30" s="11">
-        <f t="shared" si="243"/>
+        <f t="shared" si="245"/>
         <v>5.2631578947368265E-2</v>
       </c>
       <c r="G30" s="11">
-        <f t="shared" si="243"/>
+        <f t="shared" si="245"/>
         <v>3.9001560062402525E-2</v>
       </c>
       <c r="H30" s="11">
-        <f t="shared" si="243"/>
+        <f t="shared" si="245"/>
         <v>8.6580086580086528E-3</v>
       </c>
       <c r="I30" s="11">
-        <f t="shared" si="243"/>
+        <f t="shared" si="245"/>
         <v>-6.0150375939849683E-2</v>
       </c>
       <c r="J30" s="11">
-        <f t="shared" si="243"/>
+        <f t="shared" si="245"/>
         <v>-2.0689655172413786E-2</v>
       </c>
       <c r="K30" s="11">
-        <f t="shared" si="243"/>
+        <f t="shared" si="245"/>
         <v>2.3448275862068955E-2</v>
       </c>
       <c r="L30" s="11">
-        <f t="shared" si="243"/>
+        <f t="shared" si="245"/>
         <v>3.3271719038817017E-2</v>
       </c>
       <c r="M30" s="11">
-        <f t="shared" si="243"/>
+        <f t="shared" si="245"/>
         <v>-3.5149384885764519E-3</v>
       </c>
       <c r="N30" s="11">
-        <f t="shared" si="243"/>
+        <f t="shared" si="245"/>
         <v>0</v>
       </c>
       <c r="O30" s="11">
-        <f t="shared" ref="O30:R30" si="244">O16/O15</f>
+        <f t="shared" ref="O30:R30" si="246">O16/O15</f>
         <v>6.4310954063604223E-2</v>
       </c>
       <c r="P30" s="11">
-        <f t="shared" si="244"/>
+        <f t="shared" si="246"/>
         <v>-0.60747663551401798</v>
       </c>
       <c r="Q30" s="11">
-        <f t="shared" si="244"/>
+        <f t="shared" si="246"/>
         <v>4.7872340425532033E-2</v>
       </c>
       <c r="R30" s="11">
-        <f t="shared" si="244"/>
+        <f t="shared" si="246"/>
         <v>0.36428571428571382</v>
       </c>
       <c r="S30" s="11">
-        <f t="shared" ref="S30:AH30" si="245">S16/S15</f>
+        <f t="shared" ref="S30:AH30" si="247">S16/S15</f>
         <v>5.7926829268292686E-2</v>
       </c>
       <c r="T30" s="11">
-        <f t="shared" si="245"/>
+        <f t="shared" si="247"/>
         <v>-0.10126582278480985</v>
       </c>
       <c r="U30" s="11">
-        <f t="shared" si="245"/>
+        <f t="shared" si="247"/>
         <v>0.80769230769230782</v>
       </c>
       <c r="V30" s="11">
-        <f t="shared" si="245"/>
+        <f t="shared" si="247"/>
         <v>5.1851851851851899E-2</v>
       </c>
       <c r="W30" s="11">
-        <f t="shared" si="245"/>
+        <f t="shared" si="247"/>
         <v>0.32647584973166366</v>
       </c>
       <c r="X30" s="11">
-        <f t="shared" si="245"/>
+        <f t="shared" si="247"/>
         <v>0.46315789473684199</v>
       </c>
       <c r="Y30" s="11">
-        <f t="shared" si="245"/>
+        <f t="shared" si="247"/>
         <v>-0.33146067415730368</v>
       </c>
       <c r="Z30" s="11">
-        <f t="shared" si="245"/>
+        <f t="shared" si="247"/>
         <v>3.9877300613496994E-2</v>
       </c>
       <c r="AA30" s="11">
-        <f t="shared" si="245"/>
+        <f t="shared" si="247"/>
         <v>0.12917115177610336</v>
       </c>
       <c r="AB30" s="11">
-        <f t="shared" si="245"/>
+        <f t="shared" si="247"/>
         <v>9.9573257467994326E-3</v>
       </c>
       <c r="AC30" s="11">
-        <f t="shared" si="245"/>
+        <f t="shared" si="247"/>
         <v>0.70634920634920506</v>
       </c>
       <c r="AD30" s="11">
-        <f t="shared" si="245"/>
+        <f t="shared" si="247"/>
         <v>0.14767255216693417</v>
       </c>
       <c r="AE30" s="11">
-        <f t="shared" si="245"/>
+        <f t="shared" si="247"/>
         <v>-0.1454545454545455</v>
       </c>
       <c r="AF30" s="11">
-        <f t="shared" si="245"/>
+        <f t="shared" si="247"/>
         <v>-0.18644067796610173</v>
       </c>
       <c r="AG30" s="11">
-        <f t="shared" si="245"/>
+        <f t="shared" si="247"/>
         <v>-3.2499999999999774</v>
       </c>
       <c r="AH30" s="11">
-        <f t="shared" si="245"/>
+        <f t="shared" si="247"/>
         <v>-0.10174418604651154</v>
       </c>
       <c r="AI30" s="11">
-        <f t="shared" ref="AI30:AL30" si="246">AI16/AI15</f>
-        <v>6.8155175704042975E-2</v>
+        <f t="shared" ref="AI30:AL30" si="248">AI16/AI15</f>
+        <v>8.1372549019607901E-2</v>
       </c>
       <c r="AJ30" s="11">
-        <f t="shared" si="246"/>
+        <f t="shared" si="248"/>
         <v>0.1</v>
       </c>
       <c r="AK30" s="11">
-        <f t="shared" si="246"/>
+        <f t="shared" si="248"/>
         <v>0.1</v>
       </c>
       <c r="AL30" s="11">
-        <f t="shared" si="246"/>
+        <f t="shared" si="248"/>
         <v>0.1</v>
       </c>
       <c r="AM30" s="11"/>
       <c r="AO30" s="11">
-        <f t="shared" ref="AO30:AQ30" si="247">AO16/AO15</f>
+        <f t="shared" ref="AO30:AQ30" si="249">AO16/AO15</f>
         <v>-6.8493150684931614E-2</v>
       </c>
       <c r="AP30" s="11">
-        <f t="shared" si="247"/>
+        <f t="shared" si="249"/>
         <v>-2.8461538461535953</v>
       </c>
       <c r="AQ30" s="11">
-        <f t="shared" si="247"/>
+        <f t="shared" si="249"/>
         <v>-4.9751243781094041E-3</v>
       </c>
       <c r="AR30" s="11">
-        <f t="shared" ref="AR30:BA30" si="248">AR16/AR15</f>
+        <f t="shared" ref="AR30:BA30" si="250">AR16/AR15</f>
         <v>-1.0191082802547781E-2</v>
       </c>
       <c r="AS30" s="11">
-        <f t="shared" si="248"/>
+        <f t="shared" si="250"/>
         <v>1.7391304347826087E-2</v>
       </c>
       <c r="AT30" s="11">
-        <f t="shared" si="248"/>
+        <f t="shared" si="250"/>
         <v>3.3409090909093506</v>
       </c>
       <c r="AU30" s="11">
-        <f t="shared" si="248"/>
+        <f t="shared" si="250"/>
         <v>-0.40590405904059085</v>
       </c>
       <c r="AV30" s="11">
-        <f t="shared" si="248"/>
+        <f t="shared" si="250"/>
         <v>-0.21314741035856591</v>
       </c>
       <c r="AW30" s="11">
-        <f t="shared" si="248"/>
-        <v>-8.1406404064800011</v>
+        <f t="shared" si="250"/>
+        <v>3.0144697581489938E-3</v>
       </c>
       <c r="AX30" s="11">
-        <f t="shared" si="248"/>
+        <f t="shared" si="250"/>
         <v>0.2</v>
       </c>
       <c r="AY30" s="11">
-        <f t="shared" si="248"/>
+        <f t="shared" si="250"/>
+        <v>0.2</v>
+      </c>
+      <c r="AZ30" s="11">
+        <f t="shared" si="250"/>
+        <v>0.2</v>
+      </c>
+      <c r="BA30" s="11">
+        <f t="shared" si="250"/>
+        <v>0.2</v>
+      </c>
+      <c r="BB30" s="11">
+        <f t="shared" ref="BB30:BF30" si="251">BB16/BB15</f>
+        <v>0.2</v>
+      </c>
+      <c r="BC30" s="11">
+        <f t="shared" si="251"/>
+        <v>0.2</v>
+      </c>
+      <c r="BD30" s="11">
+        <f t="shared" si="251"/>
+        <v>0.2</v>
+      </c>
+      <c r="BE30" s="11">
+        <f t="shared" si="251"/>
         <v>0.19999999999999998</v>
       </c>
-      <c r="AZ30" s="11">
-        <f t="shared" si="248"/>
-        <v>0.2</v>
-      </c>
-      <c r="BA30" s="11">
-        <f t="shared" si="248"/>
-        <v>0.2</v>
-      </c>
-      <c r="BB30" s="11">
-        <f t="shared" ref="BB30:BF30" si="249">BB16/BB15</f>
-        <v>0.2</v>
-      </c>
-      <c r="BC30" s="11">
-        <f t="shared" si="249"/>
-        <v>0.2</v>
-      </c>
-      <c r="BD30" s="11">
-        <f t="shared" si="249"/>
-        <v>0.20000000000000004</v>
-      </c>
-      <c r="BE30" s="11">
-        <f t="shared" si="249"/>
-        <v>0.2</v>
-      </c>
       <c r="BF30" s="11">
-        <f t="shared" si="249"/>
-        <v>0.2</v>
+        <f t="shared" si="251"/>
+        <v>0.19999999999999998</v>
       </c>
       <c r="BG30" s="11">
-        <f t="shared" ref="BG30" si="250">BG16/BG15</f>
+        <f t="shared" ref="BG30" si="252">BG16/BG15</f>
         <v>0.2</v>
       </c>
       <c r="BI30" t="s">
@@ -6527,7 +6559,7 @@
       </c>
       <c r="BJ30" s="4">
         <f>BJ28+BJ29</f>
-        <v>1251.8867249429243</v>
+        <v>1467.4054073126847</v>
       </c>
     </row>
     <row r="31" spans="2:181" x14ac:dyDescent="0.3">
@@ -6539,228 +6571,228 @@
         <v>9.7654584221748358E-2</v>
       </c>
       <c r="D31" s="11">
-        <f t="shared" ref="D31:BA31" si="251">D17/D6</f>
+        <f t="shared" ref="D31:BA31" si="253">D17/D6</f>
         <v>-0.17461167648634182</v>
       </c>
       <c r="E31" s="11">
-        <f t="shared" si="251"/>
+        <f t="shared" si="253"/>
         <v>-0.12955854126679459</v>
       </c>
       <c r="F31" s="11">
-        <f t="shared" si="251"/>
+        <f t="shared" si="253"/>
         <v>-6.5958226456577715E-3</v>
       </c>
       <c r="G31" s="11">
-        <f t="shared" si="251"/>
+        <f t="shared" si="253"/>
         <v>0.12409347300564053</v>
       </c>
       <c r="H31" s="11">
-        <f t="shared" si="251"/>
+        <f t="shared" si="253"/>
         <v>-0.10894386298763091</v>
       </c>
       <c r="I31" s="11">
-        <f t="shared" si="251"/>
+        <f t="shared" si="253"/>
         <v>-5.420991926182233E-2</v>
       </c>
       <c r="J31" s="11">
-        <f t="shared" si="251"/>
+        <f t="shared" si="253"/>
         <v>-0.10061182868796742</v>
       </c>
       <c r="K31" s="11">
-        <f t="shared" si="251"/>
+        <f t="shared" si="253"/>
         <v>0.12595623554527668</v>
       </c>
       <c r="L31" s="11">
-        <f t="shared" si="251"/>
+        <f t="shared" si="253"/>
         <v>-0.29868646487721295</v>
       </c>
       <c r="M31" s="11">
-        <f t="shared" si="251"/>
+        <f t="shared" si="253"/>
         <v>-0.22904131568391484</v>
       </c>
       <c r="N31" s="11">
-        <f t="shared" si="251"/>
+        <f t="shared" si="253"/>
         <v>5.4149499705709259E-2</v>
       </c>
       <c r="O31" s="11">
-        <f t="shared" si="251"/>
+        <f t="shared" si="253"/>
         <v>0.20508054522924415</v>
       </c>
       <c r="P31" s="11">
-        <f t="shared" si="251"/>
+        <f t="shared" si="253"/>
         <v>5.1667167317512801E-2</v>
       </c>
       <c r="Q31" s="11">
-        <f t="shared" si="251"/>
+        <f t="shared" si="253"/>
         <v>4.7266965936097062E-2</v>
       </c>
       <c r="R31" s="11">
-        <f t="shared" si="251"/>
+        <f t="shared" si="253"/>
         <v>-2.4763494713411292E-2</v>
       </c>
       <c r="S31" s="11">
-        <f t="shared" ref="S31:AH31" si="252">S17/S6</f>
+        <f t="shared" ref="S31:AH31" si="254">S17/S6</f>
         <v>0.18600451467268622</v>
       </c>
       <c r="T31" s="11">
-        <f t="shared" si="252"/>
+        <f t="shared" si="254"/>
         <v>2.1760880440220166E-2</v>
       </c>
       <c r="U31" s="11">
-        <f t="shared" si="252"/>
+        <f t="shared" si="254"/>
         <v>-1.3448090371167283E-3</v>
       </c>
       <c r="V31" s="11">
-        <f t="shared" si="252"/>
+        <f t="shared" si="254"/>
         <v>-0.20233955105912091</v>
       </c>
       <c r="W31" s="11">
-        <f t="shared" si="252"/>
+        <f t="shared" si="254"/>
         <v>0.11195361284567353</v>
       </c>
       <c r="X31" s="11">
-        <f t="shared" si="252"/>
+        <f t="shared" si="254"/>
         <v>-0.10059171597633142</v>
       </c>
       <c r="Y31" s="11">
-        <f t="shared" si="252"/>
+        <f t="shared" si="254"/>
         <v>-6.3470808784145641E-2</v>
       </c>
       <c r="Z31" s="11">
-        <f t="shared" si="252"/>
+        <f t="shared" si="254"/>
         <v>-0.10258931497869535</v>
       </c>
       <c r="AA31" s="11">
-        <f t="shared" si="252"/>
+        <f t="shared" si="254"/>
         <v>0.1319954315549029</v>
       </c>
       <c r="AB31" s="11">
-        <f t="shared" si="252"/>
+        <f t="shared" si="254"/>
         <v>-0.27542540561931139</v>
       </c>
       <c r="AC31" s="11">
-        <f t="shared" si="252"/>
+        <f t="shared" si="254"/>
         <v>9.3175522538403981E-3</v>
       </c>
       <c r="AD31" s="11">
-        <f t="shared" si="252"/>
+        <f t="shared" si="254"/>
         <v>-0.20790916209866878</v>
       </c>
       <c r="AE31" s="11">
-        <f t="shared" si="252"/>
+        <f t="shared" si="254"/>
         <v>9.1486658195679776E-2</v>
       </c>
       <c r="AF31" s="11">
-        <f t="shared" si="252"/>
+        <f t="shared" si="254"/>
         <v>-0.26943802925327176</v>
       </c>
       <c r="AG31" s="11">
-        <f t="shared" si="252"/>
+        <f t="shared" si="254"/>
         <v>-9.8607888631090657E-3</v>
       </c>
       <c r="AH31" s="11">
-        <f t="shared" si="252"/>
+        <f t="shared" si="254"/>
         <v>-0.1316429315734631</v>
       </c>
       <c r="AI31" s="11">
-        <f t="shared" ref="AI31:AL31" si="253">AI17/AI6</f>
-        <v>0.12777943925233645</v>
+        <f t="shared" ref="AI31:AL31" si="255">AI17/AI6</f>
+        <v>0.17170606560381155</v>
       </c>
       <c r="AJ31" s="11">
-        <f t="shared" si="253"/>
+        <f t="shared" si="255"/>
         <v>-0.1876604380992371</v>
       </c>
       <c r="AK31" s="11">
-        <f t="shared" si="253"/>
+        <f t="shared" si="255"/>
         <v>7.6119543769109814E-3</v>
       </c>
       <c r="AL31" s="11">
-        <f t="shared" si="253"/>
+        <f t="shared" si="255"/>
         <v>-9.1358241106908239E-2</v>
       </c>
       <c r="AM31" s="11"/>
       <c r="AO31" s="11">
-        <f t="shared" si="251"/>
+        <f t="shared" si="253"/>
         <v>-1.3720316622691272E-2</v>
       </c>
       <c r="AP31" s="11">
-        <f t="shared" si="251"/>
+        <f t="shared" si="253"/>
         <v>-3.9654215243081249E-3</v>
       </c>
       <c r="AQ31" s="11">
-        <f t="shared" si="251"/>
+        <f t="shared" si="253"/>
         <v>-1.5230340043730818E-2</v>
       </c>
       <c r="AR31" s="11">
-        <f t="shared" si="251"/>
+        <f t="shared" si="253"/>
         <v>9.2391937550972775E-2</v>
       </c>
       <c r="AS31" s="11">
-        <f t="shared" si="251"/>
+        <f t="shared" si="253"/>
         <v>3.8689796850034215E-2</v>
       </c>
       <c r="AT31" s="11">
-        <f t="shared" si="251"/>
+        <f t="shared" si="253"/>
         <v>-6.222437020479879E-3</v>
       </c>
       <c r="AU31" s="11">
-        <f t="shared" si="251"/>
+        <f t="shared" si="253"/>
         <v>-2.509716092484025E-2</v>
       </c>
       <c r="AV31" s="11">
-        <f t="shared" si="251"/>
+        <f t="shared" si="253"/>
         <v>-4.2192046556740991E-2</v>
       </c>
       <c r="AW31" s="11">
-        <f t="shared" si="251"/>
-        <v>2.4637821375518535E-3</v>
+        <f t="shared" si="253"/>
+        <v>1.4160109824056655E-2</v>
       </c>
       <c r="AX31" s="11">
-        <f t="shared" si="251"/>
-        <v>1.9151601515512547E-2</v>
+        <f t="shared" si="253"/>
+        <v>2.3016920640967983E-2</v>
       </c>
       <c r="AY31" s="11">
-        <f t="shared" si="251"/>
-        <v>4.2778950097481186E-2</v>
+        <f t="shared" si="253"/>
+        <v>4.6443130107696101E-2</v>
       </c>
       <c r="AZ31" s="11">
-        <f t="shared" si="251"/>
-        <v>5.4642325306474553E-2</v>
+        <f t="shared" si="253"/>
+        <v>5.8234937636003056E-2</v>
       </c>
       <c r="BA31" s="11">
-        <f t="shared" si="251"/>
-        <v>6.4559118465698812E-2</v>
+        <f t="shared" si="253"/>
+        <v>6.8116505822943499E-2</v>
       </c>
       <c r="BB31" s="11">
-        <f t="shared" ref="BB31:BF31" si="254">BB17/BB6</f>
-        <v>6.6439538890394792E-2</v>
+        <f t="shared" ref="BB31:BF31" si="256">BB17/BB6</f>
+        <v>6.9962049875252522E-2</v>
       </c>
       <c r="BC31" s="11">
-        <f t="shared" si="254"/>
-        <v>6.8239255983302105E-2</v>
+        <f t="shared" si="256"/>
+        <v>7.172723254653772E-2</v>
       </c>
       <c r="BD31" s="11">
-        <f t="shared" si="254"/>
-        <v>7.0020840415789307E-2</v>
+        <f t="shared" si="256"/>
+        <v>7.3474621130364126E-2</v>
       </c>
       <c r="BE31" s="11">
-        <f t="shared" si="254"/>
-        <v>7.1784954503838844E-2</v>
+        <f t="shared" si="256"/>
+        <v>7.5204874623172657E-2</v>
       </c>
       <c r="BF31" s="11">
-        <f t="shared" si="254"/>
-        <v>7.3531773325688624E-2</v>
+        <f t="shared" si="256"/>
+        <v>7.6918164816401652E-2</v>
       </c>
       <c r="BG31" s="11">
-        <f t="shared" ref="BG31" si="255">BG17/BG6</f>
-        <v>7.5261466472578878E-2</v>
+        <f t="shared" ref="BG31" si="257">BG17/BG6</f>
+        <v>7.8614658046716218E-2</v>
       </c>
       <c r="BI31" t="s">
         <v>45</v>
       </c>
       <c r="BJ31" s="5">
         <f>BJ30/BA18</f>
-        <v>10.380486939825243</v>
+        <v>12.167540690818281</v>
       </c>
     </row>
     <row r="32" spans="2:181" x14ac:dyDescent="0.3">
@@ -6769,24 +6801,24 @@
       </c>
       <c r="BJ32" s="5">
         <f>Main!D3</f>
-        <v>16.64</v>
+        <v>16.41</v>
       </c>
     </row>
-    <row r="33" spans="2:62" s="14" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="14" t="s">
+    <row r="33" spans="2:62" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="AS33" s="15">
+      <c r="AS33" s="13">
         <v>1188.4000000000001</v>
       </c>
-      <c r="AT33" s="15">
+      <c r="AT33" s="13">
         <f>1002.2</f>
         <v>1002.2</v>
       </c>
-      <c r="AU33" s="15">
+      <c r="AU33" s="13">
         <v>916.3</v>
       </c>
-      <c r="AV33" s="15">
+      <c r="AV33" s="13">
         <v>823.3</v>
       </c>
       <c r="BI33" s="1" t="s">
@@ -6794,21 +6826,21 @@
       </c>
       <c r="BJ33" s="8">
         <f>BJ31/BJ32-1</f>
-        <v>-0.37617265986627146</v>
+        <v>-0.25852890366738079</v>
       </c>
     </row>
     <row r="34" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
         <v>95</v>
       </c>
-      <c r="AV34" s="16">
+      <c r="AV34" s="14">
         <f>Main!D9/Model!AV33</f>
-        <v>2.1610397182072147</v>
-      </c>
-      <c r="BI34" s="12" t="s">
+        <v>1.9622810640106887</v>
+      </c>
+      <c r="BI34" t="s">
         <v>48</v>
       </c>
-      <c r="BJ34" s="13" t="s">
+      <c r="BJ34" s="6" t="s">
         <v>72</v>
       </c>
     </row>
@@ -6818,7 +6850,7 @@
       </c>
       <c r="AV35" s="11">
         <f>AV33/Main!D9-1</f>
-        <v>-0.53725977751598486</v>
+        <v>-0.49038900780293471</v>
       </c>
     </row>
     <row r="37" spans="2:62" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -6842,48 +6874,48 @@
         <v>-60.899999999999949</v>
       </c>
       <c r="AW37" s="7">
-        <f t="shared" ref="AW37:BF37" si="256">AW17</f>
-        <v>3.6339529999999685</v>
+        <f t="shared" ref="AW37:BF37" si="258">AW17</f>
+        <v>21.036952999999944</v>
       </c>
       <c r="AX37" s="7">
-        <f t="shared" si="256"/>
-        <v>30.507446344000009</v>
+        <f t="shared" si="258"/>
+        <v>36.93067034400012</v>
       </c>
       <c r="AY37" s="7">
-        <f t="shared" si="256"/>
-        <v>71.551736802751961</v>
+        <f t="shared" si="258"/>
+        <v>78.243947234752</v>
       </c>
       <c r="AZ37" s="7">
-        <f t="shared" si="256"/>
-        <v>94.136154996821872</v>
+        <f t="shared" si="258"/>
+        <v>101.05320891067797</v>
       </c>
       <c r="BA37" s="7">
-        <f t="shared" si="256"/>
-        <v>113.44491822454722</v>
+        <f t="shared" si="258"/>
+        <v>120.56438296440214</v>
       </c>
       <c r="BB37" s="7">
-        <f t="shared" si="256"/>
-        <v>119.08422543762181</v>
+        <f t="shared" si="258"/>
+        <v>126.30756521746453</v>
       </c>
       <c r="BC37" s="7">
-        <f t="shared" si="256"/>
-        <v>124.75618374999985</v>
+        <f t="shared" si="258"/>
+        <v>132.08426513048201</v>
       </c>
       <c r="BD37" s="7">
-        <f t="shared" si="256"/>
-        <v>130.57357325359413</v>
+        <f t="shared" si="258"/>
+        <v>138.00808720839805</v>
       </c>
       <c r="BE37" s="7">
-        <f t="shared" si="256"/>
-        <v>136.54052591984174</v>
+        <f t="shared" si="258"/>
+        <v>144.08319975706988</v>
       </c>
       <c r="BF37" s="7">
-        <f t="shared" si="256"/>
-        <v>142.66037239314022</v>
+        <f t="shared" si="258"/>
+        <v>150.31296400605194</v>
       </c>
       <c r="BG37" s="7">
-        <f t="shared" ref="BG37" si="257">BG17</f>
-        <v>148.93650615498763</v>
+        <f t="shared" ref="BG37" si="259">BG17</f>
+        <v>156.70080454208221</v>
       </c>
       <c r="BI37"/>
       <c r="BJ37"/>
@@ -6917,35 +6949,35 @@
         <v>72.930815999999993</v>
       </c>
       <c r="AZ38" s="4">
-        <f t="shared" ref="AZ38:BF38" si="258">AY38*0.96</f>
+        <f t="shared" ref="AZ38:BF38" si="260">AY38*0.96</f>
         <v>70.013583359999984</v>
       </c>
       <c r="BA38" s="4">
-        <f t="shared" si="258"/>
+        <f t="shared" si="260"/>
         <v>67.21304002559998</v>
       </c>
       <c r="BB38" s="4">
-        <f t="shared" si="258"/>
+        <f t="shared" si="260"/>
         <v>64.524518424575973</v>
       </c>
       <c r="BC38" s="4">
-        <f t="shared" si="258"/>
+        <f t="shared" si="260"/>
         <v>61.943537687592929</v>
       </c>
       <c r="BD38" s="4">
-        <f t="shared" si="258"/>
+        <f t="shared" si="260"/>
         <v>59.465796180089207</v>
       </c>
       <c r="BE38" s="4">
-        <f t="shared" si="258"/>
+        <f t="shared" si="260"/>
         <v>57.087164332885635</v>
       </c>
       <c r="BF38" s="4">
-        <f t="shared" si="258"/>
+        <f t="shared" si="260"/>
         <v>54.803677759570206</v>
       </c>
       <c r="BG38" s="4">
-        <f t="shared" ref="BG38" si="259">BF38*0.96</f>
+        <f t="shared" ref="BG38" si="261">BF38*0.96</f>
         <v>52.611530649187394</v>
       </c>
     </row>
@@ -6970,43 +7002,43 @@
         <v>63.545999999999999</v>
       </c>
       <c r="AX39" s="4">
-        <f t="shared" ref="AX39:BF39" si="260">AW39*1.02</f>
+        <f t="shared" ref="AX39:BF39" si="262">AW39*1.02</f>
         <v>64.816919999999996</v>
       </c>
       <c r="AY39" s="4">
-        <f t="shared" si="260"/>
+        <f t="shared" si="262"/>
         <v>66.113258399999992</v>
       </c>
       <c r="AZ39" s="4">
-        <f t="shared" si="260"/>
+        <f t="shared" si="262"/>
         <v>67.435523567999994</v>
       </c>
       <c r="BA39" s="4">
-        <f t="shared" si="260"/>
+        <f t="shared" si="262"/>
         <v>68.784234039360001</v>
       </c>
       <c r="BB39" s="4">
-        <f t="shared" si="260"/>
+        <f t="shared" si="262"/>
         <v>70.159918720147203</v>
       </c>
       <c r="BC39" s="4">
-        <f t="shared" si="260"/>
+        <f t="shared" si="262"/>
         <v>71.563117094550151</v>
       </c>
       <c r="BD39" s="4">
-        <f t="shared" si="260"/>
+        <f t="shared" si="262"/>
         <v>72.99437943644115</v>
       </c>
       <c r="BE39" s="4">
-        <f t="shared" si="260"/>
+        <f t="shared" si="262"/>
         <v>74.454267025169969</v>
       </c>
       <c r="BF39" s="4">
-        <f t="shared" si="260"/>
+        <f t="shared" si="262"/>
         <v>75.943352365673363</v>
       </c>
       <c r="BG39" s="4">
-        <f t="shared" ref="BG39" si="261">BF39*1.02</f>
+        <f t="shared" ref="BG39" si="263">BF39*1.02</f>
         <v>77.462219412986826</v>
       </c>
     </row>
@@ -7636,47 +7668,47 @@
       </c>
       <c r="AW52" s="7">
         <f>AW37+SUM(AW38:AW51)</f>
-        <v>149.69995299999997</v>
+        <v>167.10295299999996</v>
       </c>
       <c r="AX52" s="7">
-        <f t="shared" ref="AX52:BG52" si="262">AX37+SUM(AX38:AX51)</f>
-        <v>171.29396634400001</v>
+        <f t="shared" ref="AX52:BG52" si="264">AX37+SUM(AX38:AX51)</f>
+        <v>177.71719034400013</v>
       </c>
       <c r="AY52" s="7">
-        <f t="shared" si="262"/>
-        <v>210.59581120275197</v>
+        <f t="shared" si="264"/>
+        <v>217.288021634752</v>
       </c>
       <c r="AZ52" s="7">
-        <f t="shared" si="262"/>
-        <v>231.58526192482185</v>
+        <f t="shared" si="264"/>
+        <v>238.50231583867796</v>
       </c>
       <c r="BA52" s="7">
-        <f t="shared" si="262"/>
-        <v>249.4421922895072</v>
+        <f t="shared" si="264"/>
+        <v>256.5616570293621</v>
       </c>
       <c r="BB52" s="7">
-        <f t="shared" si="262"/>
-        <v>253.76866258234497</v>
+        <f t="shared" si="264"/>
+        <v>260.99200236218769</v>
       </c>
       <c r="BC52" s="7">
-        <f t="shared" si="262"/>
-        <v>258.26283853214295</v>
+        <f t="shared" si="264"/>
+        <v>265.59091991262505</v>
       </c>
       <c r="BD52" s="7">
-        <f t="shared" si="262"/>
-        <v>263.0337488701245</v>
+        <f t="shared" si="264"/>
+        <v>270.46826282492839</v>
       </c>
       <c r="BE52" s="7">
-        <f t="shared" si="262"/>
-        <v>268.08195727789735</v>
+        <f t="shared" si="264"/>
+        <v>275.62463111512545</v>
       </c>
       <c r="BF52" s="7">
-        <f t="shared" si="262"/>
-        <v>273.40740251838378</v>
+        <f t="shared" si="264"/>
+        <v>281.05999413129553</v>
       </c>
       <c r="BG52" s="7">
-        <f t="shared" si="262"/>
-        <v>279.01025621716184</v>
+        <f t="shared" si="264"/>
+        <v>286.77455460425642</v>
       </c>
       <c r="BI52"/>
       <c r="BJ52"/>
@@ -7705,39 +7737,39 @@
         <v>42</v>
       </c>
       <c r="AY53" s="4">
-        <f t="shared" ref="AY53:BF53" si="263">AX53*1.05</f>
+        <f t="shared" ref="AY53:BF53" si="265">AX53*1.05</f>
         <v>44.1</v>
       </c>
       <c r="AZ53" s="4">
-        <f t="shared" si="263"/>
+        <f t="shared" si="265"/>
         <v>46.305000000000007</v>
       </c>
       <c r="BA53" s="4">
-        <f t="shared" si="263"/>
+        <f t="shared" si="265"/>
         <v>48.620250000000006</v>
       </c>
       <c r="BB53" s="4">
-        <f t="shared" si="263"/>
+        <f t="shared" si="265"/>
         <v>51.051262500000007</v>
       </c>
       <c r="BC53" s="4">
-        <f t="shared" si="263"/>
+        <f t="shared" si="265"/>
         <v>53.603825625000013</v>
       </c>
       <c r="BD53" s="4">
-        <f t="shared" si="263"/>
+        <f t="shared" si="265"/>
         <v>56.284016906250017</v>
       </c>
       <c r="BE53" s="4">
-        <f t="shared" si="263"/>
+        <f t="shared" si="265"/>
         <v>59.098217751562522</v>
       </c>
       <c r="BF53" s="4">
-        <f t="shared" si="263"/>
+        <f t="shared" si="265"/>
         <v>62.053128639140652</v>
       </c>
       <c r="BG53" s="4">
-        <f t="shared" ref="BG53" si="264">BF53*1.05</f>
+        <f t="shared" ref="BG53" si="266">BF53*1.05</f>
         <v>65.155785071097682</v>
       </c>
     </row>
@@ -7763,399 +7795,399 @@
       </c>
       <c r="AW54" s="7">
         <f>AW52-AW53</f>
-        <v>109.69995299999997</v>
+        <v>127.10295299999996</v>
       </c>
       <c r="AX54" s="7">
-        <f t="shared" ref="AX54:BG54" si="265">AX52-AX53</f>
-        <v>129.29396634400001</v>
+        <f t="shared" ref="AX54:BG54" si="267">AX52-AX53</f>
+        <v>135.71719034400013</v>
       </c>
       <c r="AY54" s="7">
-        <f t="shared" si="265"/>
-        <v>166.49581120275198</v>
+        <f t="shared" si="267"/>
+        <v>173.188021634752</v>
       </c>
       <c r="AZ54" s="7">
-        <f t="shared" si="265"/>
-        <v>185.28026192482184</v>
+        <f t="shared" si="267"/>
+        <v>192.19731583867795</v>
       </c>
       <c r="BA54" s="7">
-        <f t="shared" si="265"/>
-        <v>200.82194228950721</v>
+        <f t="shared" si="267"/>
+        <v>207.9414070293621</v>
       </c>
       <c r="BB54" s="7">
-        <f t="shared" si="265"/>
-        <v>202.71740008234497</v>
+        <f t="shared" si="267"/>
+        <v>209.94073986218768</v>
       </c>
       <c r="BC54" s="7">
-        <f t="shared" si="265"/>
-        <v>204.65901290714294</v>
+        <f t="shared" si="267"/>
+        <v>211.98709428762504</v>
       </c>
       <c r="BD54" s="7">
-        <f t="shared" si="265"/>
-        <v>206.74973196387447</v>
+        <f t="shared" si="267"/>
+        <v>214.18424591867836</v>
       </c>
       <c r="BE54" s="7">
-        <f t="shared" si="265"/>
-        <v>208.98373952633483</v>
+        <f t="shared" si="267"/>
+        <v>216.52641336356294</v>
       </c>
       <c r="BF54" s="7">
-        <f t="shared" si="265"/>
-        <v>211.35427387924312</v>
+        <f t="shared" si="267"/>
+        <v>219.00686549215487</v>
       </c>
       <c r="BG54" s="7">
-        <f t="shared" si="265"/>
-        <v>213.85447114606416</v>
+        <f t="shared" si="267"/>
+        <v>221.61876953315874</v>
       </c>
       <c r="BH54" s="1">
-        <f t="shared" ref="BH54:DS54" si="266">BG54*(1+$BJ$26)</f>
-        <v>211.71592643460352</v>
+        <f t="shared" ref="BH54:DS54" si="268">BG54*(1+$BJ$26)</f>
+        <v>219.40258183782714</v>
       </c>
       <c r="BI54" s="1">
-        <f t="shared" si="266"/>
-        <v>209.59876717025747</v>
+        <f t="shared" si="268"/>
+        <v>217.20855601944888</v>
       </c>
       <c r="BJ54" s="1">
-        <f t="shared" si="266"/>
-        <v>207.5027794985549</v>
+        <f t="shared" si="268"/>
+        <v>215.03647045925439</v>
       </c>
       <c r="BK54" s="1">
-        <f t="shared" si="266"/>
-        <v>205.42775170356936</v>
+        <f t="shared" si="268"/>
+        <v>212.88610575466186</v>
       </c>
       <c r="BL54" s="1">
-        <f t="shared" si="266"/>
-        <v>203.37347418653366</v>
+        <f t="shared" si="268"/>
+        <v>210.75724469711523</v>
       </c>
       <c r="BM54" s="1">
-        <f t="shared" si="266"/>
-        <v>201.33973944466831</v>
+        <f t="shared" si="268"/>
+        <v>208.64967225014408</v>
       </c>
       <c r="BN54" s="1">
-        <f t="shared" si="266"/>
-        <v>199.32634205022163</v>
+        <f t="shared" si="268"/>
+        <v>206.56317552764264</v>
       </c>
       <c r="BO54" s="1">
-        <f t="shared" si="266"/>
-        <v>197.33307862971941</v>
+        <f t="shared" si="268"/>
+        <v>204.49754377236621</v>
       </c>
       <c r="BP54" s="1">
-        <f t="shared" si="266"/>
-        <v>195.35974784342221</v>
+        <f t="shared" si="268"/>
+        <v>202.45256833464256</v>
       </c>
       <c r="BQ54" s="1">
-        <f t="shared" si="266"/>
-        <v>193.40615036498798</v>
+        <f t="shared" si="268"/>
+        <v>200.42804265129612</v>
       </c>
       <c r="BR54" s="1">
-        <f t="shared" si="266"/>
-        <v>191.47208886133811</v>
+        <f t="shared" si="268"/>
+        <v>198.42376222478316</v>
       </c>
       <c r="BS54" s="1">
-        <f t="shared" si="266"/>
-        <v>189.55736797272473</v>
+        <f t="shared" si="268"/>
+        <v>196.43952460253533</v>
       </c>
       <c r="BT54" s="1">
-        <f t="shared" si="266"/>
-        <v>187.66179429299748</v>
+        <f t="shared" si="268"/>
+        <v>194.47512935650997</v>
       </c>
       <c r="BU54" s="1">
-        <f t="shared" si="266"/>
-        <v>185.7851763500675</v>
+        <f t="shared" si="268"/>
+        <v>192.53037806294486</v>
       </c>
       <c r="BV54" s="1">
-        <f t="shared" si="266"/>
-        <v>183.92732458656681</v>
+        <f t="shared" si="268"/>
+        <v>190.6050742823154</v>
       </c>
       <c r="BW54" s="1">
-        <f t="shared" si="266"/>
-        <v>182.08805134070113</v>
+        <f t="shared" si="268"/>
+        <v>188.69902353949223</v>
       </c>
       <c r="BX54" s="1">
-        <f t="shared" si="266"/>
-        <v>180.26717082729411</v>
+        <f t="shared" si="268"/>
+        <v>186.8120333040973</v>
       </c>
       <c r="BY54" s="1">
-        <f t="shared" si="266"/>
-        <v>178.46449911902116</v>
+        <f t="shared" si="268"/>
+        <v>184.94391297105633</v>
       </c>
       <c r="BZ54" s="1">
-        <f t="shared" si="266"/>
-        <v>176.67985412783094</v>
+        <f t="shared" si="268"/>
+        <v>183.09447384134577</v>
       </c>
       <c r="CA54" s="1">
-        <f t="shared" si="266"/>
-        <v>174.91305558655262</v>
+        <f t="shared" si="268"/>
+        <v>181.26352910293232</v>
       </c>
       <c r="CB54" s="1">
-        <f t="shared" si="266"/>
-        <v>173.1639250306871</v>
+        <f t="shared" si="268"/>
+        <v>179.450893811903</v>
       </c>
       <c r="CC54" s="1">
-        <f t="shared" si="266"/>
-        <v>171.43228578038023</v>
+        <f t="shared" si="268"/>
+        <v>177.65638487378396</v>
       </c>
       <c r="CD54" s="1">
-        <f t="shared" si="266"/>
-        <v>169.71796292257642</v>
+        <f t="shared" si="268"/>
+        <v>175.87982102504611</v>
       </c>
       <c r="CE54" s="1">
-        <f t="shared" si="266"/>
-        <v>168.02078329335066</v>
+        <f t="shared" si="268"/>
+        <v>174.12102281479565</v>
       </c>
       <c r="CF54" s="1">
-        <f t="shared" si="266"/>
-        <v>166.34057546041714</v>
+        <f t="shared" si="268"/>
+        <v>172.37981258664769</v>
       </c>
       <c r="CG54" s="1">
-        <f t="shared" si="266"/>
-        <v>164.67716970581296</v>
+        <f t="shared" si="268"/>
+        <v>170.65601446078122</v>
       </c>
       <c r="CH54" s="1">
-        <f t="shared" si="266"/>
-        <v>163.03039800875482</v>
+        <f t="shared" si="268"/>
+        <v>168.94945431617342</v>
       </c>
       <c r="CI54" s="1">
-        <f t="shared" si="266"/>
-        <v>161.40009402866727</v>
+        <f t="shared" si="268"/>
+        <v>167.25995977301167</v>
       </c>
       <c r="CJ54" s="1">
-        <f t="shared" si="266"/>
-        <v>159.7860930883806</v>
+        <f t="shared" si="268"/>
+        <v>165.58736017528156</v>
       </c>
       <c r="CK54" s="1">
-        <f t="shared" si="266"/>
-        <v>158.1882321574968</v>
+        <f t="shared" si="268"/>
+        <v>163.93148657352873</v>
       </c>
       <c r="CL54" s="1">
-        <f t="shared" si="266"/>
-        <v>156.60634983592183</v>
+        <f t="shared" si="268"/>
+        <v>162.29217170779344</v>
       </c>
       <c r="CM54" s="1">
-        <f t="shared" si="266"/>
-        <v>155.04028633756261</v>
+        <f t="shared" si="268"/>
+        <v>160.66924999071551</v>
       </c>
       <c r="CN54" s="1">
-        <f t="shared" si="266"/>
-        <v>153.48988347418697</v>
+        <f t="shared" si="268"/>
+        <v>159.06255749080836</v>
       </c>
       <c r="CO54" s="1">
-        <f t="shared" si="266"/>
-        <v>151.95498463944509</v>
+        <f t="shared" si="268"/>
+        <v>157.47193191590029</v>
       </c>
       <c r="CP54" s="1">
-        <f t="shared" si="266"/>
-        <v>150.43543479305063</v>
+        <f t="shared" si="268"/>
+        <v>155.89721259674127</v>
       </c>
       <c r="CQ54" s="1">
-        <f t="shared" si="266"/>
-        <v>148.93108044512013</v>
+        <f t="shared" si="268"/>
+        <v>154.33824047077385</v>
       </c>
       <c r="CR54" s="1">
-        <f t="shared" si="266"/>
-        <v>147.44176964066892</v>
+        <f t="shared" si="268"/>
+        <v>152.79485806606613</v>
       </c>
       <c r="CS54" s="1">
-        <f t="shared" si="266"/>
-        <v>145.96735194426222</v>
+        <f t="shared" si="268"/>
+        <v>151.26690948540548</v>
       </c>
       <c r="CT54" s="1">
-        <f t="shared" si="266"/>
-        <v>144.5076784248196</v>
+        <f t="shared" si="268"/>
+        <v>149.75424039055142</v>
       </c>
       <c r="CU54" s="1">
-        <f t="shared" si="266"/>
-        <v>143.06260164057142</v>
+        <f t="shared" si="268"/>
+        <v>148.25669798664589</v>
       </c>
       <c r="CV54" s="1">
-        <f t="shared" si="266"/>
-        <v>141.6319756241657</v>
+        <f t="shared" si="268"/>
+        <v>146.77413100677944</v>
       </c>
       <c r="CW54" s="1">
-        <f t="shared" si="266"/>
-        <v>140.21565586792406</v>
+        <f t="shared" si="268"/>
+        <v>145.30638969671165</v>
       </c>
       <c r="CX54" s="1">
-        <f t="shared" si="266"/>
-        <v>138.8134993092448</v>
+        <f t="shared" si="268"/>
+        <v>143.85332579974454</v>
       </c>
       <c r="CY54" s="1">
-        <f t="shared" si="266"/>
-        <v>137.42536431615235</v>
+        <f t="shared" si="268"/>
+        <v>142.41479254174709</v>
       </c>
       <c r="CZ54" s="1">
-        <f t="shared" si="266"/>
-        <v>136.05111067299083</v>
+        <f t="shared" si="268"/>
+        <v>140.9906446163296</v>
       </c>
       <c r="DA54" s="1">
-        <f t="shared" si="266"/>
-        <v>134.69059956626091</v>
+        <f t="shared" si="268"/>
+        <v>139.58073817016631</v>
       </c>
       <c r="DB54" s="1">
-        <f t="shared" si="266"/>
-        <v>133.3436935705983</v>
+        <f t="shared" si="268"/>
+        <v>138.18493078846464</v>
       </c>
       <c r="DC54" s="1">
-        <f t="shared" si="266"/>
-        <v>132.01025663489233</v>
+        <f t="shared" si="268"/>
+        <v>136.80308148058</v>
       </c>
       <c r="DD54" s="1">
-        <f t="shared" si="266"/>
-        <v>130.69015406854339</v>
+        <f t="shared" si="268"/>
+        <v>135.43505066577421</v>
       </c>
       <c r="DE54" s="1">
-        <f t="shared" si="266"/>
-        <v>129.38325252785796</v>
+        <f t="shared" si="268"/>
+        <v>134.08070015911647</v>
       </c>
       <c r="DF54" s="1">
-        <f t="shared" si="266"/>
-        <v>128.08942000257937</v>
+        <f t="shared" si="268"/>
+        <v>132.7398931575253</v>
       </c>
       <c r="DG54" s="1">
-        <f t="shared" si="266"/>
-        <v>126.80852580255358</v>
+        <f t="shared" si="268"/>
+        <v>131.41249422595004</v>
       </c>
       <c r="DH54" s="1">
-        <f t="shared" si="266"/>
-        <v>125.54044054452804</v>
+        <f t="shared" si="268"/>
+        <v>130.09836928369054</v>
       </c>
       <c r="DI54" s="1">
-        <f t="shared" si="266"/>
-        <v>124.28503613908276</v>
+        <f t="shared" si="268"/>
+        <v>128.79738559085365</v>
       </c>
       <c r="DJ54" s="1">
-        <f t="shared" si="266"/>
-        <v>123.04218577769194</v>
+        <f t="shared" si="268"/>
+        <v>127.50941173494512</v>
       </c>
       <c r="DK54" s="1">
-        <f t="shared" si="266"/>
-        <v>121.81176391991502</v>
+        <f t="shared" si="268"/>
+        <v>126.23431761759566</v>
       </c>
       <c r="DL54" s="1">
-        <f t="shared" si="266"/>
-        <v>120.59364628071587</v>
+        <f t="shared" si="268"/>
+        <v>124.9719744414197</v>
       </c>
       <c r="DM54" s="1">
-        <f t="shared" si="266"/>
-        <v>119.38770981790871</v>
+        <f t="shared" si="268"/>
+        <v>123.72225469700551</v>
       </c>
       <c r="DN54" s="1">
-        <f t="shared" si="266"/>
-        <v>118.19383271972963</v>
+        <f t="shared" si="268"/>
+        <v>122.48503215003545</v>
       </c>
       <c r="DO54" s="1">
-        <f t="shared" si="266"/>
-        <v>117.01189439253233</v>
+        <f t="shared" si="268"/>
+        <v>121.2601818285351</v>
       </c>
       <c r="DP54" s="1">
-        <f t="shared" si="266"/>
-        <v>115.841775448607</v>
+        <f t="shared" si="268"/>
+        <v>120.04758001024975</v>
       </c>
       <c r="DQ54" s="1">
-        <f t="shared" si="266"/>
-        <v>114.68335769412093</v>
+        <f t="shared" si="268"/>
+        <v>118.84710421014725</v>
       </c>
       <c r="DR54" s="1">
-        <f t="shared" si="266"/>
-        <v>113.53652411717972</v>
+        <f t="shared" si="268"/>
+        <v>117.65863316804578</v>
       </c>
       <c r="DS54" s="1">
-        <f t="shared" si="266"/>
-        <v>112.40115887600793</v>
+        <f t="shared" si="268"/>
+        <v>116.48204683636533</v>
       </c>
       <c r="DT54" s="1">
-        <f t="shared" ref="DT54:EQ54" si="267">DS54*(1+$BJ$26)</f>
-        <v>111.27714728724784</v>
+        <f t="shared" ref="DT54:EQ54" si="269">DS54*(1+$BJ$26)</f>
+        <v>115.31722636800167</v>
       </c>
       <c r="DU54" s="1">
-        <f t="shared" si="267"/>
-        <v>110.16437581437536</v>
+        <f t="shared" si="269"/>
+        <v>114.16405410432165</v>
       </c>
       <c r="DV54" s="1">
-        <f t="shared" si="267"/>
-        <v>109.06273205623161</v>
+        <f t="shared" si="269"/>
+        <v>113.02241356327843</v>
       </c>
       <c r="DW54" s="1">
-        <f t="shared" si="267"/>
-        <v>107.97210473566929</v>
+        <f t="shared" si="269"/>
+        <v>111.89218942764565</v>
       </c>
       <c r="DX54" s="1">
-        <f t="shared" si="267"/>
-        <v>106.89238368831259</v>
+        <f t="shared" si="269"/>
+        <v>110.77326753336919</v>
       </c>
       <c r="DY54" s="1">
-        <f t="shared" si="267"/>
-        <v>105.82345985142946</v>
+        <f t="shared" si="269"/>
+        <v>109.6655348580355</v>
       </c>
       <c r="DZ54" s="1">
-        <f t="shared" si="267"/>
-        <v>104.76522525291517</v>
+        <f t="shared" si="269"/>
+        <v>108.56887950945514</v>
       </c>
       <c r="EA54" s="1">
-        <f t="shared" si="267"/>
-        <v>103.71757300038603</v>
+        <f t="shared" si="269"/>
+        <v>107.48319071436059</v>
       </c>
       <c r="EB54" s="1">
-        <f t="shared" si="267"/>
-        <v>102.68039727038216</v>
+        <f t="shared" si="269"/>
+        <v>106.40835880721698</v>
       </c>
       <c r="EC54" s="1">
-        <f t="shared" si="267"/>
-        <v>101.65359329767834</v>
+        <f t="shared" si="269"/>
+        <v>105.34427521914482</v>
       </c>
       <c r="ED54" s="1">
-        <f t="shared" si="267"/>
-        <v>100.63705736470156</v>
+        <f t="shared" si="269"/>
+        <v>104.29083246695338</v>
       </c>
       <c r="EE54" s="1">
-        <f t="shared" si="267"/>
-        <v>99.630686791054544</v>
+        <f t="shared" si="269"/>
+        <v>103.24792414228384</v>
       </c>
       <c r="EF54" s="1">
-        <f t="shared" si="267"/>
-        <v>98.634379923143996</v>
+        <f t="shared" si="269"/>
+        <v>102.215444900861</v>
       </c>
       <c r="EG54" s="1">
-        <f t="shared" si="267"/>
-        <v>97.648036123912561</v>
+        <f t="shared" si="269"/>
+        <v>101.19329045185239</v>
       </c>
       <c r="EH54" s="1">
-        <f t="shared" si="267"/>
-        <v>96.671555762673435</v>
+        <f t="shared" si="269"/>
+        <v>100.18135754733386</v>
       </c>
       <c r="EI54" s="1">
-        <f t="shared" si="267"/>
-        <v>95.704840205046693</v>
+        <f t="shared" si="269"/>
+        <v>99.179543971860525</v>
       </c>
       <c r="EJ54" s="1">
-        <f t="shared" si="267"/>
-        <v>94.747791802996232</v>
+        <f t="shared" si="269"/>
+        <v>98.187748532141924</v>
       </c>
       <c r="EK54" s="1">
-        <f t="shared" si="267"/>
-        <v>93.800313884966272</v>
+        <f t="shared" si="269"/>
+        <v>97.205871046820505</v>
       </c>
       <c r="EL54" s="1">
-        <f t="shared" si="267"/>
-        <v>92.862310746116606</v>
+        <f t="shared" si="269"/>
+        <v>96.233812336352301</v>
       </c>
       <c r="EM54" s="1">
-        <f t="shared" si="267"/>
-        <v>91.933687638655442</v>
+        <f t="shared" si="269"/>
+        <v>95.271474212988778</v>
       </c>
       <c r="EN54" s="1">
-        <f t="shared" si="267"/>
-        <v>91.01435076226889</v>
+        <f t="shared" si="269"/>
+        <v>94.318759470858893</v>
       </c>
       <c r="EO54" s="1">
-        <f t="shared" si="267"/>
-        <v>90.104207254646198</v>
+        <f t="shared" si="269"/>
+        <v>93.375571876150303</v>
       </c>
       <c r="EP54" s="1">
-        <f t="shared" si="267"/>
-        <v>89.203165182099738</v>
+        <f t="shared" si="269"/>
+        <v>92.4418161573888</v>
       </c>
       <c r="EQ54" s="1">
-        <f t="shared" si="267"/>
-        <v>88.311133530278738</v>
+        <f t="shared" si="269"/>
+        <v>91.517397995814918</v>
       </c>
     </row>
     <row r="56" spans="2:147" x14ac:dyDescent="0.3">
@@ -8164,7 +8196,7 @@
       </c>
       <c r="BJ56" s="4">
         <f>NPV(BJ27,AW54:EQ54)</f>
-        <v>1818.4166107360506</v>
+        <v>1898.3854257513749</v>
       </c>
     </row>
     <row r="57" spans="2:147" x14ac:dyDescent="0.3">
@@ -8173,7 +8205,7 @@
       </c>
       <c r="BJ57" s="4">
         <f>Main!D8</f>
-        <v>227.6</v>
+        <v>363.5</v>
       </c>
     </row>
     <row r="58" spans="2:147" x14ac:dyDescent="0.3">
@@ -8182,7 +8214,7 @@
       </c>
       <c r="BJ58" s="4">
         <f>BJ56+BJ57</f>
-        <v>2046.0166107360506</v>
+        <v>2261.8854257513749</v>
       </c>
     </row>
     <row r="59" spans="2:147" x14ac:dyDescent="0.3">
@@ -8191,7 +8223,7 @@
       </c>
       <c r="BJ59" s="5">
         <f>BJ58/BF18</f>
-        <v>16.965311863483006</v>
+        <v>18.755268870243572</v>
       </c>
     </row>
     <row r="60" spans="2:147" x14ac:dyDescent="0.3">
@@ -8200,7 +8232,7 @@
       </c>
       <c r="BJ60" s="5">
         <f>Main!D3</f>
-        <v>16.64</v>
+        <v>16.41</v>
       </c>
     </row>
     <row r="61" spans="2:147" x14ac:dyDescent="0.3">
@@ -8209,7 +8241,7 @@
       </c>
       <c r="BJ61" s="8">
         <f>BJ59/BJ60-1</f>
-        <v>1.9549991795853705E-2</v>
+        <v>0.14291705485944983</v>
       </c>
     </row>
   </sheetData>
